--- a/data/seat/04-abril2026.xlsx
+++ b/data/seat/04-abril2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoefe.sharepoint.com/sites/GOFEFEVALPARASO/Documentos compartidos/UNIDAD DE GESTION/Datos Operacionales/Energía/SEAT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{2315B196-EB3F-49CD-81C9-DCAB73BD5354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6607D11D-9622-4F70-B387-ECFAE947A5B8}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{466AE003-77E3-4875-813A-539BD3A3DB7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{193354A9-05D4-492B-A2F4-99529545814F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2012,6 +2012,60 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2042,39 +2096,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2087,31 +2108,10 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4063,37 +4063,37 @@
                   <c:v>2398</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>2833</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0</c:v>
+                  <c:v>2854</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
+                  <c:v>3079</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0</c:v>
+                  <c:v>2981</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0</c:v>
+                  <c:v>2808</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0</c:v>
+                  <c:v>2489</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0</c:v>
+                  <c:v>2506</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0</c:v>
+                  <c:v>2946</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0</c:v>
+                  <c:v>2948</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0</c:v>
+                  <c:v>2963</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0</c:v>
+                  <c:v>3010</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6987,293 +6987,293 @@
       <c r="A1" s="127">
         <v>1.1111111E+55</v>
       </c>
-      <c r="B1" s="183" t="s">
+      <c r="B1" s="201" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="128"/>
-      <c r="D1" s="185" t="s">
+      <c r="D1" s="203" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="186"/>
-      <c r="F1" s="186"/>
-      <c r="G1" s="186"/>
-      <c r="H1" s="186"/>
-      <c r="I1" s="186"/>
-      <c r="J1" s="186"/>
-      <c r="K1" s="186"/>
-      <c r="L1" s="186"/>
-      <c r="M1" s="186"/>
-      <c r="N1" s="186"/>
-      <c r="O1" s="187"/>
-      <c r="P1" s="188"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="204"/>
+      <c r="I1" s="204"/>
+      <c r="J1" s="204"/>
+      <c r="K1" s="204"/>
+      <c r="L1" s="204"/>
+      <c r="M1" s="204"/>
+      <c r="N1" s="204"/>
+      <c r="O1" s="205"/>
+      <c r="P1" s="206"/>
       <c r="Q1" s="129"/>
-      <c r="R1" s="193" t="s">
+      <c r="R1" s="183" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="194"/>
-      <c r="W1" s="194"/>
-      <c r="X1" s="194"/>
-      <c r="Y1" s="194"/>
-      <c r="Z1" s="194"/>
-      <c r="AA1" s="195"/>
+      <c r="S1" s="184"/>
+      <c r="T1" s="184"/>
+      <c r="U1" s="184"/>
+      <c r="V1" s="184"/>
+      <c r="W1" s="184"/>
+      <c r="X1" s="184"/>
+      <c r="Y1" s="184"/>
+      <c r="Z1" s="184"/>
+      <c r="AA1" s="185"/>
       <c r="AB1" s="130"/>
-      <c r="AC1" s="193" t="s">
+      <c r="AC1" s="183" t="s">
         <v>3</v>
       </c>
-      <c r="AD1" s="194"/>
-      <c r="AE1" s="194"/>
-      <c r="AF1" s="194"/>
-      <c r="AG1" s="194"/>
-      <c r="AH1" s="194"/>
-      <c r="AI1" s="194"/>
-      <c r="AJ1" s="194"/>
-      <c r="AK1" s="195"/>
+      <c r="AD1" s="184"/>
+      <c r="AE1" s="184"/>
+      <c r="AF1" s="184"/>
+      <c r="AG1" s="184"/>
+      <c r="AH1" s="184"/>
+      <c r="AI1" s="184"/>
+      <c r="AJ1" s="184"/>
+      <c r="AK1" s="185"/>
       <c r="AL1" s="131"/>
-      <c r="AM1" s="193" t="s">
+      <c r="AM1" s="183" t="s">
         <v>4</v>
       </c>
-      <c r="AN1" s="194"/>
-      <c r="AO1" s="194"/>
-      <c r="AP1" s="194"/>
-      <c r="AQ1" s="194"/>
-      <c r="AR1" s="194"/>
-      <c r="AS1" s="194"/>
-      <c r="AT1" s="194"/>
-      <c r="AU1" s="195"/>
+      <c r="AN1" s="184"/>
+      <c r="AO1" s="184"/>
+      <c r="AP1" s="184"/>
+      <c r="AQ1" s="184"/>
+      <c r="AR1" s="184"/>
+      <c r="AS1" s="184"/>
+      <c r="AT1" s="184"/>
+      <c r="AU1" s="185"/>
       <c r="AV1" s="131"/>
-      <c r="AW1" s="193" t="s">
+      <c r="AW1" s="183" t="s">
         <v>57</v>
       </c>
-      <c r="AX1" s="194"/>
-      <c r="AY1" s="194"/>
-      <c r="AZ1" s="194"/>
-      <c r="BA1" s="194"/>
-      <c r="BB1" s="194"/>
-      <c r="BC1" s="194"/>
-      <c r="BD1" s="194"/>
-      <c r="BE1" s="194"/>
-      <c r="BF1" s="194"/>
-      <c r="BG1" s="194"/>
-      <c r="BH1" s="195"/>
+      <c r="AX1" s="184"/>
+      <c r="AY1" s="184"/>
+      <c r="AZ1" s="184"/>
+      <c r="BA1" s="184"/>
+      <c r="BB1" s="184"/>
+      <c r="BC1" s="184"/>
+      <c r="BD1" s="184"/>
+      <c r="BE1" s="184"/>
+      <c r="BF1" s="184"/>
+      <c r="BG1" s="184"/>
+      <c r="BH1" s="185"/>
       <c r="BI1" s="131"/>
-      <c r="BJ1" s="193" t="s">
+      <c r="BJ1" s="183" t="s">
         <v>5</v>
       </c>
-      <c r="BK1" s="194"/>
-      <c r="BL1" s="194"/>
-      <c r="BM1" s="194"/>
-      <c r="BN1" s="194"/>
-      <c r="BO1" s="194"/>
-      <c r="BP1" s="194"/>
-      <c r="BQ1" s="194"/>
-      <c r="BR1" s="195"/>
+      <c r="BK1" s="184"/>
+      <c r="BL1" s="184"/>
+      <c r="BM1" s="184"/>
+      <c r="BN1" s="184"/>
+      <c r="BO1" s="184"/>
+      <c r="BP1" s="184"/>
+      <c r="BQ1" s="184"/>
+      <c r="BR1" s="185"/>
       <c r="BS1" s="132"/>
     </row>
     <row r="2" spans="1:71" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="183"/>
+      <c r="B2" s="201"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="189"/>
-      <c r="E2" s="190"/>
-      <c r="F2" s="190"/>
-      <c r="G2" s="190"/>
-      <c r="H2" s="190"/>
-      <c r="I2" s="190"/>
-      <c r="J2" s="190"/>
-      <c r="K2" s="190"/>
-      <c r="L2" s="190"/>
-      <c r="M2" s="190"/>
-      <c r="N2" s="190"/>
-      <c r="O2" s="191"/>
-      <c r="P2" s="192"/>
+      <c r="D2" s="207"/>
+      <c r="E2" s="208"/>
+      <c r="F2" s="208"/>
+      <c r="G2" s="208"/>
+      <c r="H2" s="208"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="208"/>
+      <c r="M2" s="208"/>
+      <c r="N2" s="208"/>
+      <c r="O2" s="209"/>
+      <c r="P2" s="210"/>
       <c r="Q2" s="58"/>
-      <c r="R2" s="196"/>
-      <c r="S2" s="197"/>
-      <c r="T2" s="197"/>
-      <c r="U2" s="197"/>
-      <c r="V2" s="197"/>
-      <c r="W2" s="197"/>
-      <c r="X2" s="197"/>
-      <c r="Y2" s="197"/>
-      <c r="Z2" s="197"/>
-      <c r="AA2" s="198"/>
+      <c r="R2" s="186"/>
+      <c r="S2" s="187"/>
+      <c r="T2" s="187"/>
+      <c r="U2" s="187"/>
+      <c r="V2" s="187"/>
+      <c r="W2" s="187"/>
+      <c r="X2" s="187"/>
+      <c r="Y2" s="187"/>
+      <c r="Z2" s="187"/>
+      <c r="AA2" s="188"/>
       <c r="AB2" s="60"/>
-      <c r="AC2" s="196"/>
-      <c r="AD2" s="197"/>
-      <c r="AE2" s="197"/>
-      <c r="AF2" s="197"/>
-      <c r="AG2" s="197"/>
-      <c r="AH2" s="197"/>
-      <c r="AI2" s="197"/>
-      <c r="AJ2" s="197"/>
-      <c r="AK2" s="198"/>
+      <c r="AC2" s="186"/>
+      <c r="AD2" s="187"/>
+      <c r="AE2" s="187"/>
+      <c r="AF2" s="187"/>
+      <c r="AG2" s="187"/>
+      <c r="AH2" s="187"/>
+      <c r="AI2" s="187"/>
+      <c r="AJ2" s="187"/>
+      <c r="AK2" s="188"/>
       <c r="AL2" s="59"/>
-      <c r="AM2" s="196"/>
-      <c r="AN2" s="197"/>
-      <c r="AO2" s="197"/>
-      <c r="AP2" s="197"/>
-      <c r="AQ2" s="197"/>
-      <c r="AR2" s="197"/>
-      <c r="AS2" s="197"/>
-      <c r="AT2" s="197"/>
-      <c r="AU2" s="198"/>
+      <c r="AM2" s="186"/>
+      <c r="AN2" s="187"/>
+      <c r="AO2" s="187"/>
+      <c r="AP2" s="187"/>
+      <c r="AQ2" s="187"/>
+      <c r="AR2" s="187"/>
+      <c r="AS2" s="187"/>
+      <c r="AT2" s="187"/>
+      <c r="AU2" s="188"/>
       <c r="AV2" s="59"/>
-      <c r="AW2" s="196"/>
-      <c r="AX2" s="197"/>
-      <c r="AY2" s="197"/>
-      <c r="AZ2" s="197"/>
-      <c r="BA2" s="197"/>
-      <c r="BB2" s="197"/>
-      <c r="BC2" s="197"/>
-      <c r="BD2" s="197"/>
-      <c r="BE2" s="197"/>
-      <c r="BF2" s="197"/>
-      <c r="BG2" s="197"/>
-      <c r="BH2" s="198"/>
+      <c r="AW2" s="186"/>
+      <c r="AX2" s="187"/>
+      <c r="AY2" s="187"/>
+      <c r="AZ2" s="187"/>
+      <c r="BA2" s="187"/>
+      <c r="BB2" s="187"/>
+      <c r="BC2" s="187"/>
+      <c r="BD2" s="187"/>
+      <c r="BE2" s="187"/>
+      <c r="BF2" s="187"/>
+      <c r="BG2" s="187"/>
+      <c r="BH2" s="188"/>
       <c r="BI2" s="59"/>
-      <c r="BJ2" s="196"/>
-      <c r="BK2" s="197"/>
-      <c r="BL2" s="197"/>
-      <c r="BM2" s="197"/>
-      <c r="BN2" s="197"/>
-      <c r="BO2" s="197"/>
-      <c r="BP2" s="197"/>
-      <c r="BQ2" s="197"/>
-      <c r="BR2" s="198"/>
+      <c r="BJ2" s="186"/>
+      <c r="BK2" s="187"/>
+      <c r="BL2" s="187"/>
+      <c r="BM2" s="187"/>
+      <c r="BN2" s="187"/>
+      <c r="BO2" s="187"/>
+      <c r="BP2" s="187"/>
+      <c r="BQ2" s="187"/>
+      <c r="BR2" s="188"/>
       <c r="BS2" s="135"/>
     </row>
     <row r="3" spans="1:71" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="183"/>
+      <c r="B3" s="201"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="202" t="s">
+      <c r="D3" s="189" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="202" t="s">
+      <c r="E3" s="189" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="202" t="s">
+      <c r="F3" s="189" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="202" t="s">
+      <c r="G3" s="189" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="202" t="s">
+      <c r="H3" s="189" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="204" t="s">
+      <c r="I3" s="211" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="205"/>
-      <c r="K3" s="206"/>
-      <c r="L3" s="207"/>
-      <c r="M3" s="204" t="s">
+      <c r="J3" s="212"/>
+      <c r="K3" s="213"/>
+      <c r="L3" s="214"/>
+      <c r="M3" s="211" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="205"/>
-      <c r="O3" s="206"/>
-      <c r="P3" s="207"/>
+      <c r="N3" s="212"/>
+      <c r="O3" s="213"/>
+      <c r="P3" s="214"/>
       <c r="Q3" s="58"/>
-      <c r="R3" s="208" t="s">
+      <c r="R3" s="193" t="s">
         <v>13</v>
       </c>
-      <c r="S3" s="200"/>
-      <c r="T3" s="209"/>
-      <c r="U3" s="209"/>
-      <c r="V3" s="208" t="s">
+      <c r="S3" s="194"/>
+      <c r="T3" s="215"/>
+      <c r="U3" s="215"/>
+      <c r="V3" s="193" t="s">
         <v>14</v>
       </c>
-      <c r="W3" s="200"/>
-      <c r="X3" s="200"/>
-      <c r="Y3" s="200"/>
-      <c r="Z3" s="200"/>
-      <c r="AA3" s="201"/>
+      <c r="W3" s="194"/>
+      <c r="X3" s="194"/>
+      <c r="Y3" s="194"/>
+      <c r="Z3" s="194"/>
+      <c r="AA3" s="195"/>
       <c r="AB3" s="60"/>
-      <c r="AC3" s="210" t="s">
+      <c r="AC3" s="191" t="s">
         <v>15</v>
       </c>
-      <c r="AD3" s="212" t="s">
+      <c r="AD3" s="216" t="s">
         <v>9</v>
       </c>
-      <c r="AE3" s="208" t="s">
+      <c r="AE3" s="193" t="s">
         <v>13</v>
       </c>
-      <c r="AF3" s="200"/>
-      <c r="AG3" s="201"/>
-      <c r="AH3" s="208" t="s">
+      <c r="AF3" s="194"/>
+      <c r="AG3" s="195"/>
+      <c r="AH3" s="193" t="s">
         <v>14</v>
       </c>
-      <c r="AI3" s="200"/>
-      <c r="AJ3" s="200"/>
-      <c r="AK3" s="201"/>
+      <c r="AI3" s="194"/>
+      <c r="AJ3" s="194"/>
+      <c r="AK3" s="195"/>
       <c r="AL3" s="59"/>
-      <c r="AM3" s="213" t="s">
+      <c r="AM3" s="196" t="s">
         <v>15</v>
       </c>
-      <c r="AN3" s="210" t="s">
+      <c r="AN3" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="AO3" s="199" t="s">
+      <c r="AO3" s="200" t="s">
         <v>13</v>
       </c>
-      <c r="AP3" s="200"/>
-      <c r="AQ3" s="201"/>
-      <c r="AR3" s="208" t="s">
+      <c r="AP3" s="194"/>
+      <c r="AQ3" s="195"/>
+      <c r="AR3" s="193" t="s">
         <v>14</v>
       </c>
-      <c r="AS3" s="200"/>
-      <c r="AT3" s="200"/>
-      <c r="AU3" s="201"/>
+      <c r="AS3" s="194"/>
+      <c r="AT3" s="194"/>
+      <c r="AU3" s="195"/>
       <c r="AV3" s="59"/>
-      <c r="AW3" s="210" t="s">
+      <c r="AW3" s="191" t="s">
         <v>15</v>
       </c>
-      <c r="AX3" s="210" t="s">
+      <c r="AX3" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="AY3" s="199" t="s">
+      <c r="AY3" s="200" t="s">
         <v>13</v>
       </c>
-      <c r="AZ3" s="199"/>
-      <c r="BA3" s="200"/>
-      <c r="BB3" s="201"/>
-      <c r="BC3" s="208" t="s">
+      <c r="AZ3" s="200"/>
+      <c r="BA3" s="194"/>
+      <c r="BB3" s="195"/>
+      <c r="BC3" s="193" t="s">
         <v>14</v>
       </c>
-      <c r="BD3" s="199"/>
-      <c r="BE3" s="199"/>
-      <c r="BF3" s="200"/>
-      <c r="BG3" s="200"/>
-      <c r="BH3" s="201"/>
+      <c r="BD3" s="200"/>
+      <c r="BE3" s="200"/>
+      <c r="BF3" s="194"/>
+      <c r="BG3" s="194"/>
+      <c r="BH3" s="195"/>
       <c r="BI3" s="59"/>
-      <c r="BJ3" s="213" t="s">
+      <c r="BJ3" s="196" t="s">
         <v>16</v>
       </c>
-      <c r="BK3" s="210" t="s">
+      <c r="BK3" s="191" t="s">
         <v>17</v>
       </c>
-      <c r="BL3" s="214" t="s">
+      <c r="BL3" s="197" t="s">
         <v>18</v>
       </c>
-      <c r="BM3" s="215"/>
-      <c r="BN3" s="216"/>
-      <c r="BO3" s="199" t="s">
+      <c r="BM3" s="198"/>
+      <c r="BN3" s="199"/>
+      <c r="BO3" s="200" t="s">
         <v>14</v>
       </c>
-      <c r="BP3" s="200"/>
-      <c r="BQ3" s="200"/>
-      <c r="BR3" s="201"/>
+      <c r="BP3" s="194"/>
+      <c r="BQ3" s="194"/>
+      <c r="BR3" s="195"/>
       <c r="BS3" s="135"/>
     </row>
     <row r="4" spans="1:71" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="184"/>
+      <c r="B4" s="202"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="203"/>
-      <c r="E4" s="203"/>
-      <c r="F4" s="203"/>
-      <c r="G4" s="203"/>
-      <c r="H4" s="203"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
       <c r="I4" s="80" t="s">
         <v>3</v>
       </c>
@@ -7330,8 +7330,8 @@
         <v>24</v>
       </c>
       <c r="AB4" s="60"/>
-      <c r="AC4" s="211"/>
-      <c r="AD4" s="194"/>
+      <c r="AC4" s="192"/>
+      <c r="AD4" s="184"/>
       <c r="AE4" s="62" t="s">
         <v>27</v>
       </c>
@@ -7354,8 +7354,8 @@
         <v>24</v>
       </c>
       <c r="AL4" s="61"/>
-      <c r="AM4" s="193"/>
-      <c r="AN4" s="211"/>
+      <c r="AM4" s="183"/>
+      <c r="AN4" s="192"/>
       <c r="AO4" s="123" t="s">
         <v>27</v>
       </c>
@@ -7378,8 +7378,8 @@
         <v>24</v>
       </c>
       <c r="AV4" s="61"/>
-      <c r="AW4" s="211"/>
-      <c r="AX4" s="211"/>
+      <c r="AW4" s="192"/>
+      <c r="AX4" s="192"/>
       <c r="AY4" s="123" t="s">
         <v>27</v>
       </c>
@@ -7411,8 +7411,8 @@
         <v>24</v>
       </c>
       <c r="BI4" s="61"/>
-      <c r="BJ4" s="193"/>
-      <c r="BK4" s="211"/>
+      <c r="BJ4" s="183"/>
+      <c r="BK4" s="192"/>
       <c r="BL4" s="123" t="s">
         <v>32</v>
       </c>
@@ -12299,164 +12299,237 @@
       <c r="C26" s="164"/>
       <c r="D26" s="87">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E26" s="159" t="e">
+        <v>59890</v>
+      </c>
+      <c r="E26" s="159">
         <f t="shared" si="60"/>
-        <v>#DIV/0!</v>
+        <v>0.88151611287360165</v>
       </c>
       <c r="F26" s="87">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G26" s="159" t="e">
+        <v>52794</v>
+      </c>
+      <c r="G26" s="159">
         <f t="shared" si="61"/>
-        <v>#DIV/0!</v>
+        <v>0.1184838871263984</v>
       </c>
       <c r="H26" s="146">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="160" t="e">
+        <v>7096</v>
+      </c>
+      <c r="I26" s="160">
         <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J26" s="159" t="e">
+        <v>0.11656631156399568</v>
+      </c>
+      <c r="J26" s="159">
         <f t="shared" si="63"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K26" s="159" t="e">
+        <v>0.15748031496062992</v>
+      </c>
+      <c r="K26" s="159">
         <f t="shared" si="64"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L26" s="161" t="e">
+        <v>0.16701423519811406</v>
+      </c>
+      <c r="L26" s="161">
         <f t="shared" si="65"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M26" s="146" t="e">
+        <v>0.58375791261386445</v>
+      </c>
+      <c r="M26" s="146">
         <f t="shared" si="66"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N26" s="146" t="e">
+        <v>6858.7617724255051</v>
+      </c>
+      <c r="N26" s="146">
         <f t="shared" si="67"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O26" s="146" t="e">
+        <v>9266.1417322834641</v>
+      </c>
+      <c r="O26" s="146">
         <f t="shared" si="68"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P26" s="146" t="e">
+        <v>9827.1175990570318</v>
+      </c>
+      <c r="P26" s="146">
         <f t="shared" si="69"/>
-        <v>#DIV/0!</v>
+        <v>34348.315578199785</v>
       </c>
       <c r="Q26" s="56">
         <f t="shared" si="28"/>
         <v>46132</v>
       </c>
-      <c r="R26" s="139"/>
-      <c r="S26" s="140"/>
-      <c r="T26" s="140"/>
-      <c r="U26" s="140"/>
-      <c r="V26" s="141"/>
-      <c r="W26" s="142"/>
-      <c r="X26" s="141"/>
-      <c r="Y26" s="142"/>
-      <c r="Z26" s="141"/>
-      <c r="AA26" s="142"/>
+      <c r="R26" s="139">
+        <v>59890</v>
+      </c>
+      <c r="S26" s="140">
+        <v>0</v>
+      </c>
+      <c r="T26" s="140">
+        <v>58840</v>
+      </c>
+      <c r="U26" s="140">
+        <v>0</v>
+      </c>
+      <c r="V26" s="141">
+        <v>14570</v>
+      </c>
+      <c r="W26" s="142">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="X26" s="141">
+        <v>4720</v>
+      </c>
+      <c r="Y26" s="142">
+        <v>0.75</v>
+      </c>
+      <c r="Z26" s="141">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="142">
+        <v>0</v>
+      </c>
       <c r="AB26" s="56">
         <f t="shared" si="29"/>
         <v>46132</v>
       </c>
-      <c r="AC26" s="76" t="e">
+      <c r="AC26" s="76">
         <f t="shared" ref="AC26:AC36" si="70">+AF26/AE26</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD26" s="162" t="e">
+        <v>1</v>
+      </c>
+      <c r="AD26" s="162">
         <f t="shared" ref="AD26:AD36" si="71">+AG26/AE26</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE26" s="163"/>
+        <v>0</v>
+      </c>
+      <c r="AE26" s="163">
+        <v>7550</v>
+      </c>
       <c r="AF26" s="118">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG26" s="147"/>
-      <c r="AH26" s="148"/>
-      <c r="AI26" s="149"/>
-      <c r="AJ26" s="148"/>
-      <c r="AK26" s="165"/>
+        <v>7550</v>
+      </c>
+      <c r="AG26" s="147">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="148">
+        <v>3950</v>
+      </c>
+      <c r="AI26" s="149">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="AJ26" s="148">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="165">
+        <v>0</v>
+      </c>
       <c r="AL26" s="56">
         <f t="shared" si="18"/>
         <v>46132</v>
       </c>
-      <c r="AM26" s="77" t="e">
+      <c r="AM26" s="77">
         <f t="shared" ref="AM26:AM36" si="72">+AP26/AO26</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AN26" s="76" t="e">
+        <v>0.62009803921568629</v>
+      </c>
+      <c r="AN26" s="76">
         <f t="shared" ref="AN26:AN36" si="73">+AQ26/AO26</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AO26" s="150"/>
+        <v>0.37990196078431371</v>
+      </c>
+      <c r="AO26" s="150">
+        <v>10200</v>
+      </c>
       <c r="AP26" s="117">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AQ26" s="151"/>
-      <c r="AR26" s="152"/>
-      <c r="AS26" s="153"/>
-      <c r="AT26" s="152"/>
-      <c r="AU26" s="154"/>
+        <v>6325</v>
+      </c>
+      <c r="AQ26" s="151">
+        <v>3875</v>
+      </c>
+      <c r="AR26" s="152">
+        <v>4050</v>
+      </c>
+      <c r="AS26" s="153">
+        <v>0.375</v>
+      </c>
+      <c r="AT26" s="152">
+        <v>180</v>
+      </c>
+      <c r="AU26" s="154">
+        <v>0.875</v>
+      </c>
       <c r="AV26" s="56">
         <f t="shared" si="30"/>
         <v>46132</v>
       </c>
-      <c r="AW26" s="110" t="e">
+      <c r="AW26" s="110">
         <f t="shared" ref="AW26:AW36" si="74">BA26/AZ26</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AX26" s="110" t="e">
+        <v>0.65027144408251902</v>
+      </c>
+      <c r="AX26" s="110">
         <f t="shared" ref="AX26:AX36" si="75">BB26/AZ26</f>
-        <v>#DIV/0!</v>
+        <v>0.34972855591748098</v>
       </c>
       <c r="AY26" s="111">
         <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="AZ26" s="112"/>
+        <v>9210</v>
+      </c>
+      <c r="AZ26" s="112">
+        <v>9210</v>
+      </c>
       <c r="BA26" s="120">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="BB26" s="113"/>
-      <c r="BC26" s="112"/>
-      <c r="BD26" s="114"/>
-      <c r="BE26" s="115"/>
-      <c r="BF26" s="114"/>
-      <c r="BG26" s="115"/>
-      <c r="BH26" s="114"/>
+        <v>5989</v>
+      </c>
+      <c r="BB26" s="113">
+        <f>2650+571</f>
+        <v>3221</v>
+      </c>
+      <c r="BC26" s="112">
+        <v>4020</v>
+      </c>
+      <c r="BD26" s="114">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="BE26" s="115">
+        <v>0</v>
+      </c>
+      <c r="BF26" s="114">
+        <v>0</v>
+      </c>
+      <c r="BG26" s="115">
+        <v>152</v>
+      </c>
+      <c r="BH26" s="114">
+        <v>0.77083333333333337</v>
+      </c>
       <c r="BI26" s="56">
         <f t="shared" si="31"/>
         <v>46132</v>
       </c>
-      <c r="BJ26" s="78" t="e">
+      <c r="BJ26" s="78">
         <f t="shared" ref="BJ26:BJ36" si="76">+BM26/BL26</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BK26" s="76" t="e">
+        <v>0.60433747685797412</v>
+      </c>
+      <c r="BK26" s="76">
         <f t="shared" ref="BK26:BK36" si="77">+BN26/BL26</f>
-        <v>#DIV/0!</v>
+        <v>0.39566252314202593</v>
       </c>
       <c r="BL26" s="79">
         <f t="shared" ref="BL26:BL36" si="78">BM26+BN26</f>
-        <v>0</v>
-      </c>
-      <c r="BM26" s="155"/>
-      <c r="BN26" s="155"/>
-      <c r="BO26" s="156"/>
-      <c r="BP26" s="157"/>
-      <c r="BQ26" s="158"/>
-      <c r="BR26" s="157"/>
+        <v>37810</v>
+      </c>
+      <c r="BM26" s="155">
+        <v>22850</v>
+      </c>
+      <c r="BN26" s="155">
+        <v>14960</v>
+      </c>
+      <c r="BO26" s="156">
+        <v>4290</v>
+      </c>
+      <c r="BP26" s="157">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="BQ26" s="158">
+        <v>2870</v>
+      </c>
+      <c r="BR26" s="157">
+        <v>0.36458333333333331</v>
+      </c>
     </row>
     <row r="27" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="14"/>
@@ -12467,164 +12540,237 @@
       <c r="C27" s="164"/>
       <c r="D27" s="87">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E27" s="159" t="e">
+        <v>59920</v>
+      </c>
+      <c r="E27" s="159">
         <f t="shared" si="60"/>
-        <v>#DIV/0!</v>
+        <v>0.88249332443257678</v>
       </c>
       <c r="F27" s="87">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G27" s="159" t="e">
+        <v>52879</v>
+      </c>
+      <c r="G27" s="159">
         <f t="shared" si="61"/>
-        <v>#DIV/0!</v>
+        <v>0.11750667556742322</v>
       </c>
       <c r="H27" s="146">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I27" s="160" t="e">
+        <v>7041</v>
+      </c>
+      <c r="I27" s="160">
         <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J27" s="159" t="e">
+        <v>0.11707542804257288</v>
+      </c>
+      <c r="J27" s="159">
         <f t="shared" si="63"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K27" s="159" t="e">
+        <v>0.1574888169057535</v>
+      </c>
+      <c r="K27" s="159">
         <f t="shared" si="64"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L27" s="161" t="e">
+        <v>0.167420814479638</v>
+      </c>
+      <c r="L27" s="161">
         <f t="shared" si="65"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M27" s="146" t="e">
+        <v>0.58275489742403208</v>
+      </c>
+      <c r="M27" s="146">
         <f t="shared" si="66"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N27" s="146" t="e">
+        <v>6894.571957427117</v>
+      </c>
+      <c r="N27" s="146">
         <f t="shared" si="67"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O27" s="146" t="e">
+        <v>9274.5164275798234</v>
+      </c>
+      <c r="O27" s="146">
         <f t="shared" si="68"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P27" s="146" t="e">
+        <v>9859.4117647058811</v>
+      </c>
+      <c r="P27" s="146">
         <f t="shared" si="69"/>
-        <v>#DIV/0!</v>
+        <v>34318.435909301246</v>
       </c>
       <c r="Q27" s="56">
         <f t="shared" si="28"/>
         <v>46133</v>
       </c>
-      <c r="R27" s="139"/>
-      <c r="S27" s="140"/>
-      <c r="T27" s="140"/>
-      <c r="U27" s="140"/>
-      <c r="V27" s="141"/>
-      <c r="W27" s="142"/>
-      <c r="X27" s="141"/>
-      <c r="Y27" s="142"/>
-      <c r="Z27" s="141"/>
-      <c r="AA27" s="142"/>
+      <c r="R27" s="139">
+        <v>59920</v>
+      </c>
+      <c r="S27" s="140">
+        <v>0</v>
+      </c>
+      <c r="T27" s="140">
+        <v>58890</v>
+      </c>
+      <c r="U27" s="140">
+        <v>0</v>
+      </c>
+      <c r="V27" s="141">
+        <v>14420</v>
+      </c>
+      <c r="W27" s="142">
+        <v>0.75</v>
+      </c>
+      <c r="X27" s="141">
+        <v>4615</v>
+      </c>
+      <c r="Y27" s="142">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="Z27" s="141">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="142">
+        <v>0</v>
+      </c>
       <c r="AB27" s="56">
         <f t="shared" si="29"/>
         <v>46133</v>
       </c>
-      <c r="AC27" s="76" t="e">
+      <c r="AC27" s="76">
         <f t="shared" si="70"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD27" s="162" t="e">
+        <v>1</v>
+      </c>
+      <c r="AD27" s="162">
         <f t="shared" si="71"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE27" s="163"/>
+        <v>0</v>
+      </c>
+      <c r="AE27" s="163">
+        <v>7590</v>
+      </c>
       <c r="AF27" s="118">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG27" s="147"/>
-      <c r="AH27" s="148"/>
-      <c r="AI27" s="149"/>
-      <c r="AJ27" s="148"/>
-      <c r="AK27" s="165"/>
+        <v>7590</v>
+      </c>
+      <c r="AG27" s="147">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="148">
+        <v>3970</v>
+      </c>
+      <c r="AI27" s="149">
+        <v>0.375</v>
+      </c>
+      <c r="AJ27" s="148">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="165">
+        <v>0</v>
+      </c>
       <c r="AL27" s="56">
         <f t="shared" si="18"/>
         <v>46133</v>
       </c>
-      <c r="AM27" s="77" t="e">
+      <c r="AM27" s="77">
         <f t="shared" si="72"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AN27" s="76" t="e">
+        <v>0.61998041136141036</v>
+      </c>
+      <c r="AN27" s="76">
         <f t="shared" si="73"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AO27" s="150"/>
+        <v>0.38001958863858964</v>
+      </c>
+      <c r="AO27" s="150">
+        <v>10210</v>
+      </c>
       <c r="AP27" s="117">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AQ27" s="151"/>
-      <c r="AR27" s="152"/>
-      <c r="AS27" s="153"/>
-      <c r="AT27" s="152"/>
-      <c r="AU27" s="154"/>
+        <v>6330</v>
+      </c>
+      <c r="AQ27" s="151">
+        <v>3880</v>
+      </c>
+      <c r="AR27" s="152">
+        <v>4090</v>
+      </c>
+      <c r="AS27" s="153">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="AT27" s="152">
+        <v>181</v>
+      </c>
+      <c r="AU27" s="154">
+        <v>0.85416666666666663</v>
+      </c>
       <c r="AV27" s="56">
         <f t="shared" si="30"/>
         <v>46133</v>
       </c>
-      <c r="AW27" s="110" t="e">
+      <c r="AW27" s="110">
         <f t="shared" si="74"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AX27" s="110" t="e">
+        <v>0.6582702702702703</v>
+      </c>
+      <c r="AX27" s="110">
         <f t="shared" si="75"/>
-        <v>#DIV/0!</v>
+        <v>0.3417297297297297</v>
       </c>
       <c r="AY27" s="111">
         <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="AZ27" s="112"/>
+        <v>9250</v>
+      </c>
+      <c r="AZ27" s="112">
+        <v>9250</v>
+      </c>
       <c r="BA27" s="120">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="BB27" s="113"/>
-      <c r="BC27" s="112"/>
-      <c r="BD27" s="114"/>
-      <c r="BE27" s="115"/>
-      <c r="BF27" s="114"/>
-      <c r="BG27" s="115"/>
-      <c r="BH27" s="114"/>
+        <v>6089</v>
+      </c>
+      <c r="BB27" s="113">
+        <f>2590+571</f>
+        <v>3161</v>
+      </c>
+      <c r="BC27" s="112">
+        <v>4050</v>
+      </c>
+      <c r="BD27" s="114">
+        <v>0.75</v>
+      </c>
+      <c r="BE27" s="115">
+        <v>0</v>
+      </c>
+      <c r="BF27" s="114">
+        <v>0</v>
+      </c>
+      <c r="BG27" s="115">
+        <v>152</v>
+      </c>
+      <c r="BH27" s="114">
+        <v>0.70833333333333337</v>
+      </c>
       <c r="BI27" s="56">
         <f t="shared" si="31"/>
         <v>46133</v>
       </c>
-      <c r="BJ27" s="78" t="e">
+      <c r="BJ27" s="78">
         <f t="shared" si="76"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BK27" s="76" t="e">
+        <v>0.60428798305982001</v>
+      </c>
+      <c r="BK27" s="76">
         <f t="shared" si="77"/>
-        <v>#DIV/0!</v>
+        <v>0.39571201694017999</v>
       </c>
       <c r="BL27" s="79">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="BM27" s="155"/>
-      <c r="BN27" s="155"/>
-      <c r="BO27" s="156"/>
-      <c r="BP27" s="157"/>
-      <c r="BQ27" s="158"/>
-      <c r="BR27" s="157"/>
+        <v>37780</v>
+      </c>
+      <c r="BM27" s="155">
+        <v>22830</v>
+      </c>
+      <c r="BN27" s="155">
+        <v>14950</v>
+      </c>
+      <c r="BO27" s="156">
+        <v>4180</v>
+      </c>
+      <c r="BP27" s="157">
+        <v>0.75</v>
+      </c>
+      <c r="BQ27" s="158">
+        <v>2790</v>
+      </c>
+      <c r="BR27" s="157">
+        <v>0.39583333333333331</v>
+      </c>
     </row>
     <row r="28" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14"/>
@@ -12635,164 +12781,237 @@
       <c r="C28" s="164"/>
       <c r="D28" s="87">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E28" s="159" t="e">
+        <v>59434</v>
+      </c>
+      <c r="E28" s="159">
         <f t="shared" si="60"/>
-        <v>#DIV/0!</v>
+        <v>0.87710737961436214</v>
       </c>
       <c r="F28" s="87">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G28" s="159" t="e">
+        <v>52130</v>
+      </c>
+      <c r="G28" s="159">
         <f t="shared" si="61"/>
-        <v>#DIV/0!</v>
+        <v>0.12289262038563785</v>
       </c>
       <c r="H28" s="146">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I28" s="160" t="e">
+        <v>7304</v>
+      </c>
+      <c r="I28" s="160">
         <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J28" s="159" t="e">
+        <v>0.12376794840593819</v>
+      </c>
+      <c r="J28" s="159">
         <f t="shared" si="63"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K28" s="159" t="e">
+        <v>0.1614291798491117</v>
+      </c>
+      <c r="K28" s="159">
         <f t="shared" si="64"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L28" s="161" t="e">
+        <v>0.17342085402881866</v>
+      </c>
+      <c r="L28" s="161">
         <f t="shared" si="65"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M28" s="146" t="e">
+        <v>0.56450778778291555</v>
+      </c>
+      <c r="M28" s="146">
         <f t="shared" si="66"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N28" s="146" t="e">
+        <v>7165.916676807009</v>
+      </c>
+      <c r="N28" s="146">
         <f t="shared" si="67"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O28" s="146" t="e">
+        <v>9346.4266549038693</v>
+      </c>
+      <c r="O28" s="146">
         <f t="shared" si="68"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P28" s="146" t="e">
+        <v>10040.720606560542</v>
+      </c>
+      <c r="P28" s="146">
         <f t="shared" si="69"/>
-        <v>#DIV/0!</v>
+        <v>32683.871897055244</v>
       </c>
       <c r="Q28" s="56">
         <f t="shared" si="28"/>
         <v>46134</v>
       </c>
-      <c r="R28" s="139"/>
-      <c r="S28" s="140"/>
-      <c r="T28" s="140"/>
-      <c r="U28" s="140"/>
-      <c r="V28" s="141"/>
-      <c r="W28" s="142"/>
-      <c r="X28" s="141"/>
-      <c r="Y28" s="142"/>
-      <c r="Z28" s="141"/>
-      <c r="AA28" s="142"/>
+      <c r="R28" s="139">
+        <v>59434</v>
+      </c>
+      <c r="S28" s="140">
+        <v>0</v>
+      </c>
+      <c r="T28" s="140">
+        <v>57898</v>
+      </c>
+      <c r="U28" s="140">
+        <v>0</v>
+      </c>
+      <c r="V28" s="141">
+        <v>16015</v>
+      </c>
+      <c r="W28" s="142">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="X28" s="141">
+        <v>5130</v>
+      </c>
+      <c r="Y28" s="142">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="Z28" s="141">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="142">
+        <v>0</v>
+      </c>
       <c r="AB28" s="56">
         <f t="shared" si="29"/>
         <v>46134</v>
       </c>
-      <c r="AC28" s="76" t="e">
+      <c r="AC28" s="76">
         <f t="shared" si="70"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD28" s="162" t="e">
+        <v>1</v>
+      </c>
+      <c r="AD28" s="162">
         <f t="shared" si="71"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE28" s="163"/>
+        <v>0</v>
+      </c>
+      <c r="AE28" s="163">
+        <v>8137</v>
+      </c>
       <c r="AF28" s="118">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG28" s="147"/>
-      <c r="AH28" s="148"/>
-      <c r="AI28" s="149"/>
-      <c r="AJ28" s="148"/>
-      <c r="AK28" s="165"/>
+        <v>8137</v>
+      </c>
+      <c r="AG28" s="147">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="148">
+        <v>4418</v>
+      </c>
+      <c r="AI28" s="149">
+        <v>0.37638888888888888</v>
+      </c>
+      <c r="AJ28" s="148">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="165">
+        <v>0</v>
+      </c>
       <c r="AL28" s="56">
         <f t="shared" si="18"/>
         <v>46134</v>
       </c>
-      <c r="AM28" s="77" t="e">
+      <c r="AM28" s="77">
         <f t="shared" si="72"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AN28" s="76" t="e">
+        <v>0.626966927353246</v>
+      </c>
+      <c r="AN28" s="76">
         <f t="shared" si="73"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AO28" s="150"/>
+        <v>0.373033072646754</v>
+      </c>
+      <c r="AO28" s="150">
+        <v>10613</v>
+      </c>
       <c r="AP28" s="117">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AQ28" s="151"/>
-      <c r="AR28" s="152"/>
-      <c r="AS28" s="153"/>
-      <c r="AT28" s="152"/>
-      <c r="AU28" s="154"/>
+        <v>6654</v>
+      </c>
+      <c r="AQ28" s="151">
+        <v>3959</v>
+      </c>
+      <c r="AR28" s="152">
+        <v>3676</v>
+      </c>
+      <c r="AS28" s="153">
+        <v>0.72638888888888886</v>
+      </c>
+      <c r="AT28" s="152">
+        <v>181</v>
+      </c>
+      <c r="AU28" s="154">
+        <v>0.80208333333333337</v>
+      </c>
       <c r="AV28" s="56">
         <f t="shared" si="30"/>
         <v>46134</v>
       </c>
-      <c r="AW28" s="110" t="e">
+      <c r="AW28" s="110">
         <f t="shared" si="74"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AX28" s="110" t="e">
+        <v>0.66147151098066992</v>
+      </c>
+      <c r="AX28" s="110">
         <f t="shared" si="75"/>
-        <v>#DIV/0!</v>
+        <v>0.33852848901933003</v>
       </c>
       <c r="AY28" s="111">
         <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="AZ28" s="112"/>
+        <v>9881</v>
+      </c>
+      <c r="AZ28" s="112">
+        <v>9881</v>
+      </c>
       <c r="BA28" s="120">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="BB28" s="113"/>
-      <c r="BC28" s="112"/>
-      <c r="BD28" s="114"/>
-      <c r="BE28" s="115"/>
-      <c r="BF28" s="114"/>
-      <c r="BG28" s="115"/>
-      <c r="BH28" s="114"/>
+        <v>6536</v>
+      </c>
+      <c r="BB28" s="113">
+        <f>2774+571</f>
+        <v>3345</v>
+      </c>
+      <c r="BC28" s="112">
+        <v>3588</v>
+      </c>
+      <c r="BD28" s="114">
+        <v>0.75</v>
+      </c>
+      <c r="BE28" s="115">
+        <v>0</v>
+      </c>
+      <c r="BF28" s="114">
+        <v>0</v>
+      </c>
+      <c r="BG28" s="115">
+        <v>162</v>
+      </c>
+      <c r="BH28" s="114">
+        <v>0.82291666666666663</v>
+      </c>
       <c r="BI28" s="56">
         <f t="shared" si="31"/>
         <v>46134</v>
       </c>
-      <c r="BJ28" s="78" t="e">
+      <c r="BJ28" s="78">
         <f t="shared" si="76"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BK28" s="76" t="e">
+        <v>0.60420876781720689</v>
+      </c>
+      <c r="BK28" s="76">
         <f t="shared" si="77"/>
-        <v>#DIV/0!</v>
+        <v>0.39579123218279311</v>
       </c>
       <c r="BL28" s="79">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="BM28" s="155"/>
-      <c r="BN28" s="155"/>
-      <c r="BO28" s="156"/>
-      <c r="BP28" s="157"/>
-      <c r="BQ28" s="158"/>
-      <c r="BR28" s="157"/>
+        <v>37113</v>
+      </c>
+      <c r="BM28" s="155">
+        <v>22424</v>
+      </c>
+      <c r="BN28" s="155">
+        <v>14689</v>
+      </c>
+      <c r="BO28" s="156">
+        <v>4179</v>
+      </c>
+      <c r="BP28" s="157">
+        <v>0.71805555555555556</v>
+      </c>
+      <c r="BQ28" s="158">
+        <v>2777</v>
+      </c>
+      <c r="BR28" s="157">
+        <v>0.71805555555555556</v>
+      </c>
     </row>
     <row r="29" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="14"/>
@@ -12803,164 +13022,237 @@
       <c r="C29" s="164"/>
       <c r="D29" s="87">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E29" s="159" t="e">
+        <v>58976</v>
+      </c>
+      <c r="E29" s="159">
         <f t="shared" si="60"/>
-        <v>#DIV/0!</v>
+        <v>0.87693298969072164</v>
       </c>
       <c r="F29" s="87">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G29" s="159" t="e">
+        <v>51718</v>
+      </c>
+      <c r="G29" s="159">
         <f t="shared" si="61"/>
-        <v>#DIV/0!</v>
+        <v>0.12306701030927836</v>
       </c>
       <c r="H29" s="146">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I29" s="160" t="e">
+        <v>7258</v>
+      </c>
+      <c r="I29" s="160">
         <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J29" s="159" t="e">
+        <v>0.12176725789885177</v>
+      </c>
+      <c r="J29" s="159">
         <f t="shared" si="63"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K29" s="159" t="e">
+        <v>0.16056782817985313</v>
+      </c>
+      <c r="K29" s="159">
         <f t="shared" si="64"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L29" s="161" t="e">
+        <v>0.17536516010526501</v>
+      </c>
+      <c r="L29" s="161">
         <f t="shared" si="65"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M29" s="146" t="e">
+        <v>0.56545200901411907</v>
+      </c>
+      <c r="M29" s="146">
         <f t="shared" si="66"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N29" s="146" t="e">
+        <v>6975.5591359936225</v>
+      </c>
+      <c r="N29" s="146">
         <f t="shared" si="67"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O29" s="146" t="e">
+        <v>9198.2886051110654</v>
+      </c>
+      <c r="O29" s="146">
         <f t="shared" si="68"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P29" s="146" t="e">
+        <v>10045.968561790211</v>
+      </c>
+      <c r="P29" s="146">
         <f t="shared" si="69"/>
-        <v>#DIV/0!</v>
+        <v>32392.483788382826</v>
       </c>
       <c r="Q29" s="56">
         <f t="shared" si="28"/>
         <v>46135</v>
       </c>
-      <c r="R29" s="139"/>
-      <c r="S29" s="140"/>
-      <c r="T29" s="140"/>
-      <c r="U29" s="140"/>
-      <c r="V29" s="141"/>
-      <c r="W29" s="142"/>
-      <c r="X29" s="141"/>
-      <c r="Y29" s="142"/>
-      <c r="Z29" s="141"/>
-      <c r="AA29" s="142"/>
+      <c r="R29" s="139">
+        <v>58976</v>
+      </c>
+      <c r="S29" s="140">
+        <v>0</v>
+      </c>
+      <c r="T29" s="140">
+        <v>57286</v>
+      </c>
+      <c r="U29" s="140">
+        <v>0</v>
+      </c>
+      <c r="V29" s="141">
+        <v>15508</v>
+      </c>
+      <c r="W29" s="142">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="X29" s="141">
+        <v>5008</v>
+      </c>
+      <c r="Y29" s="142">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="Z29" s="141">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="142">
+        <v>0</v>
+      </c>
       <c r="AB29" s="56">
         <f t="shared" si="29"/>
         <v>46135</v>
       </c>
-      <c r="AC29" s="76" t="e">
+      <c r="AC29" s="76">
         <f t="shared" si="70"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD29" s="162" t="e">
+        <v>1</v>
+      </c>
+      <c r="AD29" s="162">
         <f t="shared" si="71"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE29" s="163"/>
+        <v>0</v>
+      </c>
+      <c r="AE29" s="163">
+        <v>7943</v>
+      </c>
       <c r="AF29" s="118">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG29" s="147"/>
-      <c r="AH29" s="148"/>
-      <c r="AI29" s="149"/>
-      <c r="AJ29" s="148"/>
-      <c r="AK29" s="165"/>
+        <v>7943</v>
+      </c>
+      <c r="AG29" s="147">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="148">
+        <v>4610</v>
+      </c>
+      <c r="AI29" s="149">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="AJ29" s="148">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="165">
+        <v>0</v>
+      </c>
       <c r="AL29" s="56">
         <f t="shared" si="18"/>
         <v>46135</v>
       </c>
-      <c r="AM29" s="77" t="e">
+      <c r="AM29" s="77">
         <f t="shared" si="72"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AN29" s="76" t="e">
+        <v>0.62640824899751768</v>
+      </c>
+      <c r="AN29" s="76">
         <f t="shared" si="73"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AO29" s="150"/>
+        <v>0.37359175100248232</v>
+      </c>
+      <c r="AO29" s="150">
+        <v>10474</v>
+      </c>
       <c r="AP29" s="117">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AQ29" s="151"/>
-      <c r="AR29" s="152"/>
-      <c r="AS29" s="153"/>
-      <c r="AT29" s="152"/>
-      <c r="AU29" s="154"/>
+        <v>6561</v>
+      </c>
+      <c r="AQ29" s="151">
+        <v>3913</v>
+      </c>
+      <c r="AR29" s="152">
+        <v>4551</v>
+      </c>
+      <c r="AS29" s="153">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="AT29" s="152">
+        <v>185</v>
+      </c>
+      <c r="AU29" s="154">
+        <v>0.79166666666666663</v>
+      </c>
       <c r="AV29" s="56">
         <f t="shared" si="30"/>
         <v>46135</v>
       </c>
-      <c r="AW29" s="110" t="e">
+      <c r="AW29" s="110">
         <f t="shared" si="74"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AX29" s="110" t="e">
+        <v>0.66310806727767146</v>
+      </c>
+      <c r="AX29" s="110">
         <f t="shared" si="75"/>
-        <v>#DIV/0!</v>
+        <v>0.33689193272232854</v>
       </c>
       <c r="AY29" s="111">
         <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="AZ29" s="112"/>
+        <v>9929</v>
+      </c>
+      <c r="AZ29" s="112">
+        <v>9929</v>
+      </c>
       <c r="BA29" s="120">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="BB29" s="113"/>
-      <c r="BC29" s="112"/>
-      <c r="BD29" s="114"/>
-      <c r="BE29" s="115"/>
-      <c r="BF29" s="114"/>
-      <c r="BG29" s="115"/>
-      <c r="BH29" s="114"/>
+        <v>6584</v>
+      </c>
+      <c r="BB29" s="113">
+        <f>2774+571</f>
+        <v>3345</v>
+      </c>
+      <c r="BC29" s="112">
+        <v>3956</v>
+      </c>
+      <c r="BD29" s="114">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="BE29" s="115">
+        <v>0</v>
+      </c>
+      <c r="BF29" s="114">
+        <v>0</v>
+      </c>
+      <c r="BG29" s="115">
+        <v>166</v>
+      </c>
+      <c r="BH29" s="114">
+        <v>0.82291666666666663</v>
+      </c>
       <c r="BI29" s="56">
         <f t="shared" si="31"/>
         <v>46135</v>
       </c>
-      <c r="BJ29" s="78" t="e">
+      <c r="BJ29" s="78">
         <f t="shared" si="76"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BK29" s="76" t="e">
+        <v>0.60341602277348516</v>
+      </c>
+      <c r="BK29" s="76">
         <f t="shared" si="77"/>
-        <v>#DIV/0!</v>
+        <v>0.39658397722651484</v>
       </c>
       <c r="BL29" s="79">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="BM29" s="155"/>
-      <c r="BN29" s="155"/>
-      <c r="BO29" s="156"/>
-      <c r="BP29" s="157"/>
-      <c r="BQ29" s="158"/>
-      <c r="BR29" s="157"/>
+        <v>36885</v>
+      </c>
+      <c r="BM29" s="155">
+        <v>22257</v>
+      </c>
+      <c r="BN29" s="155">
+        <v>14628</v>
+      </c>
+      <c r="BO29" s="156">
+        <v>4288</v>
+      </c>
+      <c r="BP29" s="157">
+        <v>0.84097222222222223</v>
+      </c>
+      <c r="BQ29" s="158">
+        <v>2902</v>
+      </c>
+      <c r="BR29" s="157">
+        <v>0.81597222222222221</v>
+      </c>
     </row>
     <row r="30" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="14"/>
@@ -12971,164 +13263,237 @@
       <c r="C30" s="164"/>
       <c r="D30" s="87">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E30" s="159" t="e">
+        <v>57738</v>
+      </c>
+      <c r="E30" s="159">
         <f t="shared" si="60"/>
-        <v>#DIV/0!</v>
+        <v>0.87670165229138519</v>
       </c>
       <c r="F30" s="87">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G30" s="159" t="e">
+        <v>50619</v>
+      </c>
+      <c r="G30" s="159">
         <f t="shared" si="61"/>
-        <v>#DIV/0!</v>
+        <v>0.12329834770861478</v>
       </c>
       <c r="H30" s="146">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I30" s="160" t="e">
+        <v>7119</v>
+      </c>
+      <c r="I30" s="160">
         <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J30" s="159" t="e">
+        <v>0.12293221904001753</v>
+      </c>
+      <c r="J30" s="159">
         <f t="shared" si="63"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K30" s="159" t="e">
+        <v>0.16032051583016418</v>
+      </c>
+      <c r="K30" s="159">
         <f t="shared" si="64"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L30" s="161" t="e">
+        <v>0.17252546451251063</v>
+      </c>
+      <c r="L30" s="161">
         <f t="shared" si="65"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M30" s="146" t="e">
+        <v>0.56750708170962638</v>
+      </c>
+      <c r="M30" s="146">
         <f t="shared" si="66"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N30" s="146" t="e">
+        <v>6907.6843200776248</v>
+      </c>
+      <c r="N30" s="146">
         <f t="shared" si="67"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O30" s="146" t="e">
+        <v>9008.5701050127554</v>
+      </c>
+      <c r="O30" s="146">
         <f t="shared" si="68"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P30" s="146" t="e">
+        <v>9694.3783764224845</v>
+      </c>
+      <c r="P30" s="146">
         <f t="shared" si="69"/>
-        <v>#DIV/0!</v>
+        <v>31888.790428345616</v>
       </c>
       <c r="Q30" s="56">
         <f t="shared" si="28"/>
         <v>46136</v>
       </c>
-      <c r="R30" s="139"/>
-      <c r="S30" s="140"/>
-      <c r="T30" s="140"/>
-      <c r="U30" s="140"/>
-      <c r="V30" s="141"/>
-      <c r="W30" s="142"/>
-      <c r="X30" s="141"/>
-      <c r="Y30" s="142"/>
-      <c r="Z30" s="141"/>
-      <c r="AA30" s="142"/>
+      <c r="R30" s="139">
+        <v>57738</v>
+      </c>
+      <c r="S30" s="140">
+        <v>0</v>
+      </c>
+      <c r="T30" s="140">
+        <v>56191</v>
+      </c>
+      <c r="U30" s="140">
+        <v>0</v>
+      </c>
+      <c r="V30" s="141">
+        <v>14723</v>
+      </c>
+      <c r="W30" s="142">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="X30" s="141">
+        <v>4836</v>
+      </c>
+      <c r="Y30" s="142">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="Z30" s="141">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="142">
+        <v>0</v>
+      </c>
       <c r="AB30" s="56">
         <f t="shared" si="29"/>
         <v>46136</v>
       </c>
-      <c r="AC30" s="76" t="e">
+      <c r="AC30" s="76">
         <f t="shared" si="70"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD30" s="162" t="e">
+        <v>1</v>
+      </c>
+      <c r="AD30" s="162">
         <f t="shared" si="71"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE30" s="163"/>
+        <v>0</v>
+      </c>
+      <c r="AE30" s="163">
+        <v>7855</v>
+      </c>
       <c r="AF30" s="118">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG30" s="147"/>
-      <c r="AH30" s="148"/>
-      <c r="AI30" s="149"/>
-      <c r="AJ30" s="148"/>
-      <c r="AK30" s="165"/>
+        <v>7855</v>
+      </c>
+      <c r="AG30" s="147">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="148">
+        <v>4038</v>
+      </c>
+      <c r="AI30" s="149">
+        <v>0.36805555555555558</v>
+      </c>
+      <c r="AJ30" s="148">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="165">
+        <v>0</v>
+      </c>
       <c r="AL30" s="56">
         <f t="shared" si="18"/>
         <v>46136</v>
       </c>
-      <c r="AM30" s="77" t="e">
+      <c r="AM30" s="77">
         <f t="shared" si="72"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AN30" s="76" t="e">
+        <v>0.62651308082780166</v>
+      </c>
+      <c r="AN30" s="76">
         <f t="shared" si="73"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AO30" s="150"/>
+        <v>0.37348691917219834</v>
+      </c>
+      <c r="AO30" s="150">
+        <v>10244</v>
+      </c>
       <c r="AP30" s="117">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AQ30" s="151"/>
-      <c r="AR30" s="152"/>
-      <c r="AS30" s="153"/>
-      <c r="AT30" s="152"/>
-      <c r="AU30" s="154"/>
+        <v>6418</v>
+      </c>
+      <c r="AQ30" s="151">
+        <v>3826</v>
+      </c>
+      <c r="AR30" s="152">
+        <v>4301</v>
+      </c>
+      <c r="AS30" s="153">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="AT30" s="152">
+        <v>189</v>
+      </c>
+      <c r="AU30" s="154">
+        <v>0.82291666666666663</v>
+      </c>
       <c r="AV30" s="56">
         <f t="shared" si="30"/>
         <v>46136</v>
       </c>
-      <c r="AW30" s="110" t="e">
+      <c r="AW30" s="110">
         <f t="shared" si="74"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AX30" s="110" t="e">
+        <v>0.65467701342281881</v>
+      </c>
+      <c r="AX30" s="110">
         <f t="shared" si="75"/>
-        <v>#DIV/0!</v>
+        <v>0.34532298657718119</v>
       </c>
       <c r="AY30" s="111">
         <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="AZ30" s="112"/>
+        <v>9536</v>
+      </c>
+      <c r="AZ30" s="112">
+        <v>9536</v>
+      </c>
       <c r="BA30" s="120">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="BB30" s="113"/>
-      <c r="BC30" s="112"/>
-      <c r="BD30" s="114"/>
-      <c r="BE30" s="115"/>
-      <c r="BF30" s="114"/>
-      <c r="BG30" s="115"/>
-      <c r="BH30" s="114"/>
+        <v>6243</v>
+      </c>
+      <c r="BB30" s="113">
+        <f>2722+571</f>
+        <v>3293</v>
+      </c>
+      <c r="BC30" s="112">
+        <v>4141</v>
+      </c>
+      <c r="BD30" s="114">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="BE30" s="115">
+        <v>0</v>
+      </c>
+      <c r="BF30" s="114">
+        <v>0</v>
+      </c>
+      <c r="BG30" s="115">
+        <v>159</v>
+      </c>
+      <c r="BH30" s="114">
+        <v>0.79166666666666663</v>
+      </c>
       <c r="BI30" s="56">
         <f t="shared" si="31"/>
         <v>46136</v>
       </c>
-      <c r="BJ30" s="78" t="e">
+      <c r="BJ30" s="78">
         <f t="shared" si="76"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BK30" s="76" t="e">
+        <v>0.604710164910926</v>
+      </c>
+      <c r="BK30" s="76">
         <f t="shared" si="77"/>
-        <v>#DIV/0!</v>
+        <v>0.39528983508907395</v>
       </c>
       <c r="BL30" s="79">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="BM30" s="155"/>
-      <c r="BN30" s="155"/>
-      <c r="BO30" s="156"/>
-      <c r="BP30" s="157"/>
-      <c r="BQ30" s="158"/>
-      <c r="BR30" s="157"/>
+        <v>36262</v>
+      </c>
+      <c r="BM30" s="155">
+        <v>21928</v>
+      </c>
+      <c r="BN30" s="155">
+        <v>14334</v>
+      </c>
+      <c r="BO30" s="156">
+        <v>4207</v>
+      </c>
+      <c r="BP30" s="157">
+        <v>0.71805555555555556</v>
+      </c>
+      <c r="BQ30" s="158">
+        <v>2890</v>
+      </c>
+      <c r="BR30" s="157">
+        <v>0.71805555555555556</v>
+      </c>
     </row>
     <row r="31" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="14"/>
@@ -13139,164 +13504,237 @@
       <c r="C31" s="164"/>
       <c r="D31" s="87">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E31" s="159" t="e">
+        <v>33136</v>
+      </c>
+      <c r="E31" s="159">
         <f t="shared" si="60"/>
-        <v>#DIV/0!</v>
+        <v>0.78944350555287301</v>
       </c>
       <c r="F31" s="87">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G31" s="159" t="e">
+        <v>26159</v>
+      </c>
+      <c r="G31" s="159">
         <f t="shared" si="61"/>
-        <v>#DIV/0!</v>
+        <v>0.21055649444712699</v>
       </c>
       <c r="H31" s="146">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I31" s="160" t="e">
+        <v>6977</v>
+      </c>
+      <c r="I31" s="160">
         <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J31" s="159" t="e">
+        <v>7.924125472162917E-2</v>
+      </c>
+      <c r="J31" s="159">
         <f t="shared" si="63"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K31" s="159" t="e">
+        <v>0.15976898231784092</v>
+      </c>
+      <c r="K31" s="159">
         <f t="shared" si="64"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L31" s="161" t="e">
+        <v>0.16996254943824157</v>
+      </c>
+      <c r="L31" s="161">
         <f t="shared" si="65"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M31" s="146" t="e">
+        <v>0.62807248042918928</v>
+      </c>
+      <c r="M31" s="146">
         <f t="shared" si="66"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N31" s="146" t="e">
+        <v>2494.4354573821647</v>
+      </c>
+      <c r="N31" s="146">
         <f t="shared" si="67"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O31" s="146" t="e">
+        <v>5029.3677943833145</v>
+      </c>
+      <c r="O31" s="146">
         <f t="shared" si="68"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P31" s="146" t="e">
+        <v>5350.2510937664065</v>
+      </c>
+      <c r="P31" s="146">
         <f t="shared" si="69"/>
-        <v>#DIV/0!</v>
+        <v>19771.09361143045</v>
       </c>
       <c r="Q31" s="56">
         <f t="shared" si="28"/>
         <v>46137</v>
       </c>
-      <c r="R31" s="139"/>
-      <c r="S31" s="140"/>
-      <c r="T31" s="140"/>
-      <c r="U31" s="140"/>
-      <c r="V31" s="141"/>
-      <c r="W31" s="142"/>
-      <c r="X31" s="141"/>
-      <c r="Y31" s="142"/>
-      <c r="Z31" s="141"/>
-      <c r="AA31" s="142"/>
+      <c r="R31" s="139">
+        <v>33136</v>
+      </c>
+      <c r="S31" s="140">
+        <v>0</v>
+      </c>
+      <c r="T31" s="140">
+        <v>31479</v>
+      </c>
+      <c r="U31" s="140">
+        <v>0</v>
+      </c>
+      <c r="V31" s="141">
+        <v>6429</v>
+      </c>
+      <c r="W31" s="142">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="X31" s="141">
+        <v>2038</v>
+      </c>
+      <c r="Y31" s="142">
+        <v>0.71875</v>
+      </c>
+      <c r="Z31" s="141">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="142">
+        <v>0</v>
+      </c>
       <c r="AB31" s="56">
         <f t="shared" si="29"/>
         <v>46137</v>
       </c>
-      <c r="AC31" s="76" t="e">
+      <c r="AC31" s="76">
         <f t="shared" si="70"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD31" s="162" t="e">
+        <v>1</v>
+      </c>
+      <c r="AD31" s="162">
         <f t="shared" si="71"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE31" s="163"/>
+        <v>0</v>
+      </c>
+      <c r="AE31" s="163">
+        <v>2895</v>
+      </c>
       <c r="AF31" s="118">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG31" s="147"/>
-      <c r="AH31" s="148"/>
-      <c r="AI31" s="149"/>
-      <c r="AJ31" s="148"/>
-      <c r="AK31" s="165"/>
+        <v>2895</v>
+      </c>
+      <c r="AG31" s="147">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="148">
+        <v>1770</v>
+      </c>
+      <c r="AI31" s="149">
+        <v>0.37916666666666665</v>
+      </c>
+      <c r="AJ31" s="148">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="165">
+        <v>0</v>
+      </c>
       <c r="AL31" s="56">
         <f t="shared" si="18"/>
         <v>46137</v>
       </c>
-      <c r="AM31" s="77" t="e">
+      <c r="AM31" s="77">
         <f t="shared" si="72"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AN31" s="76" t="e">
+        <v>0.35326366284050026</v>
+      </c>
+      <c r="AN31" s="76">
         <f t="shared" si="73"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AO31" s="150"/>
+        <v>0.64673633715949974</v>
+      </c>
+      <c r="AO31" s="150">
+        <v>5837</v>
+      </c>
       <c r="AP31" s="117">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AQ31" s="151"/>
-      <c r="AR31" s="152"/>
-      <c r="AS31" s="153"/>
-      <c r="AT31" s="152"/>
-      <c r="AU31" s="154"/>
+        <v>2062</v>
+      </c>
+      <c r="AQ31" s="151">
+        <v>3775</v>
+      </c>
+      <c r="AR31" s="152">
+        <v>1713</v>
+      </c>
+      <c r="AS31" s="153">
+        <v>0.62986111111111109</v>
+      </c>
+      <c r="AT31" s="152">
+        <v>182</v>
+      </c>
+      <c r="AU31" s="154">
+        <v>0.90625</v>
+      </c>
       <c r="AV31" s="56">
         <f t="shared" si="30"/>
         <v>46137</v>
       </c>
-      <c r="AW31" s="110" t="e">
+      <c r="AW31" s="110">
         <f t="shared" si="74"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AX31" s="110" t="e">
+        <v>0.34060955518945635</v>
+      </c>
+      <c r="AX31" s="110">
         <f t="shared" si="75"/>
-        <v>#DIV/0!</v>
+        <v>0.65939044481054365</v>
       </c>
       <c r="AY31" s="111">
         <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="AZ31" s="112"/>
+        <v>4856</v>
+      </c>
+      <c r="AZ31" s="112">
+        <v>4856</v>
+      </c>
       <c r="BA31" s="120">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="BB31" s="113"/>
-      <c r="BC31" s="112"/>
-      <c r="BD31" s="114"/>
-      <c r="BE31" s="115"/>
-      <c r="BF31" s="114"/>
-      <c r="BG31" s="115"/>
-      <c r="BH31" s="114"/>
+        <v>1654</v>
+      </c>
+      <c r="BB31" s="113">
+        <f>2631+571</f>
+        <v>3202</v>
+      </c>
+      <c r="BC31" s="112">
+        <v>1654</v>
+      </c>
+      <c r="BD31" s="114">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="BE31" s="115">
+        <v>0</v>
+      </c>
+      <c r="BF31" s="114">
+        <v>0</v>
+      </c>
+      <c r="BG31" s="115">
+        <v>157</v>
+      </c>
+      <c r="BH31" s="114">
+        <v>0.80208333333333337</v>
+      </c>
       <c r="BI31" s="56">
         <f t="shared" si="31"/>
         <v>46137</v>
       </c>
-      <c r="BJ31" s="78" t="e">
+      <c r="BJ31" s="78">
         <f t="shared" si="76"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BK31" s="76" t="e">
+        <v>0.60585723001830383</v>
+      </c>
+      <c r="BK31" s="76">
         <f t="shared" si="77"/>
-        <v>#DIV/0!</v>
+        <v>0.39414276998169617</v>
       </c>
       <c r="BL31" s="79">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="BM31" s="155"/>
-      <c r="BN31" s="155"/>
-      <c r="BO31" s="156"/>
-      <c r="BP31" s="157"/>
-      <c r="BQ31" s="158"/>
-      <c r="BR31" s="157"/>
+        <v>22946</v>
+      </c>
+      <c r="BM31" s="155">
+        <v>13902</v>
+      </c>
+      <c r="BN31" s="155">
+        <v>9044</v>
+      </c>
+      <c r="BO31" s="156">
+        <v>2706</v>
+      </c>
+      <c r="BP31" s="157">
+        <v>0.61388888888888893</v>
+      </c>
+      <c r="BQ31" s="158">
+        <v>1787</v>
+      </c>
+      <c r="BR31" s="157">
+        <v>0.61458333333333337</v>
+      </c>
     </row>
     <row r="32" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="14"/>
@@ -13307,164 +13745,237 @@
       <c r="C32" s="164"/>
       <c r="D32" s="87">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E32" s="159" t="e">
+        <v>28800</v>
+      </c>
+      <c r="E32" s="159">
         <f t="shared" si="60"/>
-        <v>#DIV/0!</v>
+        <v>0.7590972222222222</v>
       </c>
       <c r="F32" s="87">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G32" s="159" t="e">
+        <v>21862</v>
+      </c>
+      <c r="G32" s="159">
         <f t="shared" si="61"/>
-        <v>#DIV/0!</v>
+        <v>0.24090277777777777</v>
       </c>
       <c r="H32" s="146">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I32" s="160" t="e">
+        <v>6938</v>
+      </c>
+      <c r="I32" s="160">
         <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J32" s="159" t="e">
+        <v>6.557429106728907E-2</v>
+      </c>
+      <c r="J32" s="159">
         <f t="shared" si="63"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K32" s="159" t="e">
+        <v>0.16741291162554381</v>
+      </c>
+      <c r="K32" s="159">
         <f t="shared" si="64"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L32" s="161" t="e">
+        <v>0.18247372280615987</v>
+      </c>
+      <c r="L32" s="161">
         <f t="shared" si="65"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M32" s="146" t="e">
+        <v>0.62478168365564768</v>
+      </c>
+      <c r="M32" s="146">
         <f t="shared" si="66"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N32" s="146" t="e">
+        <v>1793.0634149439522</v>
+      </c>
+      <c r="N32" s="146">
         <f t="shared" si="67"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O32" s="146" t="e">
+        <v>4577.7386554888699</v>
+      </c>
+      <c r="O32" s="146">
         <f t="shared" si="68"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P32" s="146" t="e">
+        <v>4989.5614764116353</v>
+      </c>
+      <c r="P32" s="146">
         <f t="shared" si="69"/>
-        <v>#DIV/0!</v>
+        <v>17084.03035788003</v>
       </c>
       <c r="Q32" s="56">
         <f t="shared" si="28"/>
         <v>46138</v>
       </c>
-      <c r="R32" s="139"/>
-      <c r="S32" s="140"/>
-      <c r="T32" s="140"/>
-      <c r="U32" s="140"/>
-      <c r="V32" s="141"/>
-      <c r="W32" s="142"/>
-      <c r="X32" s="141"/>
-      <c r="Y32" s="142"/>
-      <c r="Z32" s="141"/>
-      <c r="AA32" s="142"/>
+      <c r="R32" s="139">
+        <v>28800</v>
+      </c>
+      <c r="S32" s="140">
+        <v>0</v>
+      </c>
+      <c r="T32" s="140">
+        <v>27344</v>
+      </c>
+      <c r="U32" s="140">
+        <v>0</v>
+      </c>
+      <c r="V32" s="141">
+        <v>6602</v>
+      </c>
+      <c r="W32" s="142">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="X32" s="141">
+        <v>1822</v>
+      </c>
+      <c r="Y32" s="142">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="Z32" s="141">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="142">
+        <v>0</v>
+      </c>
       <c r="AB32" s="168">
         <f t="shared" si="29"/>
         <v>46138</v>
       </c>
-      <c r="AC32" s="76" t="e">
+      <c r="AC32" s="76">
         <f t="shared" si="70"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD32" s="162" t="e">
+        <v>1</v>
+      </c>
+      <c r="AD32" s="162">
         <f t="shared" si="71"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE32" s="163"/>
+        <v>0</v>
+      </c>
+      <c r="AE32" s="163">
+        <v>2065</v>
+      </c>
       <c r="AF32" s="118">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG32" s="147"/>
-      <c r="AH32" s="148"/>
-      <c r="AI32" s="149"/>
-      <c r="AJ32" s="148"/>
-      <c r="AK32" s="165"/>
+        <v>2065</v>
+      </c>
+      <c r="AG32" s="147">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="148">
+        <v>1815</v>
+      </c>
+      <c r="AI32" s="149">
+        <v>0.92986111111111114</v>
+      </c>
+      <c r="AJ32" s="148">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="165">
+        <v>0</v>
+      </c>
       <c r="AL32" s="168">
         <f t="shared" si="18"/>
         <v>46138</v>
       </c>
-      <c r="AM32" s="77" t="e">
+      <c r="AM32" s="77">
         <f t="shared" si="72"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AN32" s="76" t="e">
+        <v>0.296092564491654</v>
+      </c>
+      <c r="AN32" s="76">
         <f t="shared" si="73"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AO32" s="150"/>
+        <v>0.703907435508346</v>
+      </c>
+      <c r="AO32" s="150">
+        <v>5272</v>
+      </c>
       <c r="AP32" s="117">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AQ32" s="151"/>
-      <c r="AR32" s="152"/>
-      <c r="AS32" s="153"/>
-      <c r="AT32" s="152"/>
-      <c r="AU32" s="154"/>
+        <v>1561</v>
+      </c>
+      <c r="AQ32" s="151">
+        <v>3711</v>
+      </c>
+      <c r="AR32" s="152">
+        <v>1915</v>
+      </c>
+      <c r="AS32" s="153">
+        <v>0.93611111111111112</v>
+      </c>
+      <c r="AT32" s="152">
+        <v>186</v>
+      </c>
+      <c r="AU32" s="154">
+        <v>0.89583333333333337</v>
+      </c>
       <c r="AV32" s="168">
         <f t="shared" si="30"/>
         <v>46138</v>
       </c>
-      <c r="AW32" s="169" t="e">
+      <c r="AW32" s="169">
         <f t="shared" si="74"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AX32" s="169" t="e">
+        <v>0.27952668006251397</v>
+      </c>
+      <c r="AX32" s="169">
         <f t="shared" si="75"/>
-        <v>#DIV/0!</v>
+        <v>0.72047331993748609</v>
       </c>
       <c r="AY32" s="111">
         <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="AZ32" s="112"/>
+        <v>4479</v>
+      </c>
+      <c r="AZ32" s="112">
+        <v>4479</v>
+      </c>
       <c r="BA32" s="120">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="BB32" s="113"/>
-      <c r="BC32" s="112"/>
-      <c r="BD32" s="114"/>
-      <c r="BE32" s="115"/>
-      <c r="BF32" s="114"/>
-      <c r="BG32" s="115"/>
-      <c r="BH32" s="114"/>
+        <v>1252</v>
+      </c>
+      <c r="BB32" s="113">
+        <f>2656+571</f>
+        <v>3227</v>
+      </c>
+      <c r="BC32" s="112">
+        <v>1966</v>
+      </c>
+      <c r="BD32" s="114">
+        <v>0.40625</v>
+      </c>
+      <c r="BE32" s="115">
+        <v>0</v>
+      </c>
+      <c r="BF32" s="114">
+        <v>0</v>
+      </c>
+      <c r="BG32" s="115">
+        <v>160</v>
+      </c>
+      <c r="BH32" s="114">
+        <v>0.84375</v>
+      </c>
       <c r="BI32" s="168">
         <f t="shared" si="31"/>
         <v>46138</v>
       </c>
-      <c r="BJ32" s="170" t="e">
+      <c r="BJ32" s="170">
         <f t="shared" si="76"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BK32" s="76" t="e">
+        <v>0.60797966963151207</v>
+      </c>
+      <c r="BK32" s="76">
         <f t="shared" si="77"/>
-        <v>#DIV/0!</v>
+        <v>0.39202033036848793</v>
       </c>
       <c r="BL32" s="79">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="BM32" s="155"/>
-      <c r="BN32" s="155"/>
-      <c r="BO32" s="156"/>
-      <c r="BP32" s="157"/>
-      <c r="BQ32" s="158"/>
-      <c r="BR32" s="157"/>
+        <v>19675</v>
+      </c>
+      <c r="BM32" s="155">
+        <v>11962</v>
+      </c>
+      <c r="BN32" s="155">
+        <v>7713</v>
+      </c>
+      <c r="BO32" s="156">
+        <v>2607</v>
+      </c>
+      <c r="BP32" s="157">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="BQ32" s="158">
+        <v>1725</v>
+      </c>
+      <c r="BR32" s="157">
+        <v>0.41666666666666669</v>
+      </c>
     </row>
     <row r="33" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="14"/>
@@ -13475,163 +13986,236 @@
       <c r="C33" s="164"/>
       <c r="D33" s="87">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E33" s="159" t="e">
+        <v>60080</v>
+      </c>
+      <c r="E33" s="159">
         <f t="shared" si="60"/>
-        <v>#DIV/0!</v>
+        <v>0.88062583222370172</v>
       </c>
       <c r="F33" s="87">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G33" s="159" t="e">
+        <v>52908</v>
+      </c>
+      <c r="G33" s="159">
         <f t="shared" si="61"/>
-        <v>#DIV/0!</v>
+        <v>0.11937416777629827</v>
       </c>
       <c r="H33" s="146">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I33" s="160" t="e">
+        <v>7172</v>
+      </c>
+      <c r="I33" s="160">
         <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J33" s="159" t="e">
+        <v>0.12470063465453239</v>
+      </c>
+      <c r="J33" s="159">
         <f t="shared" si="63"/>
-        <v>#DIV/0!</v>
+        <v>0.1627050652616453</v>
       </c>
       <c r="K33" s="159">
         <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="L33" s="161" t="e">
+        <v>0.19782019536352824</v>
+      </c>
+      <c r="L33" s="161">
         <f t="shared" si="65"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M33" s="146" t="e">
+        <v>0.56072626032810446</v>
+      </c>
+      <c r="M33" s="146">
         <f t="shared" si="66"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N33" s="146" t="e">
+        <v>7274.4115225721471</v>
+      </c>
+      <c r="N33" s="146">
         <f t="shared" si="67"/>
-        <v>#DIV/0!</v>
+        <v>9491.3999820380777</v>
       </c>
       <c r="O33" s="146">
         <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-      <c r="P33" s="146" t="e">
+        <v>11539.84109653142</v>
+      </c>
+      <c r="P33" s="146">
         <f t="shared" si="69"/>
-        <v>#DIV/0!</v>
+        <v>32709.966396239975</v>
       </c>
       <c r="Q33" s="56">
         <f t="shared" si="28"/>
         <v>46139</v>
       </c>
-      <c r="R33" s="139"/>
-      <c r="S33" s="140"/>
-      <c r="T33" s="140"/>
-      <c r="U33" s="140"/>
-      <c r="V33" s="141"/>
-      <c r="W33" s="142"/>
-      <c r="X33" s="141"/>
-      <c r="Y33" s="142"/>
-      <c r="Z33" s="141"/>
-      <c r="AA33" s="142"/>
+      <c r="R33" s="139">
+        <v>60080</v>
+      </c>
+      <c r="S33" s="140">
+        <v>0</v>
+      </c>
+      <c r="T33" s="140">
+        <v>58335</v>
+      </c>
+      <c r="U33" s="140">
+        <v>0</v>
+      </c>
+      <c r="V33" s="141">
+        <v>14411</v>
+      </c>
+      <c r="W33" s="142">
+        <v>0.40625</v>
+      </c>
+      <c r="X33" s="141">
+        <v>4920</v>
+      </c>
+      <c r="Y33" s="142">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="Z33" s="141">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="142">
+        <v>0</v>
+      </c>
       <c r="AB33" s="56">
         <f t="shared" si="29"/>
         <v>46139</v>
       </c>
-      <c r="AC33" s="76" t="e">
+      <c r="AC33" s="76">
         <f t="shared" si="70"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD33" s="162" t="e">
+        <v>1</v>
+      </c>
+      <c r="AD33" s="162">
         <f t="shared" si="71"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE33" s="163"/>
+        <v>0</v>
+      </c>
+      <c r="AE33" s="163">
+        <v>8331</v>
+      </c>
       <c r="AF33" s="118">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG33" s="147"/>
-      <c r="AH33" s="148"/>
-      <c r="AI33" s="149"/>
-      <c r="AJ33" s="148"/>
-      <c r="AK33" s="165"/>
+        <v>8331</v>
+      </c>
+      <c r="AG33" s="147">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="148">
+        <v>4641</v>
+      </c>
+      <c r="AI33" s="149">
+        <v>0.34444444444444444</v>
+      </c>
+      <c r="AJ33" s="148">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="165">
+        <v>0</v>
+      </c>
       <c r="AL33" s="168">
         <f t="shared" si="18"/>
         <v>46139</v>
       </c>
-      <c r="AM33" s="77" t="e">
+      <c r="AM33" s="77">
         <f t="shared" si="72"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AN33" s="76" t="e">
+        <v>0</v>
+      </c>
+      <c r="AN33" s="76">
         <f t="shared" si="73"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AO33" s="150"/>
+        <v>0.35409383624655016</v>
+      </c>
+      <c r="AO33" s="150">
+        <v>10870</v>
+      </c>
       <c r="AP33" s="117">
-        <v>3924</v>
-      </c>
-      <c r="AQ33" s="151"/>
-      <c r="AR33" s="152"/>
-      <c r="AS33" s="153"/>
-      <c r="AT33" s="152"/>
-      <c r="AU33" s="154"/>
+        <v>0</v>
+      </c>
+      <c r="AQ33" s="151">
+        <v>3849</v>
+      </c>
+      <c r="AR33" s="152">
+        <v>4134</v>
+      </c>
+      <c r="AS33" s="153">
+        <v>0.33611111111111114</v>
+      </c>
+      <c r="AT33" s="152">
+        <v>184</v>
+      </c>
+      <c r="AU33" s="154">
+        <v>0.77083333333333337</v>
+      </c>
       <c r="AV33" s="56">
         <f t="shared" si="30"/>
         <v>46139</v>
       </c>
-      <c r="AW33" s="169" t="e">
+      <c r="AW33" s="169">
         <f t="shared" si="74"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AX33" s="169" t="e">
+        <v>0.67248176621328604</v>
+      </c>
+      <c r="AX33" s="169">
         <f t="shared" si="75"/>
-        <v>#DIV/0!</v>
+        <v>0.32751823378671396</v>
       </c>
       <c r="AY33" s="111">
         <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="AZ33" s="112"/>
+        <v>10146</v>
+      </c>
+      <c r="AZ33" s="112">
+        <v>10146</v>
+      </c>
       <c r="BA33" s="120">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="BB33" s="113"/>
-      <c r="BC33" s="112"/>
-      <c r="BD33" s="114"/>
-      <c r="BE33" s="115"/>
-      <c r="BF33" s="114"/>
-      <c r="BG33" s="115"/>
-      <c r="BH33" s="114"/>
+        <v>6823</v>
+      </c>
+      <c r="BB33" s="113">
+        <f>2752+571</f>
+        <v>3323</v>
+      </c>
+      <c r="BC33" s="112">
+        <v>3929</v>
+      </c>
+      <c r="BD33" s="114">
+        <v>0.78125</v>
+      </c>
+      <c r="BE33" s="115">
+        <v>0</v>
+      </c>
+      <c r="BF33" s="114">
+        <v>0</v>
+      </c>
+      <c r="BG33" s="115">
+        <v>169</v>
+      </c>
+      <c r="BH33" s="114">
+        <v>0.78125</v>
+      </c>
       <c r="BI33" s="56">
         <f t="shared" si="31"/>
         <v>46139</v>
       </c>
-      <c r="BJ33" s="170" t="e">
+      <c r="BJ33" s="170">
         <f t="shared" si="76"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BK33" s="76" t="e">
+        <v>0.60505592482848825</v>
+      </c>
+      <c r="BK33" s="76">
         <f t="shared" si="77"/>
-        <v>#DIV/0!</v>
+        <v>0.3949440751715117</v>
       </c>
       <c r="BL33" s="79">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="BM33" s="155"/>
-      <c r="BN33" s="155"/>
-      <c r="BO33" s="156"/>
-      <c r="BP33" s="157"/>
-      <c r="BQ33" s="158"/>
-      <c r="BR33" s="157"/>
+        <v>37461</v>
+      </c>
+      <c r="BM33" s="155">
+        <v>22666</v>
+      </c>
+      <c r="BN33" s="155">
+        <v>14795</v>
+      </c>
+      <c r="BO33" s="156">
+        <v>4021</v>
+      </c>
+      <c r="BP33" s="157">
+        <v>0.77708333333333335</v>
+      </c>
+      <c r="BQ33" s="158">
+        <v>2710</v>
+      </c>
+      <c r="BR33" s="157">
+        <v>0.77708333333333335</v>
+      </c>
     </row>
     <row r="34" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="14"/>
@@ -13642,164 +14226,237 @@
       <c r="C34" s="164"/>
       <c r="D34" s="87">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E34" s="159" t="e">
+        <v>68388</v>
+      </c>
+      <c r="E34" s="159">
         <f t="shared" si="60"/>
-        <v>#DIV/0!</v>
+        <v>0.89328537170263789</v>
       </c>
       <c r="F34" s="87">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G34" s="159" t="e">
+        <v>61090</v>
+      </c>
+      <c r="G34" s="159">
         <f t="shared" si="61"/>
-        <v>#DIV/0!</v>
+        <v>0.10671462829736211</v>
       </c>
       <c r="H34" s="146">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I34" s="160" t="e">
+        <v>7298</v>
+      </c>
+      <c r="I34" s="160">
         <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J34" s="159" t="e">
+        <v>0.13357923857199314</v>
+      </c>
+      <c r="J34" s="159">
         <f t="shared" si="63"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K34" s="159" t="e">
+        <v>0.17506257410090897</v>
+      </c>
+      <c r="K34" s="159">
         <f t="shared" si="64"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L34" s="161" t="e">
+        <v>0.17029980888676541</v>
+      </c>
+      <c r="L34" s="161">
         <f t="shared" si="65"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M34" s="146" t="e">
+        <v>0.54110130417599789</v>
+      </c>
+      <c r="M34" s="146">
         <f t="shared" si="66"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N34" s="146" t="e">
+        <v>8941.79423000922</v>
+      </c>
+      <c r="N34" s="146">
         <f t="shared" si="67"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O34" s="146" t="e">
+        <v>11718.688710314847</v>
+      </c>
+      <c r="O34" s="146">
         <f t="shared" si="68"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P34" s="146" t="e">
+        <v>11399.869206880076</v>
+      </c>
+      <c r="P34" s="146">
         <f t="shared" si="69"/>
-        <v>#DIV/0!</v>
+        <v>36221.321301541298</v>
       </c>
       <c r="Q34" s="56">
         <f t="shared" si="28"/>
         <v>46140</v>
       </c>
-      <c r="R34" s="139"/>
-      <c r="S34" s="140"/>
-      <c r="T34" s="140"/>
-      <c r="U34" s="140"/>
-      <c r="V34" s="141"/>
-      <c r="W34" s="142"/>
-      <c r="X34" s="141"/>
-      <c r="Y34" s="142"/>
-      <c r="Z34" s="141"/>
-      <c r="AA34" s="142"/>
+      <c r="R34" s="139">
+        <v>68388</v>
+      </c>
+      <c r="S34" s="140">
+        <v>0</v>
+      </c>
+      <c r="T34" s="140">
+        <v>66940</v>
+      </c>
+      <c r="U34" s="140">
+        <v>0</v>
+      </c>
+      <c r="V34" s="141">
+        <v>14057</v>
+      </c>
+      <c r="W34" s="142">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="X34" s="141">
+        <v>5204</v>
+      </c>
+      <c r="Y34" s="142">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="Z34" s="141">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="142">
+        <v>0</v>
+      </c>
       <c r="AB34" s="56">
         <f t="shared" si="29"/>
         <v>46140</v>
       </c>
-      <c r="AC34" s="76" t="e">
+      <c r="AC34" s="76">
         <f t="shared" si="70"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD34" s="162" t="e">
+        <v>0.97435897435897434</v>
+      </c>
+      <c r="AD34" s="162">
         <f t="shared" si="71"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE34" s="163"/>
+        <v>2.564102564102564E-2</v>
+      </c>
+      <c r="AE34" s="163">
+        <v>10140</v>
+      </c>
       <c r="AF34" s="118">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG34" s="147"/>
-      <c r="AH34" s="148"/>
-      <c r="AI34" s="149"/>
-      <c r="AJ34" s="148"/>
-      <c r="AK34" s="165"/>
+        <v>9880</v>
+      </c>
+      <c r="AG34" s="147">
+        <v>260</v>
+      </c>
+      <c r="AH34" s="148">
+        <v>5596</v>
+      </c>
+      <c r="AI34" s="149">
+        <v>0.67986111111111114</v>
+      </c>
+      <c r="AJ34" s="148">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="165">
+        <v>0</v>
+      </c>
       <c r="AL34" s="56">
         <f t="shared" si="18"/>
         <v>46140</v>
       </c>
-      <c r="AM34" s="77" t="e">
+      <c r="AM34" s="77">
         <f t="shared" si="72"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AN34" s="76" t="e">
+        <v>0.72541199488298591</v>
+      </c>
+      <c r="AN34" s="76">
         <f t="shared" si="73"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AO34" s="150"/>
+        <v>0.27458800511701409</v>
+      </c>
+      <c r="AO34" s="150">
+        <v>13289</v>
+      </c>
       <c r="AP34" s="117">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AQ34" s="151"/>
-      <c r="AR34" s="152"/>
-      <c r="AS34" s="153"/>
-      <c r="AT34" s="152"/>
-      <c r="AU34" s="154"/>
+        <v>9640</v>
+      </c>
+      <c r="AQ34" s="151">
+        <v>3649</v>
+      </c>
+      <c r="AR34" s="152">
+        <v>4864</v>
+      </c>
+      <c r="AS34" s="153">
+        <v>0.33263888888888887</v>
+      </c>
+      <c r="AT34" s="152">
+        <v>181</v>
+      </c>
+      <c r="AU34" s="154">
+        <v>0.78125</v>
+      </c>
       <c r="AV34" s="56">
         <f t="shared" si="30"/>
         <v>46140</v>
       </c>
-      <c r="AW34" s="110" t="e">
+      <c r="AW34" s="110">
         <f t="shared" si="74"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AX34" s="110" t="e">
+        <v>0.70287567946694718</v>
+      </c>
+      <c r="AX34" s="110">
         <f t="shared" si="75"/>
-        <v>#DIV/0!</v>
+        <v>0.29712432053305277</v>
       </c>
       <c r="AY34" s="111">
         <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="AZ34" s="112"/>
+        <v>11406</v>
+      </c>
+      <c r="AZ34" s="112">
+        <v>11406</v>
+      </c>
       <c r="BA34" s="120">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="BB34" s="113"/>
-      <c r="BC34" s="112"/>
-      <c r="BD34" s="114"/>
-      <c r="BE34" s="115"/>
-      <c r="BF34" s="114"/>
-      <c r="BG34" s="115"/>
-      <c r="BH34" s="114"/>
+        <v>8017</v>
+      </c>
+      <c r="BB34" s="113">
+        <f>2818+571</f>
+        <v>3389</v>
+      </c>
+      <c r="BC34" s="112">
+        <v>4893</v>
+      </c>
+      <c r="BD34" s="114">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="BE34" s="115">
+        <v>0</v>
+      </c>
+      <c r="BF34" s="114">
+        <v>0</v>
+      </c>
+      <c r="BG34" s="115">
+        <v>165</v>
+      </c>
+      <c r="BH34" s="114">
+        <v>0.79166666666666663</v>
+      </c>
       <c r="BI34" s="56">
         <f t="shared" si="31"/>
         <v>46140</v>
       </c>
-      <c r="BJ34" s="78" t="e">
+      <c r="BJ34" s="78">
         <f t="shared" si="76"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BK34" s="76" t="e">
+        <v>0.59997565429093125</v>
+      </c>
+      <c r="BK34" s="76">
         <f t="shared" si="77"/>
-        <v>#DIV/0!</v>
+        <v>0.40002434570906875</v>
       </c>
       <c r="BL34" s="79">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="BM34" s="155"/>
-      <c r="BN34" s="155"/>
-      <c r="BO34" s="156"/>
-      <c r="BP34" s="157"/>
-      <c r="BQ34" s="158"/>
-      <c r="BR34" s="157"/>
+        <v>41075</v>
+      </c>
+      <c r="BM34" s="155">
+        <v>24644</v>
+      </c>
+      <c r="BN34" s="155">
+        <v>16431</v>
+      </c>
+      <c r="BO34" s="156">
+        <v>5498</v>
+      </c>
+      <c r="BP34" s="157">
+        <v>0.40138888888888891</v>
+      </c>
+      <c r="BQ34" s="158">
+        <v>3089</v>
+      </c>
+      <c r="BR34" s="157">
+        <v>0.40138888888888891</v>
+      </c>
     </row>
     <row r="35" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="14"/>
@@ -13810,164 +14467,237 @@
       <c r="C35" s="164"/>
       <c r="D35" s="87">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E35" s="159" t="e">
+        <v>60964</v>
+      </c>
+      <c r="E35" s="159">
         <f t="shared" si="60"/>
-        <v>#DIV/0!</v>
+        <v>0.87938783544386856</v>
       </c>
       <c r="F35" s="87">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G35" s="159" t="e">
+        <v>53611</v>
+      </c>
+      <c r="G35" s="159">
         <f t="shared" si="61"/>
-        <v>#DIV/0!</v>
+        <v>0.12061216455613148</v>
       </c>
       <c r="H35" s="146">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I35" s="160" t="e">
+        <v>7353</v>
+      </c>
+      <c r="I35" s="160">
         <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J35" s="159" t="e">
+        <v>0.11570333387494645</v>
+      </c>
+      <c r="J35" s="159">
         <f t="shared" si="63"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K35" s="159" t="e">
+        <v>0.15793438603228999</v>
+      </c>
+      <c r="K35" s="159">
         <f t="shared" si="64"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L35" s="161" t="e">
+        <v>0.16787903980047802</v>
+      </c>
+      <c r="L35" s="161">
         <f t="shared" si="65"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M35" s="146" t="e">
+        <v>0.58318438972510678</v>
+      </c>
+      <c r="M35" s="146">
         <f t="shared" si="66"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N35" s="146" t="e">
+        <v>6891.7533789273102</v>
+      </c>
+      <c r="N35" s="146">
         <f t="shared" si="67"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O35" s="146" t="e">
+        <v>9407.2037696273201</v>
+      </c>
+      <c r="O35" s="146">
         <f t="shared" si="68"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P35" s="146" t="e">
+        <v>9999.5471266756722</v>
+      </c>
+      <c r="P35" s="146">
         <f t="shared" si="69"/>
-        <v>#DIV/0!</v>
+        <v>34736.794989586262</v>
       </c>
       <c r="Q35" s="56">
         <f t="shared" si="28"/>
         <v>46141</v>
       </c>
-      <c r="R35" s="139"/>
-      <c r="S35" s="140"/>
-      <c r="T35" s="140"/>
-      <c r="U35" s="140"/>
-      <c r="V35" s="141"/>
-      <c r="W35" s="142"/>
-      <c r="X35" s="141"/>
-      <c r="Y35" s="142"/>
-      <c r="Z35" s="141"/>
-      <c r="AA35" s="142"/>
+      <c r="R35" s="139">
+        <v>60964</v>
+      </c>
+      <c r="S35" s="140">
+        <v>0</v>
+      </c>
+      <c r="T35" s="140">
+        <v>59564</v>
+      </c>
+      <c r="U35" s="140">
+        <v>0</v>
+      </c>
+      <c r="V35" s="141">
+        <v>14086</v>
+      </c>
+      <c r="W35" s="142">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="X35" s="141">
+        <v>4619</v>
+      </c>
+      <c r="Y35" s="142">
+        <v>0.40625</v>
+      </c>
+      <c r="Z35" s="141">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="142">
+        <v>0</v>
+      </c>
       <c r="AB35" s="56">
         <f t="shared" si="29"/>
         <v>46141</v>
       </c>
-      <c r="AC35" s="76" t="e">
+      <c r="AC35" s="76">
         <f t="shared" si="70"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD35" s="162" t="e">
+        <v>1</v>
+      </c>
+      <c r="AD35" s="162">
         <f t="shared" si="71"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE35" s="163"/>
+        <v>0</v>
+      </c>
+      <c r="AE35" s="163">
+        <v>7833</v>
+      </c>
       <c r="AF35" s="118">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG35" s="147"/>
-      <c r="AH35" s="148"/>
-      <c r="AI35" s="149"/>
-      <c r="AJ35" s="148"/>
-      <c r="AK35" s="165"/>
+        <v>7833</v>
+      </c>
+      <c r="AG35" s="147">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="148">
+        <v>4265</v>
+      </c>
+      <c r="AI35" s="149">
+        <v>0.33541666666666664</v>
+      </c>
+      <c r="AJ35" s="148">
+        <v>0</v>
+      </c>
+      <c r="AK35" s="165">
+        <v>0</v>
+      </c>
       <c r="AL35" s="56">
         <f t="shared" si="18"/>
         <v>46141</v>
       </c>
-      <c r="AM35" s="77" t="e">
+      <c r="AM35" s="77">
         <f t="shared" si="72"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AN35" s="76" t="e">
+        <v>0.63243546576879905</v>
+      </c>
+      <c r="AN35" s="76">
         <f t="shared" si="73"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AO35" s="150"/>
+        <v>0.36756453423120089</v>
+      </c>
+      <c r="AO35" s="150">
+        <v>10692</v>
+      </c>
       <c r="AP35" s="117">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AQ35" s="151"/>
-      <c r="AR35" s="152"/>
-      <c r="AS35" s="153"/>
-      <c r="AT35" s="152"/>
-      <c r="AU35" s="154"/>
+        <v>6762</v>
+      </c>
+      <c r="AQ35" s="151">
+        <v>3930</v>
+      </c>
+      <c r="AR35" s="152">
+        <v>3582</v>
+      </c>
+      <c r="AS35" s="153">
+        <v>0.7104166666666667</v>
+      </c>
+      <c r="AT35" s="152">
+        <v>183</v>
+      </c>
+      <c r="AU35" s="154">
+        <v>0.8125</v>
+      </c>
       <c r="AV35" s="56">
         <f>AV34+1</f>
         <v>46141</v>
       </c>
-      <c r="AW35" s="110" t="e">
+      <c r="AW35" s="110">
         <f t="shared" si="74"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AX35" s="110" t="e">
+        <v>0.64685855772206746</v>
+      </c>
+      <c r="AX35" s="110">
         <f t="shared" si="75"/>
-        <v>#DIV/0!</v>
+        <v>0.35314144227793254</v>
       </c>
       <c r="AY35" s="111">
         <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="AZ35" s="112"/>
+        <v>9693</v>
+      </c>
+      <c r="AZ35" s="112">
+        <v>9693</v>
+      </c>
       <c r="BA35" s="120">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="BB35" s="113"/>
-      <c r="BC35" s="112"/>
-      <c r="BD35" s="114"/>
-      <c r="BE35" s="115"/>
-      <c r="BF35" s="114"/>
-      <c r="BG35" s="115"/>
-      <c r="BH35" s="114"/>
+        <v>6270</v>
+      </c>
+      <c r="BB35" s="113">
+        <f>2852+571</f>
+        <v>3423</v>
+      </c>
+      <c r="BC35" s="112">
+        <v>4573</v>
+      </c>
+      <c r="BD35" s="114">
+        <v>0.75</v>
+      </c>
+      <c r="BE35" s="115">
+        <v>0</v>
+      </c>
+      <c r="BF35" s="114">
+        <v>0</v>
+      </c>
+      <c r="BG35" s="115">
+        <v>171</v>
+      </c>
+      <c r="BH35" s="114">
+        <v>0.8125</v>
+      </c>
       <c r="BI35" s="56">
         <f t="shared" si="31"/>
         <v>46141</v>
       </c>
-      <c r="BJ35" s="78" t="e">
+      <c r="BJ35" s="78">
         <f t="shared" si="76"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BK35" s="76" t="e">
+        <v>0.60173247891390791</v>
+      </c>
+      <c r="BK35" s="76">
         <f t="shared" si="77"/>
-        <v>#DIV/0!</v>
+        <v>0.39826752108609204</v>
       </c>
       <c r="BL35" s="79">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="BM35" s="155"/>
-      <c r="BN35" s="155"/>
-      <c r="BO35" s="156"/>
-      <c r="BP35" s="157"/>
-      <c r="BQ35" s="158"/>
-      <c r="BR35" s="157"/>
+        <v>39481</v>
+      </c>
+      <c r="BM35" s="155">
+        <v>23757</v>
+      </c>
+      <c r="BN35" s="155">
+        <v>15724</v>
+      </c>
+      <c r="BO35" s="156">
+        <v>4148</v>
+      </c>
+      <c r="BP35" s="157">
+        <v>0.7680555555555556</v>
+      </c>
+      <c r="BQ35" s="158">
+        <v>2796</v>
+      </c>
+      <c r="BR35" s="157">
+        <v>0.76875000000000004</v>
+      </c>
     </row>
     <row r="36" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="14"/>
@@ -13978,164 +14708,237 @@
       <c r="C36" s="164"/>
       <c r="D36" s="87">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E36" s="159" t="e">
+        <v>60370</v>
+      </c>
+      <c r="E36" s="159">
         <f t="shared" si="60"/>
-        <v>#DIV/0!</v>
+        <v>0.88056981944674506</v>
       </c>
       <c r="F36" s="87">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G36" s="159" t="e">
+        <v>53160</v>
+      </c>
+      <c r="G36" s="159">
         <f t="shared" si="61"/>
-        <v>#DIV/0!</v>
+        <v>0.11943018055325492</v>
       </c>
       <c r="H36" s="146">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I36" s="160" t="e">
+        <v>7210</v>
+      </c>
+      <c r="I36" s="160">
         <f t="shared" si="62"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J36" s="159" t="e">
+        <v>0.11370911826751443</v>
+      </c>
+      <c r="J36" s="159">
         <f t="shared" si="63"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K36" s="159" t="e">
+        <v>0.15458716273031703</v>
+      </c>
+      <c r="K36" s="159">
         <f t="shared" si="64"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L36" s="161" t="e">
+        <v>0.16171161967034464</v>
+      </c>
+      <c r="L36" s="161">
         <f t="shared" si="65"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M36" s="146" t="e">
+        <v>0.59160310974080577</v>
+      </c>
+      <c r="M36" s="146">
         <f>(S36+T36)*I36</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N36" s="146" t="e">
+        <v>6699.7412483219496</v>
+      </c>
+      <c r="N36" s="146">
         <f>(S36+T36)*J36</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O36" s="146" t="e">
+        <v>9108.2756280702797</v>
+      </c>
+      <c r="O36" s="146">
         <f>(S36+T36)*K36</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P36" s="146" t="e">
+        <v>9528.0486309767057</v>
+      </c>
+      <c r="P36" s="146">
         <f>(S36+T36)*L36</f>
-        <v>#DIV/0!</v>
+        <v>34857.255225928275</v>
       </c>
       <c r="Q36" s="56">
         <f t="shared" si="28"/>
         <v>46142</v>
       </c>
-      <c r="R36" s="139"/>
-      <c r="S36" s="140"/>
-      <c r="T36" s="140"/>
-      <c r="U36" s="140"/>
-      <c r="V36" s="141"/>
-      <c r="W36" s="142"/>
-      <c r="X36" s="141"/>
-      <c r="Y36" s="142"/>
-      <c r="Z36" s="141"/>
-      <c r="AA36" s="142"/>
+      <c r="R36" s="139">
+        <v>60370</v>
+      </c>
+      <c r="S36" s="140">
+        <v>0</v>
+      </c>
+      <c r="T36" s="140">
+        <v>58920</v>
+      </c>
+      <c r="U36" s="140">
+        <v>0</v>
+      </c>
+      <c r="V36" s="141">
+        <v>13899</v>
+      </c>
+      <c r="W36" s="142">
+        <v>0.84375</v>
+      </c>
+      <c r="X36" s="141">
+        <v>4597</v>
+      </c>
+      <c r="Y36" s="142">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="Z36" s="141">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="142">
+        <v>0</v>
+      </c>
       <c r="AB36" s="56">
         <f t="shared" si="29"/>
         <v>46142</v>
       </c>
-      <c r="AC36" s="76" t="e">
+      <c r="AC36" s="76">
         <f t="shared" si="70"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD36" s="162" t="e">
+        <v>1</v>
+      </c>
+      <c r="AD36" s="162">
         <f t="shared" si="71"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE36" s="163"/>
+        <v>0</v>
+      </c>
+      <c r="AE36" s="163">
+        <v>7708</v>
+      </c>
       <c r="AF36" s="118">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG36" s="147"/>
-      <c r="AH36" s="148"/>
-      <c r="AI36" s="149"/>
-      <c r="AJ36" s="148"/>
-      <c r="AK36" s="165"/>
+        <v>7708</v>
+      </c>
+      <c r="AG36" s="147">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="148">
+        <v>3530</v>
+      </c>
+      <c r="AI36" s="149">
+        <v>0.33888888888888891</v>
+      </c>
+      <c r="AJ36" s="148">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="165">
+        <v>0</v>
+      </c>
       <c r="AL36" s="56">
         <f t="shared" si="18"/>
         <v>46142</v>
       </c>
-      <c r="AM36" s="77" t="e">
+      <c r="AM36" s="77">
         <f t="shared" si="72"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AN36" s="76" t="e">
+        <v>0.62725450901803603</v>
+      </c>
+      <c r="AN36" s="76">
         <f t="shared" si="73"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AO36" s="150"/>
+        <v>0.37274549098196391</v>
+      </c>
+      <c r="AO36" s="150">
+        <v>10479</v>
+      </c>
       <c r="AP36" s="117">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AQ36" s="151"/>
-      <c r="AR36" s="152"/>
-      <c r="AS36" s="153"/>
-      <c r="AT36" s="152"/>
-      <c r="AU36" s="154"/>
+        <v>6573</v>
+      </c>
+      <c r="AQ36" s="151">
+        <v>3906</v>
+      </c>
+      <c r="AR36" s="152">
+        <v>3569</v>
+      </c>
+      <c r="AS36" s="153">
+        <v>0.76111111111111107</v>
+      </c>
+      <c r="AT36" s="152">
+        <v>183</v>
+      </c>
+      <c r="AU36" s="154">
+        <v>0.73958333333333337</v>
+      </c>
       <c r="AV36" s="56">
         <f t="shared" si="30"/>
         <v>46142</v>
       </c>
-      <c r="AW36" s="110" t="e">
+      <c r="AW36" s="110">
         <f t="shared" si="74"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AX36" s="110" t="e">
+        <v>0.65210066336737915</v>
+      </c>
+      <c r="AX36" s="110">
         <f t="shared" si="75"/>
-        <v>#DIV/0!</v>
+        <v>0.34789933663262085</v>
       </c>
       <c r="AY36" s="111">
         <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="AZ36" s="112"/>
+        <v>9497</v>
+      </c>
+      <c r="AZ36" s="112">
+        <v>9497</v>
+      </c>
       <c r="BA36" s="120">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="BB36" s="113"/>
-      <c r="BC36" s="112"/>
-      <c r="BD36" s="114"/>
-      <c r="BE36" s="115"/>
-      <c r="BF36" s="114"/>
-      <c r="BG36" s="115"/>
-      <c r="BH36" s="114"/>
+        <v>6193</v>
+      </c>
+      <c r="BB36" s="113">
+        <f>2733+571</f>
+        <v>3304</v>
+      </c>
+      <c r="BC36" s="112">
+        <v>4318</v>
+      </c>
+      <c r="BD36" s="114">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="BE36" s="115">
+        <v>0</v>
+      </c>
+      <c r="BF36" s="114">
+        <v>0</v>
+      </c>
+      <c r="BG36" s="115">
+        <v>157</v>
+      </c>
+      <c r="BH36" s="114">
+        <v>0.86458333333333337</v>
+      </c>
       <c r="BI36" s="56">
         <f t="shared" si="31"/>
         <v>46142</v>
       </c>
-      <c r="BJ36" s="78" t="e">
+      <c r="BJ36" s="78">
         <f t="shared" si="76"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="BK36" s="76" t="e">
+        <v>0.6346906715208338</v>
+      </c>
+      <c r="BK36" s="76">
         <f t="shared" si="77"/>
-        <v>#DIV/0!</v>
+        <v>0.36530932847916614</v>
       </c>
       <c r="BL36" s="79">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="BM36" s="155"/>
-      <c r="BN36" s="155"/>
-      <c r="BO36" s="156"/>
-      <c r="BP36" s="157"/>
-      <c r="BQ36" s="158"/>
-      <c r="BR36" s="157"/>
+        <v>40103</v>
+      </c>
+      <c r="BM36" s="155">
+        <v>25453</v>
+      </c>
+      <c r="BN36" s="155">
+        <v>14650</v>
+      </c>
+      <c r="BO36" s="156">
+        <v>4080</v>
+      </c>
+      <c r="BP36" s="157">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="BQ36" s="158">
+        <v>2707</v>
+      </c>
+      <c r="BR36" s="157">
+        <v>0.36527777777777776</v>
+      </c>
     </row>
     <row r="37" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="56">
@@ -14324,7 +15127,7 @@
     <row r="39" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="S39" s="176">
         <f>R36-T36</f>
-        <v>0</v>
+        <v>1450</v>
       </c>
       <c r="T39" s="176"/>
       <c r="U39" s="175"/>
@@ -14347,6 +15150,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="D1:P2"/>
+    <mergeCell ref="R1:AA2"/>
+    <mergeCell ref="AC1:AK2"/>
+    <mergeCell ref="AM1:AU2"/>
+    <mergeCell ref="AO3:AQ3"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="M3:P3"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:AA3"/>
+    <mergeCell ref="AC3:AC4"/>
+    <mergeCell ref="AD3:AD4"/>
+    <mergeCell ref="AE3:AG3"/>
+    <mergeCell ref="AH3:AK3"/>
+    <mergeCell ref="AM3:AM4"/>
     <mergeCell ref="BJ1:BR2"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
@@ -14363,22 +15182,6 @@
     <mergeCell ref="AX3:AX4"/>
     <mergeCell ref="AY3:BB3"/>
     <mergeCell ref="BC3:BH3"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="D1:P2"/>
-    <mergeCell ref="R1:AA2"/>
-    <mergeCell ref="AC1:AK2"/>
-    <mergeCell ref="AM1:AU2"/>
-    <mergeCell ref="AO3:AQ3"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="M3:P3"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:AA3"/>
-    <mergeCell ref="AC3:AC4"/>
-    <mergeCell ref="AD3:AD4"/>
-    <mergeCell ref="AE3:AG3"/>
-    <mergeCell ref="AH3:AK3"/>
-    <mergeCell ref="AM3:AM4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="88" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
@@ -16215,462 +17018,814 @@
         <f t="shared" si="6"/>
         <v>46132</v>
       </c>
-      <c r="D34" s="171"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="88"/>
+      <c r="D34" s="171">
+        <v>98</v>
+      </c>
+      <c r="E34" s="89">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="F34" s="88">
+        <v>1190</v>
+      </c>
       <c r="G34" s="93">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H34" s="88"/>
+        <v>661</v>
+      </c>
+      <c r="H34" s="88">
+        <v>529</v>
+      </c>
       <c r="I34" s="90">
         <f t="shared" si="1"/>
         <v>46132</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="88"/>
+      <c r="J34" s="91">
+        <v>30</v>
+      </c>
+      <c r="K34" s="89">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="L34" s="88">
+        <v>558</v>
+      </c>
       <c r="M34" s="90">
         <f t="shared" si="2"/>
         <v>46132</v>
       </c>
-      <c r="N34" s="91"/>
-      <c r="O34" s="89"/>
-      <c r="P34" s="91"/>
-      <c r="Q34" s="89"/>
+      <c r="N34" s="91">
+        <v>22</v>
+      </c>
+      <c r="O34" s="89">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="P34" s="91">
+        <v>11</v>
+      </c>
+      <c r="Q34" s="89">
+        <v>0.6875</v>
+      </c>
       <c r="R34" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S34" s="88"/>
-      <c r="T34" s="88"/>
+        <v>570</v>
+      </c>
+      <c r="S34" s="88">
+        <v>335</v>
+      </c>
+      <c r="T34" s="88">
+        <v>235</v>
+      </c>
       <c r="U34" s="90">
         <f t="shared" si="4"/>
         <v>46132</v>
       </c>
-      <c r="V34" s="91"/>
-      <c r="W34" s="89"/>
-      <c r="X34" s="88"/>
+      <c r="V34" s="91">
+        <v>30</v>
+      </c>
+      <c r="W34" s="89">
+        <v>0.5625</v>
+      </c>
+      <c r="X34" s="88">
+        <v>515</v>
+      </c>
     </row>
     <row r="35" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="90">
         <f t="shared" si="6"/>
         <v>46133</v>
       </c>
-      <c r="D35" s="171"/>
-      <c r="E35" s="89"/>
-      <c r="F35" s="88"/>
+      <c r="D35" s="171">
+        <v>99</v>
+      </c>
+      <c r="E35" s="89">
+        <v>0.4375</v>
+      </c>
+      <c r="F35" s="88">
+        <v>1200</v>
+      </c>
       <c r="G35" s="93">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H35" s="88"/>
+        <v>675</v>
+      </c>
+      <c r="H35" s="88">
+        <v>525</v>
+      </c>
       <c r="I35" s="90">
         <f t="shared" si="1"/>
         <v>46133</v>
       </c>
-      <c r="J35" s="91"/>
-      <c r="K35" s="89"/>
-      <c r="L35" s="88"/>
+      <c r="J35" s="91">
+        <v>30</v>
+      </c>
+      <c r="K35" s="89">
+        <v>0.75</v>
+      </c>
+      <c r="L35" s="88">
+        <v>558</v>
+      </c>
       <c r="M35" s="90">
         <f t="shared" si="2"/>
         <v>46133</v>
       </c>
-      <c r="N35" s="91"/>
-      <c r="O35" s="89"/>
-      <c r="P35" s="91"/>
-      <c r="Q35" s="89"/>
+      <c r="N35" s="91">
+        <v>24</v>
+      </c>
+      <c r="O35" s="89">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="P35" s="91">
+        <v>13</v>
+      </c>
+      <c r="Q35" s="89">
+        <v>0.72916666666666663</v>
+      </c>
       <c r="R35" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S35" s="88"/>
-      <c r="T35" s="88"/>
+        <v>576</v>
+      </c>
+      <c r="S35" s="88">
+        <v>338</v>
+      </c>
+      <c r="T35" s="88">
+        <v>238</v>
+      </c>
       <c r="U35" s="90">
         <f t="shared" si="4"/>
         <v>46133</v>
       </c>
-      <c r="V35" s="91"/>
-      <c r="W35" s="89"/>
-      <c r="X35" s="88"/>
+      <c r="V35" s="91">
+        <v>30</v>
+      </c>
+      <c r="W35" s="89">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="X35" s="88">
+        <v>520</v>
+      </c>
     </row>
     <row r="36" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="90">
         <f t="shared" si="6"/>
         <v>46134</v>
       </c>
-      <c r="D36" s="171"/>
-      <c r="E36" s="89"/>
-      <c r="F36" s="88"/>
+      <c r="D36" s="171">
+        <v>95</v>
+      </c>
+      <c r="E36" s="89">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="F36" s="88">
+        <v>1310</v>
+      </c>
       <c r="G36" s="93">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H36" s="88"/>
+        <v>781</v>
+      </c>
+      <c r="H36" s="88">
+        <v>529</v>
+      </c>
       <c r="I36" s="90">
         <f t="shared" si="1"/>
         <v>46134</v>
       </c>
-      <c r="J36" s="91"/>
-      <c r="K36" s="89"/>
-      <c r="L36" s="88"/>
+      <c r="J36" s="91">
+        <v>37</v>
+      </c>
+      <c r="K36" s="89">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="L36" s="88">
+        <v>593</v>
+      </c>
       <c r="M36" s="90">
         <f t="shared" si="2"/>
         <v>46134</v>
       </c>
-      <c r="N36" s="91"/>
-      <c r="O36" s="89"/>
-      <c r="P36" s="91"/>
-      <c r="Q36" s="89"/>
+      <c r="N36" s="91">
+        <v>23</v>
+      </c>
+      <c r="O36" s="89">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="P36" s="91">
+        <v>13.8</v>
+      </c>
+      <c r="Q36" s="89">
+        <v>0.63541666666666663</v>
+      </c>
       <c r="R36" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S36" s="88"/>
-      <c r="T36" s="88"/>
+        <v>580</v>
+      </c>
+      <c r="S36" s="88">
+        <v>347</v>
+      </c>
+      <c r="T36" s="88">
+        <v>233</v>
+      </c>
       <c r="U36" s="90">
         <f t="shared" si="4"/>
         <v>46134</v>
       </c>
-      <c r="V36" s="91"/>
-      <c r="W36" s="89"/>
-      <c r="X36" s="88"/>
+      <c r="V36" s="91">
+        <v>33</v>
+      </c>
+      <c r="W36" s="89">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="X36" s="88">
+        <v>596</v>
+      </c>
     </row>
     <row r="37" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="90">
         <f t="shared" si="6"/>
         <v>46135</v>
       </c>
-      <c r="D37" s="171"/>
-      <c r="E37" s="89"/>
-      <c r="F37" s="88"/>
+      <c r="D37" s="171">
+        <v>84</v>
+      </c>
+      <c r="E37" s="89">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="F37" s="88">
+        <v>1291</v>
+      </c>
       <c r="G37" s="93">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H37" s="88"/>
+        <v>784</v>
+      </c>
+      <c r="H37" s="88">
+        <v>507</v>
+      </c>
       <c r="I37" s="90">
         <f t="shared" si="1"/>
         <v>46135</v>
       </c>
-      <c r="J37" s="91"/>
-      <c r="K37" s="89"/>
-      <c r="L37" s="88"/>
+      <c r="J37" s="91">
+        <v>30</v>
+      </c>
+      <c r="K37" s="89">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="L37" s="88">
+        <v>581</v>
+      </c>
       <c r="M37" s="90">
         <f t="shared" si="2"/>
         <v>46135</v>
       </c>
-      <c r="N37" s="91"/>
-      <c r="O37" s="89"/>
-      <c r="P37" s="91"/>
-      <c r="Q37" s="89"/>
+      <c r="N37" s="91">
+        <v>24</v>
+      </c>
+      <c r="O37" s="89">
+        <v>0.46875</v>
+      </c>
+      <c r="P37" s="91">
+        <v>15</v>
+      </c>
+      <c r="Q37" s="89">
+        <v>0.72916666666666663</v>
+      </c>
       <c r="R37" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S37" s="88"/>
-      <c r="T37" s="88"/>
+        <v>596</v>
+      </c>
+      <c r="S37" s="88">
+        <v>360</v>
+      </c>
+      <c r="T37" s="88">
+        <v>236</v>
+      </c>
       <c r="U37" s="90">
         <f t="shared" si="4"/>
         <v>46135</v>
       </c>
-      <c r="V37" s="91"/>
-      <c r="W37" s="89"/>
-      <c r="X37" s="88"/>
+      <c r="V37" s="91">
+        <v>29</v>
+      </c>
+      <c r="W37" s="89">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="X37" s="88">
+        <v>513</v>
+      </c>
     </row>
     <row r="38" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="90">
         <f t="shared" si="6"/>
         <v>46136</v>
       </c>
-      <c r="D38" s="171"/>
-      <c r="E38" s="89"/>
-      <c r="F38" s="88"/>
+      <c r="D38" s="171">
+        <v>86</v>
+      </c>
+      <c r="E38" s="89">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F38" s="88">
+        <v>1136</v>
+      </c>
       <c r="G38" s="93">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H38" s="88"/>
+        <v>639</v>
+      </c>
+      <c r="H38" s="88">
+        <v>497</v>
+      </c>
       <c r="I38" s="90">
         <f t="shared" si="1"/>
         <v>46136</v>
       </c>
-      <c r="J38" s="91"/>
-      <c r="K38" s="89"/>
-      <c r="L38" s="88"/>
+      <c r="J38" s="91">
+        <v>32</v>
+      </c>
+      <c r="K38" s="89">
+        <v>0.11458333333333333</v>
+      </c>
+      <c r="L38" s="88">
+        <v>582</v>
+      </c>
       <c r="M38" s="90">
         <f t="shared" si="2"/>
         <v>46136</v>
       </c>
-      <c r="N38" s="91"/>
-      <c r="O38" s="89"/>
-      <c r="P38" s="91"/>
-      <c r="Q38" s="89"/>
+      <c r="N38" s="91">
+        <v>25</v>
+      </c>
+      <c r="O38" s="89">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="P38" s="91">
+        <v>14</v>
+      </c>
+      <c r="Q38" s="89">
+        <v>0.40625</v>
+      </c>
       <c r="R38" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S38" s="88"/>
-      <c r="T38" s="88"/>
+        <v>596</v>
+      </c>
+      <c r="S38" s="88">
+        <v>359</v>
+      </c>
+      <c r="T38" s="88">
+        <v>237</v>
+      </c>
       <c r="U38" s="90">
         <f t="shared" si="4"/>
         <v>46136</v>
       </c>
-      <c r="V38" s="91"/>
-      <c r="W38" s="89"/>
-      <c r="X38" s="88"/>
+      <c r="V38" s="91">
+        <v>30</v>
+      </c>
+      <c r="W38" s="89">
+        <v>0.75</v>
+      </c>
+      <c r="X38" s="88">
+        <v>494</v>
+      </c>
     </row>
     <row r="39" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="90">
         <f t="shared" si="6"/>
         <v>46137</v>
       </c>
-      <c r="D39" s="171"/>
-      <c r="E39" s="89"/>
-      <c r="F39" s="88"/>
+      <c r="D39" s="171">
+        <v>66</v>
+      </c>
+      <c r="E39" s="89">
+        <v>0.21875</v>
+      </c>
+      <c r="F39" s="88">
+        <v>816</v>
+      </c>
       <c r="G39" s="93">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H39" s="88"/>
+        <v>350</v>
+      </c>
+      <c r="H39" s="88">
+        <v>466</v>
+      </c>
       <c r="I39" s="90">
         <f t="shared" si="1"/>
         <v>46137</v>
       </c>
-      <c r="J39" s="91"/>
-      <c r="K39" s="89"/>
-      <c r="L39" s="88"/>
+      <c r="J39" s="91">
+        <v>34</v>
+      </c>
+      <c r="K39" s="89">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L39" s="88">
+        <v>574</v>
+      </c>
       <c r="M39" s="90">
         <f t="shared" si="2"/>
         <v>46137</v>
       </c>
-      <c r="N39" s="91"/>
-      <c r="O39" s="89"/>
-      <c r="P39" s="91"/>
-      <c r="Q39" s="89"/>
+      <c r="N39" s="91">
+        <v>29</v>
+      </c>
+      <c r="O39" s="89">
+        <v>0.5625</v>
+      </c>
+      <c r="P39" s="91">
+        <v>14</v>
+      </c>
+      <c r="Q39" s="89">
+        <v>0.3125</v>
+      </c>
       <c r="R39" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S39" s="88"/>
-      <c r="T39" s="88"/>
+        <v>583</v>
+      </c>
+      <c r="S39" s="88">
+        <v>356</v>
+      </c>
+      <c r="T39" s="88">
+        <v>227</v>
+      </c>
       <c r="U39" s="90">
         <f t="shared" si="4"/>
         <v>46137</v>
       </c>
-      <c r="V39" s="91"/>
-      <c r="W39" s="89"/>
-      <c r="X39" s="88"/>
+      <c r="V39" s="91">
+        <v>27</v>
+      </c>
+      <c r="W39" s="89">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="X39" s="88">
+        <v>516</v>
+      </c>
     </row>
     <row r="40" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="90">
         <f t="shared" si="6"/>
         <v>46138</v>
       </c>
-      <c r="D40" s="171"/>
-      <c r="E40" s="172"/>
-      <c r="F40" s="173"/>
+      <c r="D40" s="171">
+        <v>53</v>
+      </c>
+      <c r="E40" s="172">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="F40" s="173">
+        <v>866</v>
+      </c>
       <c r="G40" s="93">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H40" s="173"/>
+        <v>412</v>
+      </c>
+      <c r="H40" s="173">
+        <v>454</v>
+      </c>
       <c r="I40" s="174">
         <f t="shared" si="1"/>
         <v>46138</v>
       </c>
-      <c r="J40" s="171"/>
-      <c r="K40" s="172"/>
-      <c r="L40" s="173"/>
+      <c r="J40" s="171">
+        <v>39</v>
+      </c>
+      <c r="K40" s="172">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="L40" s="173">
+        <v>577</v>
+      </c>
       <c r="M40" s="174">
         <f t="shared" si="2"/>
         <v>46138</v>
       </c>
-      <c r="N40" s="171"/>
-      <c r="O40" s="172"/>
-      <c r="P40" s="171"/>
-      <c r="Q40" s="172"/>
+      <c r="N40" s="171">
+        <v>30</v>
+      </c>
+      <c r="O40" s="172">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="P40" s="171">
+        <v>11</v>
+      </c>
+      <c r="Q40" s="172">
+        <v>0.92708333333333337</v>
+      </c>
       <c r="R40" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S40" s="173"/>
-      <c r="T40" s="173"/>
+        <v>573</v>
+      </c>
+      <c r="S40" s="173">
+        <v>349</v>
+      </c>
+      <c r="T40" s="173">
+        <v>224</v>
+      </c>
       <c r="U40" s="174">
         <f t="shared" si="4"/>
         <v>46138</v>
       </c>
-      <c r="V40" s="171"/>
-      <c r="W40" s="172"/>
-      <c r="X40" s="173"/>
+      <c r="V40" s="171">
+        <v>28</v>
+      </c>
+      <c r="W40" s="172">
+        <v>0.90208333333333335</v>
+      </c>
+      <c r="X40" s="173">
+        <v>490</v>
+      </c>
     </row>
     <row r="41" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="90">
         <f t="shared" si="6"/>
         <v>46139</v>
       </c>
-      <c r="D41" s="171"/>
-      <c r="E41" s="89"/>
-      <c r="F41" s="88"/>
+      <c r="D41" s="171">
+        <v>111</v>
+      </c>
+      <c r="E41" s="89">
+        <v>0.4375</v>
+      </c>
+      <c r="F41" s="88">
+        <v>1212</v>
+      </c>
       <c r="G41" s="93">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H41" s="88"/>
+        <v>718</v>
+      </c>
+      <c r="H41" s="88">
+        <v>494</v>
+      </c>
       <c r="I41" s="90">
         <f t="shared" si="1"/>
         <v>46139</v>
       </c>
-      <c r="J41" s="91"/>
-      <c r="K41" s="89"/>
-      <c r="L41" s="88"/>
+      <c r="J41" s="91">
+        <v>33</v>
+      </c>
+      <c r="K41" s="89">
+        <v>0.17708333333333334</v>
+      </c>
+      <c r="L41" s="88">
+        <v>619</v>
+      </c>
       <c r="M41" s="90">
         <f t="shared" si="2"/>
         <v>46139</v>
       </c>
-      <c r="N41" s="91"/>
-      <c r="O41" s="89"/>
-      <c r="P41" s="91"/>
-      <c r="Q41" s="89"/>
+      <c r="N41" s="91">
+        <v>24</v>
+      </c>
+      <c r="O41" s="89">
+        <v>0.53125</v>
+      </c>
+      <c r="P41" s="91">
+        <v>15</v>
+      </c>
+      <c r="Q41" s="89">
+        <v>0.47916666666666669</v>
+      </c>
       <c r="R41" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S41" s="88"/>
-      <c r="T41" s="88"/>
+        <v>610</v>
+      </c>
+      <c r="S41" s="88">
+        <v>362</v>
+      </c>
+      <c r="T41" s="88">
+        <v>248</v>
+      </c>
       <c r="U41" s="90">
         <f t="shared" si="4"/>
         <v>46139</v>
       </c>
-      <c r="V41" s="91"/>
-      <c r="W41" s="89"/>
-      <c r="X41" s="88"/>
+      <c r="V41" s="91">
+        <v>28</v>
+      </c>
+      <c r="W41" s="89">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="X41" s="88">
+        <v>505</v>
+      </c>
     </row>
     <row r="42" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="90">
         <f t="shared" si="6"/>
         <v>46140</v>
       </c>
-      <c r="D42" s="171"/>
-      <c r="E42" s="89"/>
-      <c r="F42" s="88"/>
+      <c r="D42" s="171">
+        <v>98</v>
+      </c>
+      <c r="E42" s="89">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="F42" s="88">
+        <v>1209</v>
+      </c>
       <c r="G42" s="93">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H42" s="88"/>
+        <v>725</v>
+      </c>
+      <c r="H42" s="88">
+        <v>484</v>
+      </c>
       <c r="I42" s="90">
         <f t="shared" si="1"/>
         <v>46140</v>
       </c>
-      <c r="J42" s="91"/>
-      <c r="K42" s="89"/>
-      <c r="L42" s="88"/>
+      <c r="J42" s="91">
+        <v>34</v>
+      </c>
+      <c r="K42" s="89">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L42" s="88">
+        <v>625</v>
+      </c>
       <c r="M42" s="90">
         <f t="shared" si="2"/>
         <v>46140</v>
       </c>
-      <c r="N42" s="91"/>
-      <c r="O42" s="89"/>
-      <c r="P42" s="91"/>
-      <c r="Q42" s="89"/>
+      <c r="N42" s="91">
+        <v>25</v>
+      </c>
+      <c r="O42" s="89">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="P42" s="91">
+        <v>13</v>
+      </c>
+      <c r="Q42" s="89">
+        <v>0.33333333333333331</v>
+      </c>
       <c r="R42" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S42" s="88"/>
-      <c r="T42" s="88"/>
+        <v>565</v>
+      </c>
+      <c r="S42" s="88">
+        <v>343</v>
+      </c>
+      <c r="T42" s="88">
+        <v>222</v>
+      </c>
       <c r="U42" s="90">
         <f t="shared" si="4"/>
         <v>46140</v>
       </c>
-      <c r="V42" s="91"/>
-      <c r="W42" s="89"/>
-      <c r="X42" s="88"/>
+      <c r="V42" s="91">
+        <v>28</v>
+      </c>
+      <c r="W42" s="89">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="X42" s="88">
+        <v>549</v>
+      </c>
     </row>
     <row r="43" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="90">
         <f t="shared" si="6"/>
         <v>46141</v>
       </c>
-      <c r="D43" s="171"/>
-      <c r="E43" s="89"/>
-      <c r="F43" s="88"/>
+      <c r="D43" s="171">
+        <v>93</v>
+      </c>
+      <c r="E43" s="89">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F43" s="88">
+        <v>1251</v>
+      </c>
       <c r="G43" s="93">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H43" s="88"/>
+        <v>748</v>
+      </c>
+      <c r="H43" s="88">
+        <v>503</v>
+      </c>
       <c r="I43" s="90">
         <f t="shared" si="1"/>
         <v>46141</v>
       </c>
-      <c r="J43" s="91"/>
-      <c r="K43" s="89"/>
-      <c r="L43" s="88"/>
+      <c r="J43" s="91">
+        <v>32</v>
+      </c>
+      <c r="K43" s="89">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="L43" s="88">
+        <v>615</v>
+      </c>
       <c r="M43" s="174">
         <f t="shared" si="2"/>
         <v>46141</v>
       </c>
-      <c r="N43" s="91"/>
-      <c r="O43" s="89"/>
-      <c r="P43" s="91"/>
-      <c r="Q43" s="89"/>
+      <c r="N43" s="91">
+        <v>19</v>
+      </c>
+      <c r="O43" s="89">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="P43" s="91">
+        <v>14</v>
+      </c>
+      <c r="Q43" s="89">
+        <v>0.32291666666666669</v>
+      </c>
       <c r="R43" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S43" s="88"/>
-      <c r="T43" s="88"/>
+        <v>581</v>
+      </c>
+      <c r="S43" s="88">
+        <v>340</v>
+      </c>
+      <c r="T43" s="88">
+        <v>241</v>
+      </c>
       <c r="U43" s="90">
         <f t="shared" si="4"/>
         <v>46141</v>
       </c>
-      <c r="V43" s="91"/>
-      <c r="W43" s="89"/>
-      <c r="X43" s="88"/>
+      <c r="V43" s="91">
+        <v>29</v>
+      </c>
+      <c r="W43" s="89">
+        <v>0.21875</v>
+      </c>
+      <c r="X43" s="88">
+        <v>516</v>
+      </c>
     </row>
     <row r="44" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B44" s="90">
         <f t="shared" si="6"/>
         <v>46142</v>
       </c>
-      <c r="D44" s="171"/>
-      <c r="E44" s="172"/>
-      <c r="F44" s="173"/>
+      <c r="D44" s="171">
+        <v>105</v>
+      </c>
+      <c r="E44" s="172">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F44" s="173">
+        <v>1257</v>
+      </c>
       <c r="G44" s="93">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H44" s="173"/>
+        <v>756</v>
+      </c>
+      <c r="H44" s="173">
+        <v>501</v>
+      </c>
       <c r="I44" s="90">
         <f t="shared" si="1"/>
         <v>46142</v>
       </c>
-      <c r="J44" s="171"/>
-      <c r="K44" s="172"/>
-      <c r="L44" s="173"/>
+      <c r="J44" s="171">
+        <v>32</v>
+      </c>
+      <c r="K44" s="172">
+        <v>1.148611111111111</v>
+      </c>
+      <c r="L44" s="173">
+        <v>618</v>
+      </c>
       <c r="M44" s="90">
         <f t="shared" si="2"/>
         <v>46142</v>
       </c>
-      <c r="N44" s="171"/>
-      <c r="O44" s="172"/>
-      <c r="P44" s="171"/>
-      <c r="Q44" s="172"/>
+      <c r="N44" s="171">
+        <v>23</v>
+      </c>
+      <c r="O44" s="172">
+        <v>0.55208333333333337</v>
+      </c>
+      <c r="P44" s="171">
+        <v>14</v>
+      </c>
+      <c r="Q44" s="172">
+        <v>0.32291666666666669</v>
+      </c>
       <c r="R44" s="92">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S44" s="173"/>
-      <c r="T44" s="173"/>
+        <v>581</v>
+      </c>
+      <c r="S44" s="173">
+        <v>343</v>
+      </c>
+      <c r="T44" s="173">
+        <v>238</v>
+      </c>
       <c r="U44" s="90">
         <f t="shared" si="4"/>
         <v>46142</v>
       </c>
-      <c r="V44" s="171"/>
-      <c r="W44" s="172"/>
-      <c r="X44" s="173"/>
+      <c r="V44" s="171">
+        <v>30</v>
+      </c>
+      <c r="W44" s="172">
+        <v>0</v>
+      </c>
+      <c r="X44" s="173">
+        <v>554</v>
+      </c>
     </row>
     <row r="45" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B45" s="90">
@@ -17318,319 +18473,319 @@
       <c r="D68" s="180">
         <v>45858</v>
       </c>
-      <c r="E68" s="178" t="e">
+      <c r="E68" s="178">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F68" s="178" t="e">
+        <v>0.42004941757853864</v>
+      </c>
+      <c r="F68" s="178">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G68" s="178" t="e">
+        <v>0.19696434874691141</v>
+      </c>
+      <c r="G68" s="178">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H68" s="178" t="e">
+        <v>0.11824920578891635</v>
+      </c>
+      <c r="H68" s="178">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I68" s="178" t="e">
+        <v>8.2950935404165191E-2</v>
+      </c>
+      <c r="I68" s="178">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
+        <v>0.1817860924814684</v>
       </c>
       <c r="J68" s="179">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="69" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D69" s="180">
         <v>45859</v>
       </c>
-      <c r="E69" s="178" t="e">
+      <c r="E69" s="178">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F69" s="178" t="e">
+        <v>0.42046250875963559</v>
+      </c>
+      <c r="F69" s="178">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G69" s="178" t="e">
+        <v>0.19551506657323056</v>
+      </c>
+      <c r="G69" s="178">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H69" s="178" t="e">
+        <v>0.11843027330063069</v>
+      </c>
+      <c r="H69" s="178">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I69" s="178" t="e">
+        <v>8.339173090399439E-2</v>
+      </c>
+      <c r="I69" s="178">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
+        <v>0.18220042046250876</v>
       </c>
       <c r="J69" s="179">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="70" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D70" s="180">
         <v>45860</v>
       </c>
-      <c r="E70" s="178" t="e">
+      <c r="E70" s="178">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F70" s="178" t="e">
+        <v>0.42546281260149399</v>
+      </c>
+      <c r="F70" s="178">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G70" s="178" t="e">
+        <v>0.19259499837609614</v>
+      </c>
+      <c r="G70" s="178">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H70" s="178" t="e">
+        <v>0.11269892822344917</v>
+      </c>
+      <c r="H70" s="178">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I70" s="178" t="e">
+        <v>7.5673920103929843E-2</v>
+      </c>
+      <c r="I70" s="178">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
+        <v>0.19356934069503084</v>
       </c>
       <c r="J70" s="179">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3079</v>
       </c>
     </row>
     <row r="71" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D71" s="180">
         <v>45861</v>
       </c>
-      <c r="E71" s="178" t="e">
+      <c r="E71" s="178">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F71" s="178" t="e">
+        <v>0.43307614894330759</v>
+      </c>
+      <c r="F71" s="178">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G71" s="178" t="e">
+        <v>0.19490103991949009</v>
+      </c>
+      <c r="G71" s="178">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H71" s="178" t="e">
+        <v>0.12076484401207649</v>
+      </c>
+      <c r="H71" s="178">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I71" s="178" t="e">
+        <v>7.9168064407916808E-2</v>
+      </c>
+      <c r="I71" s="178">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
+        <v>0.172089902717209</v>
       </c>
       <c r="J71" s="179">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>2981</v>
       </c>
     </row>
     <row r="72" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D72" s="180">
         <v>45862</v>
       </c>
-      <c r="E72" s="178" t="e">
+      <c r="E72" s="178">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F72" s="178" t="e">
+        <v>0.40455840455840458</v>
+      </c>
+      <c r="F72" s="178">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G72" s="178" t="e">
+        <v>0.20726495726495728</v>
+      </c>
+      <c r="G72" s="178">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H72" s="178" t="e">
+        <v>0.12784900284900286</v>
+      </c>
+      <c r="H72" s="178">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I72" s="178" t="e">
+        <v>8.4401709401709407E-2</v>
+      </c>
+      <c r="I72" s="178">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
+        <v>0.17592592592592593</v>
       </c>
       <c r="J72" s="179">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="73" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D73" s="180">
         <v>45863</v>
       </c>
-      <c r="E73" s="178" t="e">
+      <c r="E73" s="178">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F73" s="178" t="e">
+        <v>0.32784250703093609</v>
+      </c>
+      <c r="F73" s="178">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G73" s="178" t="e">
+        <v>0.23061470470068302</v>
+      </c>
+      <c r="G73" s="178">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H73" s="178" t="e">
+        <v>0.14302932904781038</v>
+      </c>
+      <c r="H73" s="178">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I73" s="178" t="e">
+        <v>9.1201285656890313E-2</v>
+      </c>
+      <c r="I73" s="178">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
+        <v>0.2073121735636802</v>
       </c>
       <c r="J73" s="179">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="74" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D74" s="180">
         <v>45864</v>
       </c>
-      <c r="E74" s="178" t="e">
+      <c r="E74" s="178">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F74" s="178" t="e">
+        <v>0.34557063048683162</v>
+      </c>
+      <c r="F74" s="178">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G74" s="178" t="e">
+        <v>0.23024740622505985</v>
+      </c>
+      <c r="G74" s="178">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H74" s="178" t="e">
+        <v>0.13926576217079009</v>
+      </c>
+      <c r="H74" s="178">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I74" s="178" t="e">
+        <v>8.9385474860335198E-2</v>
+      </c>
+      <c r="I74" s="178">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
+        <v>0.19553072625698323</v>
       </c>
       <c r="J74" s="179">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="75" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D75" s="180">
         <v>45865</v>
       </c>
-      <c r="E75" s="178" t="e">
+      <c r="E75" s="178">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F75" s="178" t="e">
+        <v>0.41140529531568226</v>
+      </c>
+      <c r="F75" s="178">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G75" s="178" t="e">
+        <v>0.21011541072640869</v>
+      </c>
+      <c r="G75" s="178">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H75" s="178" t="e">
+        <v>0.12287847929395791</v>
+      </c>
+      <c r="H75" s="178">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I75" s="178" t="e">
+        <v>8.4181941615750169E-2</v>
+      </c>
+      <c r="I75" s="178">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
+        <v>0.17141887304820094</v>
       </c>
       <c r="J75" s="179">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>2946</v>
       </c>
     </row>
     <row r="76" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D76" s="180">
         <v>45866</v>
       </c>
-      <c r="E76" s="178" t="e">
+      <c r="E76" s="178">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F76" s="178" t="e">
+        <v>0.41010854816824965</v>
+      </c>
+      <c r="F76" s="178">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G76" s="178" t="e">
+        <v>0.21200814111261873</v>
+      </c>
+      <c r="G76" s="178">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H76" s="178" t="e">
+        <v>0.11635006784260515</v>
+      </c>
+      <c r="H76" s="178">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I76" s="178" t="e">
+        <v>7.5305291723202175E-2</v>
+      </c>
+      <c r="I76" s="178">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
+        <v>0.1862279511533243</v>
       </c>
       <c r="J76" s="179">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="77" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D77" s="180">
         <v>45867</v>
       </c>
-      <c r="E77" s="178" t="e">
+      <c r="E77" s="178">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F77" s="178" t="e">
+        <v>0.42220722240971986</v>
+      </c>
+      <c r="F77" s="178">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G77" s="178" t="e">
+        <v>0.20755990550118122</v>
+      </c>
+      <c r="G77" s="178">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H77" s="178" t="e">
+        <v>0.11474856564292946</v>
+      </c>
+      <c r="H77" s="178">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I77" s="178" t="e">
+        <v>8.1336483293958831E-2</v>
+      </c>
+      <c r="I77" s="178">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
+        <v>0.17414782315221058</v>
       </c>
       <c r="J77" s="179">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="78" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D78" s="180">
         <v>45868</v>
       </c>
-      <c r="E78" s="178" t="e">
+      <c r="E78" s="178">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F78" s="178" t="e">
+        <v>0.4176079734219269</v>
+      </c>
+      <c r="F78" s="178">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G78" s="178" t="e">
+        <v>0.20531561461794021</v>
+      </c>
+      <c r="G78" s="178">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H78" s="178" t="e">
+        <v>0.11395348837209303</v>
+      </c>
+      <c r="H78" s="178">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I78" s="178" t="e">
+        <v>7.9069767441860464E-2</v>
+      </c>
+      <c r="I78" s="178">
         <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
+        <v>0.1840531561461794</v>
       </c>
       <c r="J78" s="179">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3010</v>
       </c>
     </row>
     <row r="79" spans="4:10" x14ac:dyDescent="0.25">
@@ -18133,19 +19288,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -18154,7 +19296,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E3C748FF7EC2ED4E8EAD43CD1EEC2D0E" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ea203103aa5aa41fa7dd49b43cb8a2de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xmlns:ns3="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49b0a91519af75797ffa607b75695ffb" ns2:_="" ns3:_="">
     <xsd:import namespace="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
@@ -18401,27 +19543,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15BED2EB-1FBF-4966-A900-EAE40FD8F5E6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
-    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BA0308F-0D10-48A2-A977-8B1B3F2AD561}">
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E773259D-A732-42EE-8607-1A2C0CE89915}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2721F021-1C61-42E5-A242-FF96DB84E665}">
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{310932AF-9637-4741-9802-1C9734A4BEF3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -18437,4 +19581,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63CCCE7E-45E5-4704-BEA3-B42CAB7F9CAC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
+    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/seat/04-abril2026.xlsx
+++ b/data/seat/04-abril2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoefe.sharepoint.com/sites/GOFEFEVALPARASO/Documentos compartidos/UNIDAD DE GESTION/Datos Operacionales/Energía/SEAT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoefe-my.sharepoint.com/personal/mvara_efevalparaiso_cl/Documents/Datos/Energía/SEAT/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{466AE003-77E3-4875-813A-539BD3A3DB7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{193354A9-05D4-492B-A2F4-99529545814F}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{466AE003-77E3-4875-813A-539BD3A3DB7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D070A3C3-C862-4288-89BB-236EC18B398F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SEAT-SERs" sheetId="1" r:id="rId1"/>
@@ -2012,60 +2012,6 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2096,6 +2042,39 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2108,10 +2087,31 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3404,40 +3404,40 @@
                 <c:formatCode>#,##0\ "Kwh"</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>51026</c:v>
+                  <c:v>50899</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>54739</c:v>
+                  <c:v>54612</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>25057</c:v>
+                  <c:v>24930</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>23436</c:v>
+                  <c:v>23309</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>21088</c:v>
+                  <c:v>20961</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>49271.14</c:v>
+                  <c:v>49144.14</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>50700.85</c:v>
+                  <c:v>50573.85</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>51784</c:v>
+                  <c:v>51657</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>51129</c:v>
+                  <c:v>51002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>50019</c:v>
+                  <c:v>49892</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>29915</c:v>
+                  <c:v>29788</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>25441.98</c:v>
+                  <c:v>25314.98</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3694,40 +3694,40 @@
                 <c:formatCode>#,##0\ "Kwh"</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>7336</c:v>
+                  <c:v>7463</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7325</c:v>
+                  <c:v>7452</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7155</c:v>
+                  <c:v>7282</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7402</c:v>
+                  <c:v>7529</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6978</c:v>
+                  <c:v>7105</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7232.8600000000006</c:v>
+                  <c:v>7359.8600000000006</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7371.15</c:v>
+                  <c:v>7498.15</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7396</c:v>
+                  <c:v>7523</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>7351</c:v>
+                  <c:v>7478</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7183</c:v>
+                  <c:v>7310</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5937</c:v>
+                  <c:v>6064</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>6600.02</c:v>
+                  <c:v>6727.02</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6987,293 +6987,293 @@
       <c r="A1" s="127">
         <v>1.1111111E+55</v>
       </c>
-      <c r="B1" s="201" t="s">
+      <c r="B1" s="183" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="128"/>
-      <c r="D1" s="203" t="s">
+      <c r="D1" s="185" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="204"/>
-      <c r="F1" s="204"/>
-      <c r="G1" s="204"/>
-      <c r="H1" s="204"/>
-      <c r="I1" s="204"/>
-      <c r="J1" s="204"/>
-      <c r="K1" s="204"/>
-      <c r="L1" s="204"/>
-      <c r="M1" s="204"/>
-      <c r="N1" s="204"/>
-      <c r="O1" s="205"/>
-      <c r="P1" s="206"/>
+      <c r="E1" s="186"/>
+      <c r="F1" s="186"/>
+      <c r="G1" s="186"/>
+      <c r="H1" s="186"/>
+      <c r="I1" s="186"/>
+      <c r="J1" s="186"/>
+      <c r="K1" s="186"/>
+      <c r="L1" s="186"/>
+      <c r="M1" s="186"/>
+      <c r="N1" s="186"/>
+      <c r="O1" s="187"/>
+      <c r="P1" s="188"/>
       <c r="Q1" s="129"/>
-      <c r="R1" s="183" t="s">
+      <c r="R1" s="193" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="184"/>
-      <c r="T1" s="184"/>
-      <c r="U1" s="184"/>
-      <c r="V1" s="184"/>
-      <c r="W1" s="184"/>
-      <c r="X1" s="184"/>
-      <c r="Y1" s="184"/>
-      <c r="Z1" s="184"/>
-      <c r="AA1" s="185"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
+      <c r="V1" s="194"/>
+      <c r="W1" s="194"/>
+      <c r="X1" s="194"/>
+      <c r="Y1" s="194"/>
+      <c r="Z1" s="194"/>
+      <c r="AA1" s="195"/>
       <c r="AB1" s="130"/>
-      <c r="AC1" s="183" t="s">
+      <c r="AC1" s="193" t="s">
         <v>3</v>
       </c>
-      <c r="AD1" s="184"/>
-      <c r="AE1" s="184"/>
-      <c r="AF1" s="184"/>
-      <c r="AG1" s="184"/>
-      <c r="AH1" s="184"/>
-      <c r="AI1" s="184"/>
-      <c r="AJ1" s="184"/>
-      <c r="AK1" s="185"/>
+      <c r="AD1" s="194"/>
+      <c r="AE1" s="194"/>
+      <c r="AF1" s="194"/>
+      <c r="AG1" s="194"/>
+      <c r="AH1" s="194"/>
+      <c r="AI1" s="194"/>
+      <c r="AJ1" s="194"/>
+      <c r="AK1" s="195"/>
       <c r="AL1" s="131"/>
-      <c r="AM1" s="183" t="s">
+      <c r="AM1" s="193" t="s">
         <v>4</v>
       </c>
-      <c r="AN1" s="184"/>
-      <c r="AO1" s="184"/>
-      <c r="AP1" s="184"/>
-      <c r="AQ1" s="184"/>
-      <c r="AR1" s="184"/>
-      <c r="AS1" s="184"/>
-      <c r="AT1" s="184"/>
-      <c r="AU1" s="185"/>
+      <c r="AN1" s="194"/>
+      <c r="AO1" s="194"/>
+      <c r="AP1" s="194"/>
+      <c r="AQ1" s="194"/>
+      <c r="AR1" s="194"/>
+      <c r="AS1" s="194"/>
+      <c r="AT1" s="194"/>
+      <c r="AU1" s="195"/>
       <c r="AV1" s="131"/>
-      <c r="AW1" s="183" t="s">
+      <c r="AW1" s="193" t="s">
         <v>57</v>
       </c>
-      <c r="AX1" s="184"/>
-      <c r="AY1" s="184"/>
-      <c r="AZ1" s="184"/>
-      <c r="BA1" s="184"/>
-      <c r="BB1" s="184"/>
-      <c r="BC1" s="184"/>
-      <c r="BD1" s="184"/>
-      <c r="BE1" s="184"/>
-      <c r="BF1" s="184"/>
-      <c r="BG1" s="184"/>
-      <c r="BH1" s="185"/>
+      <c r="AX1" s="194"/>
+      <c r="AY1" s="194"/>
+      <c r="AZ1" s="194"/>
+      <c r="BA1" s="194"/>
+      <c r="BB1" s="194"/>
+      <c r="BC1" s="194"/>
+      <c r="BD1" s="194"/>
+      <c r="BE1" s="194"/>
+      <c r="BF1" s="194"/>
+      <c r="BG1" s="194"/>
+      <c r="BH1" s="195"/>
       <c r="BI1" s="131"/>
-      <c r="BJ1" s="183" t="s">
+      <c r="BJ1" s="193" t="s">
         <v>5</v>
       </c>
-      <c r="BK1" s="184"/>
-      <c r="BL1" s="184"/>
-      <c r="BM1" s="184"/>
-      <c r="BN1" s="184"/>
-      <c r="BO1" s="184"/>
-      <c r="BP1" s="184"/>
-      <c r="BQ1" s="184"/>
-      <c r="BR1" s="185"/>
+      <c r="BK1" s="194"/>
+      <c r="BL1" s="194"/>
+      <c r="BM1" s="194"/>
+      <c r="BN1" s="194"/>
+      <c r="BO1" s="194"/>
+      <c r="BP1" s="194"/>
+      <c r="BQ1" s="194"/>
+      <c r="BR1" s="195"/>
       <c r="BS1" s="132"/>
     </row>
     <row r="2" spans="1:71" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="201"/>
+      <c r="B2" s="183"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="207"/>
-      <c r="E2" s="208"/>
-      <c r="F2" s="208"/>
-      <c r="G2" s="208"/>
-      <c r="H2" s="208"/>
-      <c r="I2" s="208"/>
-      <c r="J2" s="208"/>
-      <c r="K2" s="208"/>
-      <c r="L2" s="208"/>
-      <c r="M2" s="208"/>
-      <c r="N2" s="208"/>
-      <c r="O2" s="209"/>
-      <c r="P2" s="210"/>
+      <c r="D2" s="189"/>
+      <c r="E2" s="190"/>
+      <c r="F2" s="190"/>
+      <c r="G2" s="190"/>
+      <c r="H2" s="190"/>
+      <c r="I2" s="190"/>
+      <c r="J2" s="190"/>
+      <c r="K2" s="190"/>
+      <c r="L2" s="190"/>
+      <c r="M2" s="190"/>
+      <c r="N2" s="190"/>
+      <c r="O2" s="191"/>
+      <c r="P2" s="192"/>
       <c r="Q2" s="58"/>
-      <c r="R2" s="186"/>
-      <c r="S2" s="187"/>
-      <c r="T2" s="187"/>
-      <c r="U2" s="187"/>
-      <c r="V2" s="187"/>
-      <c r="W2" s="187"/>
-      <c r="X2" s="187"/>
-      <c r="Y2" s="187"/>
-      <c r="Z2" s="187"/>
-      <c r="AA2" s="188"/>
+      <c r="R2" s="196"/>
+      <c r="S2" s="197"/>
+      <c r="T2" s="197"/>
+      <c r="U2" s="197"/>
+      <c r="V2" s="197"/>
+      <c r="W2" s="197"/>
+      <c r="X2" s="197"/>
+      <c r="Y2" s="197"/>
+      <c r="Z2" s="197"/>
+      <c r="AA2" s="198"/>
       <c r="AB2" s="60"/>
-      <c r="AC2" s="186"/>
-      <c r="AD2" s="187"/>
-      <c r="AE2" s="187"/>
-      <c r="AF2" s="187"/>
-      <c r="AG2" s="187"/>
-      <c r="AH2" s="187"/>
-      <c r="AI2" s="187"/>
-      <c r="AJ2" s="187"/>
-      <c r="AK2" s="188"/>
+      <c r="AC2" s="196"/>
+      <c r="AD2" s="197"/>
+      <c r="AE2" s="197"/>
+      <c r="AF2" s="197"/>
+      <c r="AG2" s="197"/>
+      <c r="AH2" s="197"/>
+      <c r="AI2" s="197"/>
+      <c r="AJ2" s="197"/>
+      <c r="AK2" s="198"/>
       <c r="AL2" s="59"/>
-      <c r="AM2" s="186"/>
-      <c r="AN2" s="187"/>
-      <c r="AO2" s="187"/>
-      <c r="AP2" s="187"/>
-      <c r="AQ2" s="187"/>
-      <c r="AR2" s="187"/>
-      <c r="AS2" s="187"/>
-      <c r="AT2" s="187"/>
-      <c r="AU2" s="188"/>
+      <c r="AM2" s="196"/>
+      <c r="AN2" s="197"/>
+      <c r="AO2" s="197"/>
+      <c r="AP2" s="197"/>
+      <c r="AQ2" s="197"/>
+      <c r="AR2" s="197"/>
+      <c r="AS2" s="197"/>
+      <c r="AT2" s="197"/>
+      <c r="AU2" s="198"/>
       <c r="AV2" s="59"/>
-      <c r="AW2" s="186"/>
-      <c r="AX2" s="187"/>
-      <c r="AY2" s="187"/>
-      <c r="AZ2" s="187"/>
-      <c r="BA2" s="187"/>
-      <c r="BB2" s="187"/>
-      <c r="BC2" s="187"/>
-      <c r="BD2" s="187"/>
-      <c r="BE2" s="187"/>
-      <c r="BF2" s="187"/>
-      <c r="BG2" s="187"/>
-      <c r="BH2" s="188"/>
+      <c r="AW2" s="196"/>
+      <c r="AX2" s="197"/>
+      <c r="AY2" s="197"/>
+      <c r="AZ2" s="197"/>
+      <c r="BA2" s="197"/>
+      <c r="BB2" s="197"/>
+      <c r="BC2" s="197"/>
+      <c r="BD2" s="197"/>
+      <c r="BE2" s="197"/>
+      <c r="BF2" s="197"/>
+      <c r="BG2" s="197"/>
+      <c r="BH2" s="198"/>
       <c r="BI2" s="59"/>
-      <c r="BJ2" s="186"/>
-      <c r="BK2" s="187"/>
-      <c r="BL2" s="187"/>
-      <c r="BM2" s="187"/>
-      <c r="BN2" s="187"/>
-      <c r="BO2" s="187"/>
-      <c r="BP2" s="187"/>
-      <c r="BQ2" s="187"/>
-      <c r="BR2" s="188"/>
+      <c r="BJ2" s="196"/>
+      <c r="BK2" s="197"/>
+      <c r="BL2" s="197"/>
+      <c r="BM2" s="197"/>
+      <c r="BN2" s="197"/>
+      <c r="BO2" s="197"/>
+      <c r="BP2" s="197"/>
+      <c r="BQ2" s="197"/>
+      <c r="BR2" s="198"/>
       <c r="BS2" s="135"/>
     </row>
     <row r="3" spans="1:71" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="201"/>
+      <c r="B3" s="183"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="189" t="s">
+      <c r="D3" s="202" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="189" t="s">
+      <c r="E3" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="189" t="s">
+      <c r="F3" s="202" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="189" t="s">
+      <c r="G3" s="202" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="189" t="s">
+      <c r="H3" s="202" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="211" t="s">
+      <c r="I3" s="204" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="212"/>
-      <c r="K3" s="213"/>
-      <c r="L3" s="214"/>
-      <c r="M3" s="211" t="s">
+      <c r="J3" s="205"/>
+      <c r="K3" s="206"/>
+      <c r="L3" s="207"/>
+      <c r="M3" s="204" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="212"/>
-      <c r="O3" s="213"/>
-      <c r="P3" s="214"/>
+      <c r="N3" s="205"/>
+      <c r="O3" s="206"/>
+      <c r="P3" s="207"/>
       <c r="Q3" s="58"/>
-      <c r="R3" s="193" t="s">
+      <c r="R3" s="208" t="s">
         <v>13</v>
       </c>
-      <c r="S3" s="194"/>
-      <c r="T3" s="215"/>
-      <c r="U3" s="215"/>
-      <c r="V3" s="193" t="s">
+      <c r="S3" s="200"/>
+      <c r="T3" s="209"/>
+      <c r="U3" s="209"/>
+      <c r="V3" s="208" t="s">
         <v>14</v>
       </c>
-      <c r="W3" s="194"/>
-      <c r="X3" s="194"/>
-      <c r="Y3" s="194"/>
-      <c r="Z3" s="194"/>
-      <c r="AA3" s="195"/>
+      <c r="W3" s="200"/>
+      <c r="X3" s="200"/>
+      <c r="Y3" s="200"/>
+      <c r="Z3" s="200"/>
+      <c r="AA3" s="201"/>
       <c r="AB3" s="60"/>
-      <c r="AC3" s="191" t="s">
+      <c r="AC3" s="210" t="s">
         <v>15</v>
       </c>
-      <c r="AD3" s="216" t="s">
+      <c r="AD3" s="212" t="s">
         <v>9</v>
       </c>
-      <c r="AE3" s="193" t="s">
+      <c r="AE3" s="208" t="s">
         <v>13</v>
       </c>
-      <c r="AF3" s="194"/>
-      <c r="AG3" s="195"/>
-      <c r="AH3" s="193" t="s">
+      <c r="AF3" s="200"/>
+      <c r="AG3" s="201"/>
+      <c r="AH3" s="208" t="s">
         <v>14</v>
       </c>
-      <c r="AI3" s="194"/>
-      <c r="AJ3" s="194"/>
-      <c r="AK3" s="195"/>
+      <c r="AI3" s="200"/>
+      <c r="AJ3" s="200"/>
+      <c r="AK3" s="201"/>
       <c r="AL3" s="59"/>
-      <c r="AM3" s="196" t="s">
+      <c r="AM3" s="213" t="s">
         <v>15</v>
       </c>
-      <c r="AN3" s="191" t="s">
+      <c r="AN3" s="210" t="s">
         <v>9</v>
       </c>
-      <c r="AO3" s="200" t="s">
+      <c r="AO3" s="199" t="s">
         <v>13</v>
       </c>
-      <c r="AP3" s="194"/>
-      <c r="AQ3" s="195"/>
-      <c r="AR3" s="193" t="s">
+      <c r="AP3" s="200"/>
+      <c r="AQ3" s="201"/>
+      <c r="AR3" s="208" t="s">
         <v>14</v>
       </c>
-      <c r="AS3" s="194"/>
-      <c r="AT3" s="194"/>
-      <c r="AU3" s="195"/>
+      <c r="AS3" s="200"/>
+      <c r="AT3" s="200"/>
+      <c r="AU3" s="201"/>
       <c r="AV3" s="59"/>
-      <c r="AW3" s="191" t="s">
+      <c r="AW3" s="210" t="s">
         <v>15</v>
       </c>
-      <c r="AX3" s="191" t="s">
+      <c r="AX3" s="210" t="s">
         <v>9</v>
       </c>
-      <c r="AY3" s="200" t="s">
+      <c r="AY3" s="199" t="s">
         <v>13</v>
       </c>
-      <c r="AZ3" s="200"/>
-      <c r="BA3" s="194"/>
-      <c r="BB3" s="195"/>
-      <c r="BC3" s="193" t="s">
+      <c r="AZ3" s="199"/>
+      <c r="BA3" s="200"/>
+      <c r="BB3" s="201"/>
+      <c r="BC3" s="208" t="s">
         <v>14</v>
       </c>
-      <c r="BD3" s="200"/>
-      <c r="BE3" s="200"/>
-      <c r="BF3" s="194"/>
-      <c r="BG3" s="194"/>
-      <c r="BH3" s="195"/>
+      <c r="BD3" s="199"/>
+      <c r="BE3" s="199"/>
+      <c r="BF3" s="200"/>
+      <c r="BG3" s="200"/>
+      <c r="BH3" s="201"/>
       <c r="BI3" s="59"/>
-      <c r="BJ3" s="196" t="s">
+      <c r="BJ3" s="213" t="s">
         <v>16</v>
       </c>
-      <c r="BK3" s="191" t="s">
+      <c r="BK3" s="210" t="s">
         <v>17</v>
       </c>
-      <c r="BL3" s="197" t="s">
+      <c r="BL3" s="214" t="s">
         <v>18</v>
       </c>
-      <c r="BM3" s="198"/>
-      <c r="BN3" s="199"/>
-      <c r="BO3" s="200" t="s">
+      <c r="BM3" s="215"/>
+      <c r="BN3" s="216"/>
+      <c r="BO3" s="199" t="s">
         <v>14</v>
       </c>
-      <c r="BP3" s="194"/>
-      <c r="BQ3" s="194"/>
-      <c r="BR3" s="195"/>
+      <c r="BP3" s="200"/>
+      <c r="BQ3" s="200"/>
+      <c r="BR3" s="201"/>
       <c r="BS3" s="135"/>
     </row>
     <row r="4" spans="1:71" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="202"/>
+      <c r="B4" s="184"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
+      <c r="D4" s="203"/>
+      <c r="E4" s="203"/>
+      <c r="F4" s="203"/>
+      <c r="G4" s="203"/>
+      <c r="H4" s="203"/>
       <c r="I4" s="80" t="s">
         <v>3</v>
       </c>
@@ -7330,8 +7330,8 @@
         <v>24</v>
       </c>
       <c r="AB4" s="60"/>
-      <c r="AC4" s="192"/>
-      <c r="AD4" s="184"/>
+      <c r="AC4" s="211"/>
+      <c r="AD4" s="194"/>
       <c r="AE4" s="62" t="s">
         <v>27</v>
       </c>
@@ -7354,8 +7354,8 @@
         <v>24</v>
       </c>
       <c r="AL4" s="61"/>
-      <c r="AM4" s="183"/>
-      <c r="AN4" s="192"/>
+      <c r="AM4" s="193"/>
+      <c r="AN4" s="211"/>
       <c r="AO4" s="123" t="s">
         <v>27</v>
       </c>
@@ -7378,8 +7378,8 @@
         <v>24</v>
       </c>
       <c r="AV4" s="61"/>
-      <c r="AW4" s="192"/>
-      <c r="AX4" s="192"/>
+      <c r="AW4" s="211"/>
+      <c r="AX4" s="211"/>
       <c r="AY4" s="123" t="s">
         <v>27</v>
       </c>
@@ -7411,8 +7411,8 @@
         <v>24</v>
       </c>
       <c r="BI4" s="61"/>
-      <c r="BJ4" s="183"/>
-      <c r="BK4" s="192"/>
+      <c r="BJ4" s="193"/>
+      <c r="BK4" s="211"/>
       <c r="BL4" s="123" t="s">
         <v>32</v>
       </c>
@@ -7730,19 +7730,19 @@
       </c>
       <c r="E7" s="159">
         <f t="shared" ref="E7:E10" si="4">F7/D7</f>
-        <v>0.87430177170076417</v>
+        <v>0.87212569822829922</v>
       </c>
       <c r="F7" s="87">
         <f t="shared" ref="F7:F37" si="5">D7-H7</f>
-        <v>51026</v>
+        <v>50899</v>
       </c>
       <c r="G7" s="159">
         <f t="shared" ref="G7:G10" si="6">H7/D7</f>
-        <v>0.1256982282992358</v>
+        <v>0.12787430177170075</v>
       </c>
       <c r="H7" s="146">
         <f t="shared" ref="H7:H37" si="7">U7+AG7+AQ7+BB7</f>
-        <v>7336</v>
+        <v>7463</v>
       </c>
       <c r="I7" s="160">
         <f t="shared" ref="I7:I10" si="8">AE7/(AE7+AO7+BL7+AY7)</f>
@@ -7884,11 +7884,11 @@
       </c>
       <c r="AW7" s="110">
         <f t="shared" ref="AW7:AW10" si="22">BA7/AZ7</f>
-        <v>0.62135922330097082</v>
+        <v>0.60750518162975897</v>
       </c>
       <c r="AX7" s="110">
         <f t="shared" ref="AX7:AX10" si="23">BB7/AZ7</f>
-        <v>0.37864077669902912</v>
+        <v>0.39249481837024108</v>
       </c>
       <c r="AY7" s="111">
         <f t="shared" si="1"/>
@@ -7899,11 +7899,11 @@
       </c>
       <c r="BA7" s="120">
         <f t="shared" si="2"/>
-        <v>5696</v>
+        <v>5569</v>
       </c>
       <c r="BB7" s="113">
-        <f>2900+571</f>
-        <v>3471</v>
+        <f>2900+698</f>
+        <v>3598</v>
       </c>
       <c r="BC7" s="112">
         <v>3886</v>
@@ -7971,19 +7971,19 @@
       </c>
       <c r="E8" s="159">
         <f t="shared" si="4"/>
-        <v>0.88197666924465068</v>
+        <v>0.87993039443155452</v>
       </c>
       <c r="F8" s="87">
         <f t="shared" si="5"/>
-        <v>54739</v>
+        <v>54612</v>
       </c>
       <c r="G8" s="159">
         <f t="shared" si="6"/>
-        <v>0.11802333075534932</v>
+        <v>0.12006960556844548</v>
       </c>
       <c r="H8" s="146">
         <f t="shared" si="7"/>
-        <v>7325</v>
+        <v>7452</v>
       </c>
       <c r="I8" s="160">
         <f t="shared" si="8"/>
@@ -8125,11 +8125,11 @@
       </c>
       <c r="AW8" s="110">
         <f t="shared" si="22"/>
-        <v>0.64650264335095564</v>
+        <v>0.63359089060593732</v>
       </c>
       <c r="AX8" s="110">
         <f t="shared" si="23"/>
-        <v>0.3534973566490443</v>
+        <v>0.36640910939406263</v>
       </c>
       <c r="AY8" s="111">
         <f>BA8+BB8</f>
@@ -8140,11 +8140,11 @@
       </c>
       <c r="BA8" s="120">
         <f t="shared" si="2"/>
-        <v>6359</v>
+        <v>6232</v>
       </c>
       <c r="BB8" s="113">
-        <f>2906+571</f>
-        <v>3477</v>
+        <f>2906+698</f>
+        <v>3604</v>
       </c>
       <c r="BC8" s="112">
         <v>4157</v>
@@ -8214,19 +8214,19 @@
       </c>
       <c r="E9" s="159">
         <f t="shared" si="4"/>
-        <v>0.77787780951198315</v>
+        <v>0.77393517943623491</v>
       </c>
       <c r="F9" s="87">
         <f t="shared" si="5"/>
-        <v>25057</v>
+        <v>24930</v>
       </c>
       <c r="G9" s="159">
         <f t="shared" si="6"/>
-        <v>0.2221221904880169</v>
+        <v>0.22606482056376506</v>
       </c>
       <c r="H9" s="146">
         <f t="shared" si="7"/>
-        <v>7155</v>
+        <v>7282</v>
       </c>
       <c r="I9" s="160">
         <f t="shared" si="8"/>
@@ -8368,11 +8368,11 @@
       </c>
       <c r="AW9" s="110">
         <f t="shared" si="22"/>
-        <v>0.23516435031987645</v>
+        <v>0.20714758438120451</v>
       </c>
       <c r="AX9" s="110">
         <f t="shared" si="23"/>
-        <v>0.76483564968012352</v>
+        <v>0.79285241561879549</v>
       </c>
       <c r="AY9" s="111">
         <f t="shared" ref="AY9:AY39" si="32">BA9+BB9</f>
@@ -8383,11 +8383,11 @@
       </c>
       <c r="BA9" s="120">
         <f t="shared" si="2"/>
-        <v>1066</v>
+        <v>939</v>
       </c>
       <c r="BB9" s="113">
-        <f>2896+571</f>
-        <v>3467</v>
+        <f>2896+698</f>
+        <v>3594</v>
       </c>
       <c r="BC9" s="112">
         <v>1472</v>
@@ -8454,19 +8454,19 @@
       </c>
       <c r="E10" s="159">
         <f t="shared" si="4"/>
-        <v>0.75997146377845515</v>
+        <v>0.75585316816914194</v>
       </c>
       <c r="F10" s="87">
         <f t="shared" si="5"/>
-        <v>23436</v>
+        <v>23309</v>
       </c>
       <c r="G10" s="159">
         <f t="shared" si="6"/>
-        <v>0.24002853622154485</v>
+        <v>0.24414683183085803</v>
       </c>
       <c r="H10" s="146">
         <f t="shared" si="7"/>
-        <v>7402</v>
+        <v>7529</v>
       </c>
       <c r="I10" s="160">
         <f t="shared" si="8"/>
@@ -8608,11 +8608,11 @@
       </c>
       <c r="AW10" s="110">
         <f t="shared" si="22"/>
-        <v>0.23557075673364686</v>
+        <v>0.20842240273621207</v>
       </c>
       <c r="AX10" s="110">
         <f t="shared" si="23"/>
-        <v>0.7644292432663532</v>
+        <v>0.79157759726378796</v>
       </c>
       <c r="AY10" s="111">
         <f t="shared" si="32"/>
@@ -8623,11 +8623,11 @@
       </c>
       <c r="BA10" s="120">
         <f t="shared" si="2"/>
-        <v>1102</v>
+        <v>975</v>
       </c>
       <c r="BB10" s="113">
-        <f>3005+571</f>
-        <v>3576</v>
+        <f>3005+698</f>
+        <v>3703</v>
       </c>
       <c r="BC10" s="112">
         <v>1457</v>
@@ -8697,19 +8697,19 @@
       </c>
       <c r="E11" s="159">
         <f t="shared" ref="E11:E24" si="33">F11/D11</f>
-        <v>0.75137176655027438</v>
+        <v>0.74684671844936934</v>
       </c>
       <c r="F11" s="87">
         <f t="shared" si="5"/>
-        <v>21088</v>
+        <v>20961</v>
       </c>
       <c r="G11" s="159">
         <f t="shared" ref="G11:G24" si="34">H11/D11</f>
-        <v>0.24862823344972565</v>
+        <v>0.25315328155063066</v>
       </c>
       <c r="H11" s="146">
         <f t="shared" si="7"/>
-        <v>6978</v>
+        <v>7105</v>
       </c>
       <c r="I11" s="160">
         <f t="shared" ref="I11:I24" si="35">AE11/(AE11+AO11+BL11+AY11)</f>
@@ -8851,11 +8851,11 @@
       </c>
       <c r="AW11" s="110">
         <f t="shared" ref="AW11:AW25" si="47">BA11/AZ11</f>
-        <v>0.22644098810612992</v>
+        <v>0.1973924977127173</v>
       </c>
       <c r="AX11" s="110">
         <f t="shared" ref="AX11:AX25" si="48">BB11/AZ11</f>
-        <v>0.77355901189387011</v>
+        <v>0.80260750228728273</v>
       </c>
       <c r="AY11" s="111">
         <f t="shared" si="32"/>
@@ -8866,11 +8866,11 @@
       </c>
       <c r="BA11" s="120">
         <f t="shared" si="2"/>
-        <v>990</v>
+        <v>863</v>
       </c>
       <c r="BB11" s="113">
-        <f>2811+571</f>
-        <v>3382</v>
+        <f>2811+698</f>
+        <v>3509</v>
       </c>
       <c r="BC11" s="112">
         <v>1416</v>
@@ -8937,19 +8937,19 @@
       </c>
       <c r="E12" s="159">
         <f t="shared" si="33"/>
-        <v>0.87199384114398981</v>
+        <v>0.86974621265751095</v>
       </c>
       <c r="F12" s="87">
         <f t="shared" si="5"/>
-        <v>49271.14</v>
+        <v>49144.14</v>
       </c>
       <c r="G12" s="159">
         <f>H12/D12</f>
-        <v>0.12800615885601022</v>
+        <v>0.13025378734248905</v>
       </c>
       <c r="H12" s="146">
         <f t="shared" si="7"/>
-        <v>7232.8600000000006</v>
+        <v>7359.8600000000006</v>
       </c>
       <c r="I12" s="160">
         <f t="shared" si="35"/>
@@ -9091,11 +9091,11 @@
       </c>
       <c r="AW12" s="110">
         <f t="shared" si="47"/>
-        <v>0.63713495398691422</v>
+        <v>0.62362359699984038</v>
       </c>
       <c r="AX12" s="110">
         <f t="shared" si="48"/>
-        <v>0.36286504601308578</v>
+        <v>0.37637640300015957</v>
       </c>
       <c r="AY12" s="111">
         <f t="shared" si="32"/>
@@ -9106,11 +9106,11 @@
       </c>
       <c r="BA12" s="120">
         <f t="shared" si="2"/>
-        <v>5988.75</v>
+        <v>5861.75</v>
       </c>
       <c r="BB12" s="113">
-        <f>2839.75+571</f>
-        <v>3410.75</v>
+        <f>2839.75+698</f>
+        <v>3537.75</v>
       </c>
       <c r="BC12" s="112">
         <v>3947.67</v>
@@ -9177,19 +9177,19 @@
       </c>
       <c r="E13" s="159">
         <f t="shared" si="33"/>
-        <v>0.87306877669100424</v>
+        <v>0.87088183634109384</v>
       </c>
       <c r="F13" s="87">
         <f t="shared" si="5"/>
-        <v>50700.85</v>
+        <v>50573.85</v>
       </c>
       <c r="G13" s="159">
         <f t="shared" si="34"/>
-        <v>0.12693122330899573</v>
+        <v>0.12911816365890619</v>
       </c>
       <c r="H13" s="146">
         <f t="shared" si="7"/>
-        <v>7371.15</v>
+        <v>7498.15</v>
       </c>
       <c r="I13" s="160">
         <f t="shared" si="35"/>
@@ -9331,11 +9331,11 @@
       </c>
       <c r="AW13" s="169">
         <f t="shared" si="47"/>
-        <v>0.6270761929870815</v>
+        <v>0.61368310044819407</v>
       </c>
       <c r="AX13" s="169">
         <f t="shared" si="48"/>
-        <v>0.37292380701291855</v>
+        <v>0.38631689955180598</v>
       </c>
       <c r="AY13" s="111">
         <f t="shared" si="32"/>
@@ -9346,11 +9346,11 @@
       </c>
       <c r="BA13" s="120">
         <f t="shared" si="2"/>
-        <v>5946.25</v>
+        <v>5819.25</v>
       </c>
       <c r="BB13" s="113">
-        <f>2965.25+571</f>
-        <v>3536.25</v>
+        <f>2965.25+698</f>
+        <v>3663.25</v>
       </c>
       <c r="BC13" s="112">
         <v>3936.21</v>
@@ -9417,19 +9417,19 @@
       </c>
       <c r="E14" s="159">
         <f t="shared" si="33"/>
-        <v>0.87502534640081109</v>
+        <v>0.87287935113213921</v>
       </c>
       <c r="F14" s="87">
         <f t="shared" si="5"/>
-        <v>51784</v>
+        <v>51657</v>
       </c>
       <c r="G14" s="159">
         <f t="shared" si="34"/>
-        <v>0.12497465359918891</v>
+        <v>0.12712064886786076</v>
       </c>
       <c r="H14" s="146">
         <f t="shared" si="7"/>
-        <v>7396</v>
+        <v>7523</v>
       </c>
       <c r="I14" s="160">
         <f t="shared" si="35"/>
@@ -9571,11 +9571,11 @@
       </c>
       <c r="AW14" s="110">
         <f t="shared" si="47"/>
-        <v>0.6259493670886076</v>
+        <v>0.61255274261603376</v>
       </c>
       <c r="AX14" s="110">
         <f t="shared" si="48"/>
-        <v>0.3740506329113924</v>
+        <v>0.38744725738396624</v>
       </c>
       <c r="AY14" s="111">
         <f t="shared" si="32"/>
@@ -9586,11 +9586,11 @@
       </c>
       <c r="BA14" s="120">
         <f t="shared" si="2"/>
-        <v>5934</v>
+        <v>5807</v>
       </c>
       <c r="BB14" s="113">
-        <f>2975+571</f>
-        <v>3546</v>
+        <f>2975+698</f>
+        <v>3673</v>
       </c>
       <c r="BC14" s="112">
         <v>3980</v>
@@ -9657,19 +9657,19 @@
       </c>
       <c r="E15" s="159">
         <f t="shared" si="33"/>
-        <v>0.87429890560875512</v>
+        <v>0.87212722298221612</v>
       </c>
       <c r="F15" s="87">
         <f t="shared" si="5"/>
-        <v>51129</v>
+        <v>51002</v>
       </c>
       <c r="G15" s="159">
         <f t="shared" si="34"/>
-        <v>0.12570109439124488</v>
+        <v>0.12787277701778385</v>
       </c>
       <c r="H15" s="146">
         <f t="shared" si="7"/>
-        <v>7351</v>
+        <v>7478</v>
       </c>
       <c r="I15" s="160">
         <f t="shared" si="35"/>
@@ -9811,11 +9811,11 @@
       </c>
       <c r="AW15" s="169">
         <f t="shared" si="47"/>
-        <v>0.61619565217391303</v>
+        <v>0.60239130434782606</v>
       </c>
       <c r="AX15" s="169">
         <f t="shared" si="48"/>
-        <v>0.38380434782608697</v>
+        <v>0.39760869565217394</v>
       </c>
       <c r="AY15" s="111">
         <f t="shared" si="32"/>
@@ -9826,11 +9826,11 @@
       </c>
       <c r="BA15" s="120">
         <f t="shared" si="2"/>
-        <v>5669</v>
+        <v>5542</v>
       </c>
       <c r="BB15" s="113">
-        <f>2960+571</f>
-        <v>3531</v>
+        <f>2960+698</f>
+        <v>3658</v>
       </c>
       <c r="BC15" s="112">
         <v>3978</v>
@@ -9897,19 +9897,19 @@
       </c>
       <c r="E16" s="159">
         <f t="shared" si="33"/>
-        <v>0.87442746757106393</v>
+        <v>0.87220726548022798</v>
       </c>
       <c r="F16" s="87">
         <f t="shared" si="5"/>
-        <v>50019</v>
+        <v>49892</v>
       </c>
       <c r="G16" s="159">
         <f t="shared" si="34"/>
-        <v>0.12557253242893604</v>
+        <v>0.12779273451977202</v>
       </c>
       <c r="H16" s="146">
         <f t="shared" si="7"/>
-        <v>7183</v>
+        <v>7310</v>
       </c>
       <c r="I16" s="160">
         <f t="shared" si="35"/>
@@ -10051,11 +10051,11 @@
       </c>
       <c r="AW16" s="110">
         <f t="shared" si="47"/>
-        <v>0.62734082397003743</v>
+        <v>0.61335095836087239</v>
       </c>
       <c r="AX16" s="110">
         <f t="shared" si="48"/>
-        <v>0.37265917602996257</v>
+        <v>0.38664904163912756</v>
       </c>
       <c r="AY16" s="111">
         <f t="shared" si="32"/>
@@ -10066,11 +10066,11 @@
       </c>
       <c r="BA16" s="120">
         <f t="shared" si="2"/>
-        <v>5695</v>
+        <v>5568</v>
       </c>
       <c r="BB16" s="113">
-        <f>2812+571</f>
-        <v>3383</v>
+        <f>2812+698</f>
+        <v>3510</v>
       </c>
       <c r="BC16" s="112">
         <v>3993</v>
@@ -10137,19 +10137,19 @@
       </c>
       <c r="E17" s="159">
         <f t="shared" si="33"/>
-        <v>0.83440254379114132</v>
+        <v>0.83086020305701214</v>
       </c>
       <c r="F17" s="87">
         <f t="shared" si="5"/>
-        <v>29915</v>
+        <v>29788</v>
       </c>
       <c r="G17" s="159">
         <f t="shared" si="34"/>
-        <v>0.16559745620885863</v>
+        <v>0.16913979694298784</v>
       </c>
       <c r="H17" s="146">
         <f t="shared" si="7"/>
-        <v>5937</v>
+        <v>6064</v>
       </c>
       <c r="I17" s="160">
         <f t="shared" si="35"/>
@@ -10291,11 +10291,11 @@
       </c>
       <c r="AW17" s="110">
         <f t="shared" si="47"/>
-        <v>0.41313840896145815</v>
+        <v>0.38902601101196127</v>
       </c>
       <c r="AX17" s="110">
         <f t="shared" si="48"/>
-        <v>0.58686159103854185</v>
+        <v>0.61097398898803879</v>
       </c>
       <c r="AY17" s="111">
         <f t="shared" si="32"/>
@@ -10306,11 +10306,11 @@
       </c>
       <c r="BA17" s="120">
         <f t="shared" si="2"/>
-        <v>2176</v>
+        <v>2049</v>
       </c>
       <c r="BB17" s="113">
-        <f>2520+571</f>
-        <v>3091</v>
+        <f>2520+698</f>
+        <v>3218</v>
       </c>
       <c r="BC17" s="112">
         <v>1710</v>
@@ -10377,19 +10377,19 @@
       </c>
       <c r="E18" s="159">
         <f t="shared" si="33"/>
-        <v>0.79401972411210286</v>
+        <v>0.79005617626864744</v>
       </c>
       <c r="F18" s="87">
         <f t="shared" si="5"/>
-        <v>25441.98</v>
+        <v>25314.98</v>
       </c>
       <c r="G18" s="159">
         <f t="shared" si="34"/>
-        <v>0.20598027588789714</v>
+        <v>0.20994382373135262</v>
       </c>
       <c r="H18" s="146">
         <f t="shared" si="7"/>
-        <v>6600.02</v>
+        <v>6727.02</v>
       </c>
       <c r="I18" s="160">
         <f t="shared" si="35"/>
@@ -10531,11 +10531,11 @@
       </c>
       <c r="AW18" s="110">
         <f t="shared" si="47"/>
-        <v>0.31837396530218842</v>
+        <v>0.28957251389046373</v>
       </c>
       <c r="AX18" s="110">
         <f t="shared" si="48"/>
-        <v>0.68162603469781158</v>
+        <v>0.71042748610953621</v>
       </c>
       <c r="AY18" s="111">
         <f t="shared" si="32"/>
@@ -10546,11 +10546,11 @@
       </c>
       <c r="BA18" s="120">
         <f t="shared" si="2"/>
-        <v>1403.87</v>
+        <v>1276.8699999999999</v>
       </c>
       <c r="BB18" s="113">
-        <f>2434.63+571</f>
-        <v>3005.63</v>
+        <f>2434.63+698</f>
+        <v>3132.63</v>
       </c>
       <c r="BC18" s="112">
         <v>1487.79</v>
@@ -10617,19 +10617,19 @@
       </c>
       <c r="E19" s="159">
         <f t="shared" si="33"/>
-        <v>0.87618338474630364</v>
+        <v>0.8739318512215013</v>
       </c>
       <c r="F19" s="87">
         <f t="shared" si="5"/>
-        <v>49422</v>
+        <v>49295</v>
       </c>
       <c r="G19" s="159">
         <f t="shared" si="34"/>
-        <v>0.12381661525369642</v>
+        <v>0.12606814877849873</v>
       </c>
       <c r="H19" s="146">
         <f t="shared" si="7"/>
-        <v>6984</v>
+        <v>7111</v>
       </c>
       <c r="I19" s="160">
         <f t="shared" si="35"/>
@@ -10771,11 +10771,11 @@
       </c>
       <c r="AW19" s="110">
         <f t="shared" ref="AW19" si="55">BA19/AZ19</f>
-        <v>0.66608884073672803</v>
+        <v>0.65232936078006498</v>
       </c>
       <c r="AX19" s="110">
         <f t="shared" ref="AX19" si="56">BB19/AZ19</f>
-        <v>0.33391115926327192</v>
+        <v>0.34767063921993502</v>
       </c>
       <c r="AY19" s="111">
         <f t="shared" si="32"/>
@@ -10786,11 +10786,11 @@
       </c>
       <c r="BA19" s="120">
         <f t="shared" si="2"/>
-        <v>6148</v>
+        <v>6021</v>
       </c>
       <c r="BB19" s="113">
-        <f>2511+571</f>
-        <v>3082</v>
+        <f>2511+698</f>
+        <v>3209</v>
       </c>
       <c r="BC19" s="181">
         <v>4365</v>
@@ -10857,19 +10857,19 @@
       </c>
       <c r="E20" s="159">
         <f t="shared" si="33"/>
-        <v>0.8863983367443069</v>
+        <v>0.88433550985933795</v>
       </c>
       <c r="F20" s="87">
         <f t="shared" si="5"/>
-        <v>54572</v>
+        <v>54445</v>
       </c>
       <c r="G20" s="159">
         <f t="shared" si="34"/>
-        <v>0.11360166325569308</v>
+        <v>0.11566449014066206</v>
       </c>
       <c r="H20" s="146">
         <f t="shared" si="7"/>
-        <v>6994</v>
+        <v>7121</v>
       </c>
       <c r="I20" s="160">
         <f t="shared" si="35"/>
@@ -11011,11 +11011,11 @@
       </c>
       <c r="AW20" s="110">
         <f t="shared" si="47"/>
-        <v>0.67235676944414813</v>
+        <v>0.6588072122052705</v>
       </c>
       <c r="AX20" s="110">
         <f t="shared" si="48"/>
-        <v>0.32764323055585193</v>
+        <v>0.34119278779472956</v>
       </c>
       <c r="AY20" s="111">
         <f t="shared" si="32"/>
@@ -11026,11 +11026,11 @@
       </c>
       <c r="BA20" s="120">
         <f t="shared" si="2"/>
-        <v>6302</v>
+        <v>6175</v>
       </c>
       <c r="BB20" s="113">
-        <f>2500+571</f>
-        <v>3071</v>
+        <f>2500+698</f>
+        <v>3198</v>
       </c>
       <c r="BC20" s="112">
         <v>4763</v>
@@ -11098,19 +11098,19 @@
       </c>
       <c r="E21" s="159">
         <f t="shared" si="33"/>
-        <v>0.88664354702793802</v>
+        <v>0.88458546703830943</v>
       </c>
       <c r="F21" s="87">
         <f t="shared" si="5"/>
-        <v>54713</v>
+        <v>54586</v>
       </c>
       <c r="G21" s="159">
         <f t="shared" si="34"/>
-        <v>0.11335645297206197</v>
+        <v>0.11541453296169055</v>
       </c>
       <c r="H21" s="146">
         <f t="shared" si="7"/>
-        <v>6995</v>
+        <v>7122</v>
       </c>
       <c r="I21" s="160">
         <f t="shared" si="35"/>
@@ -11252,11 +11252,11 @@
       </c>
       <c r="AW21" s="110">
         <f t="shared" si="47"/>
-        <v>0.67924528301886788</v>
+        <v>0.66615114960305188</v>
       </c>
       <c r="AX21" s="110">
         <f t="shared" si="48"/>
-        <v>0.32075471698113206</v>
+        <v>0.33384885039694812</v>
       </c>
       <c r="AY21" s="111">
         <f t="shared" si="32"/>
@@ -11267,11 +11267,11 @@
       </c>
       <c r="BA21" s="120">
         <f t="shared" si="2"/>
-        <v>6588</v>
+        <v>6461</v>
       </c>
       <c r="BB21" s="113">
-        <f>2540+571</f>
-        <v>3111</v>
+        <f>2540+698</f>
+        <v>3238</v>
       </c>
       <c r="BC21" s="112">
         <v>4269</v>
@@ -11339,19 +11339,19 @@
       </c>
       <c r="E22" s="159">
         <f t="shared" si="33"/>
-        <v>0.88848356852580712</v>
+        <v>0.88645163354772649</v>
       </c>
       <c r="F22" s="87">
         <f t="shared" si="5"/>
-        <v>55532</v>
+        <v>55405</v>
       </c>
       <c r="G22" s="159">
         <f t="shared" si="34"/>
-        <v>0.11151643147419282</v>
+        <v>0.11354836645227352</v>
       </c>
       <c r="H22" s="146">
         <f t="shared" si="7"/>
-        <v>6970</v>
+        <v>7097</v>
       </c>
       <c r="I22" s="160">
         <f t="shared" si="35"/>
@@ -11493,11 +11493,11 @@
       </c>
       <c r="AW22" s="110">
         <f t="shared" si="47"/>
-        <v>0.68283120099050765</v>
+        <v>0.66972761040033013</v>
       </c>
       <c r="AX22" s="110">
         <f t="shared" si="48"/>
-        <v>0.31716879900949235</v>
+        <v>0.33027238959966981</v>
       </c>
       <c r="AY22" s="111">
         <f t="shared" si="32"/>
@@ -11508,11 +11508,11 @@
       </c>
       <c r="BA22" s="120">
         <f t="shared" si="2"/>
-        <v>6618</v>
+        <v>6491</v>
       </c>
       <c r="BB22" s="113">
-        <f>2503+571</f>
-        <v>3074</v>
+        <f>2503+698</f>
+        <v>3201</v>
       </c>
       <c r="BC22" s="112">
         <v>3856</v>
@@ -11580,19 +11580,19 @@
       </c>
       <c r="E23" s="159">
         <f t="shared" si="33"/>
-        <v>0.88546113068387611</v>
+        <v>0.88337032037140695</v>
       </c>
       <c r="F23" s="87">
         <f t="shared" si="5"/>
-        <v>53784.68</v>
+        <v>53657.68</v>
       </c>
       <c r="G23" s="159">
         <f t="shared" si="34"/>
-        <v>0.11453886931612393</v>
+        <v>0.11662967962859307</v>
       </c>
       <c r="H23" s="146">
         <f t="shared" si="7"/>
-        <v>6957.32</v>
+        <v>7084.32</v>
       </c>
       <c r="I23" s="160">
         <f t="shared" si="35"/>
@@ -11734,11 +11734,11 @@
       </c>
       <c r="AW23" s="110">
         <f t="shared" si="47"/>
-        <v>0.67248498498498499</v>
+        <v>0.6588642213642214</v>
       </c>
       <c r="AX23" s="110">
         <f t="shared" si="48"/>
-        <v>0.32751501501501501</v>
+        <v>0.34113577863577865</v>
       </c>
       <c r="AY23" s="111">
         <f t="shared" si="32"/>
@@ -11749,11 +11749,11 @@
       </c>
       <c r="BA23" s="120">
         <f t="shared" si="2"/>
-        <v>6270.25</v>
+        <v>6143.25</v>
       </c>
       <c r="BB23" s="113">
-        <f>2482.75+571</f>
-        <v>3053.75</v>
+        <f>2482.75+698</f>
+        <v>3180.75</v>
       </c>
       <c r="BC23" s="112">
         <v>3880.09</v>
@@ -11821,19 +11821,19 @@
       </c>
       <c r="E24" s="159">
         <f t="shared" si="33"/>
-        <v>0.79373936891408847</v>
+        <v>0.78982589670898562</v>
       </c>
       <c r="F24" s="87">
         <f t="shared" si="5"/>
-        <v>25758.43</v>
+        <v>25631.43</v>
       </c>
       <c r="G24" s="159">
         <f t="shared" si="34"/>
-        <v>0.2062606310859115</v>
+        <v>0.21017410329101441</v>
       </c>
       <c r="H24" s="146">
         <f t="shared" si="7"/>
-        <v>6693.57</v>
+        <v>6820.57</v>
       </c>
       <c r="I24" s="160">
         <f t="shared" si="35"/>
@@ -11975,11 +11975,11 @@
       </c>
       <c r="AW24" s="110">
         <f t="shared" si="47"/>
-        <v>0.3718995452666391</v>
+        <v>0.34564902852418355</v>
       </c>
       <c r="AX24" s="110">
         <f t="shared" si="48"/>
-        <v>0.62810045473336085</v>
+        <v>0.65435097147581645</v>
       </c>
       <c r="AY24" s="111">
         <f t="shared" si="32"/>
@@ -11990,11 +11990,11 @@
       </c>
       <c r="BA24" s="120">
         <f t="shared" si="2"/>
-        <v>1799.25</v>
+        <v>1672.25</v>
       </c>
       <c r="BB24" s="113">
-        <f>2467.75+571</f>
-        <v>3038.75</v>
+        <f>2467.75+698</f>
+        <v>3165.75</v>
       </c>
       <c r="BC24" s="112">
         <v>1792.07</v>
@@ -12062,19 +12062,19 @@
       </c>
       <c r="E25" s="159">
         <f t="shared" ref="E25:E36" si="60">F25/D25</f>
-        <v>0.78535530250015906</v>
+        <v>0.78131560531840449</v>
       </c>
       <c r="F25" s="87">
         <f t="shared" si="5"/>
-        <v>24690</v>
+        <v>24563</v>
       </c>
       <c r="G25" s="159">
         <f t="shared" ref="G25:G36" si="61">H25/D25</f>
-        <v>0.21464469749984097</v>
+        <v>0.21868439468159553</v>
       </c>
       <c r="H25" s="146">
         <f t="shared" si="7"/>
-        <v>6748</v>
+        <v>6875</v>
       </c>
       <c r="I25" s="160">
         <f t="shared" ref="I25:I36" si="62">AE25/(AE25+AO25+BL25+AY25)</f>
@@ -12216,11 +12216,11 @@
       </c>
       <c r="AW25" s="169">
         <f t="shared" si="47"/>
-        <v>0.29633765073693613</v>
+        <v>0.26797677534613668</v>
       </c>
       <c r="AX25" s="169">
         <f t="shared" si="48"/>
-        <v>0.70366234926306381</v>
+        <v>0.73202322465386338</v>
       </c>
       <c r="AY25" s="111">
         <f t="shared" si="32"/>
@@ -12231,11 +12231,11 @@
       </c>
       <c r="BA25" s="120">
         <f t="shared" si="2"/>
-        <v>1327</v>
+        <v>1200</v>
       </c>
       <c r="BB25" s="113">
-        <f>2580+571</f>
-        <v>3151</v>
+        <f>2580+698</f>
+        <v>3278</v>
       </c>
       <c r="BC25" s="112">
         <v>2376</v>
@@ -12303,19 +12303,19 @@
       </c>
       <c r="E26" s="159">
         <f t="shared" si="60"/>
-        <v>0.88151611287360165</v>
+        <v>0.87939555852396056</v>
       </c>
       <c r="F26" s="87">
         <f t="shared" si="5"/>
-        <v>52794</v>
+        <v>52667</v>
       </c>
       <c r="G26" s="159">
         <f t="shared" si="61"/>
-        <v>0.1184838871263984</v>
+        <v>0.12060444147603941</v>
       </c>
       <c r="H26" s="146">
         <f t="shared" si="7"/>
-        <v>7096</v>
+        <v>7223</v>
       </c>
       <c r="I26" s="160">
         <f t="shared" si="62"/>
@@ -12457,11 +12457,11 @@
       </c>
       <c r="AW26" s="110">
         <f t="shared" ref="AW26:AW36" si="74">BA26/AZ26</f>
-        <v>0.65027144408251902</v>
+        <v>0.63648208469055378</v>
       </c>
       <c r="AX26" s="110">
         <f t="shared" ref="AX26:AX36" si="75">BB26/AZ26</f>
-        <v>0.34972855591748098</v>
+        <v>0.36351791530944627</v>
       </c>
       <c r="AY26" s="111">
         <f t="shared" si="32"/>
@@ -12472,11 +12472,11 @@
       </c>
       <c r="BA26" s="120">
         <f t="shared" si="2"/>
-        <v>5989</v>
+        <v>5862</v>
       </c>
       <c r="BB26" s="113">
-        <f>2650+571</f>
-        <v>3221</v>
+        <f>2650+698</f>
+        <v>3348</v>
       </c>
       <c r="BC26" s="112">
         <v>4020</v>
@@ -12544,19 +12544,19 @@
       </c>
       <c r="E27" s="159">
         <f t="shared" si="60"/>
-        <v>0.88249332443257678</v>
+        <v>0.88037383177570094</v>
       </c>
       <c r="F27" s="87">
         <f t="shared" si="5"/>
-        <v>52879</v>
+        <v>52752</v>
       </c>
       <c r="G27" s="159">
         <f t="shared" si="61"/>
-        <v>0.11750667556742322</v>
+        <v>0.11962616822429907</v>
       </c>
       <c r="H27" s="146">
         <f t="shared" si="7"/>
-        <v>7041</v>
+        <v>7168</v>
       </c>
       <c r="I27" s="160">
         <f t="shared" si="62"/>
@@ -12698,11 +12698,11 @@
       </c>
       <c r="AW27" s="110">
         <f t="shared" si="74"/>
-        <v>0.6582702702702703</v>
+        <v>0.64454054054054055</v>
       </c>
       <c r="AX27" s="110">
         <f t="shared" si="75"/>
-        <v>0.3417297297297297</v>
+        <v>0.35545945945945945</v>
       </c>
       <c r="AY27" s="111">
         <f t="shared" si="32"/>
@@ -12713,11 +12713,11 @@
       </c>
       <c r="BA27" s="120">
         <f t="shared" si="2"/>
-        <v>6089</v>
+        <v>5962</v>
       </c>
       <c r="BB27" s="113">
-        <f>2590+571</f>
-        <v>3161</v>
+        <f>2590+698</f>
+        <v>3288</v>
       </c>
       <c r="BC27" s="112">
         <v>4050</v>
@@ -12785,19 +12785,19 @@
       </c>
       <c r="E28" s="159">
         <f t="shared" si="60"/>
-        <v>0.87710737961436214</v>
+        <v>0.87497055557425041</v>
       </c>
       <c r="F28" s="87">
         <f t="shared" si="5"/>
-        <v>52130</v>
+        <v>52003</v>
       </c>
       <c r="G28" s="159">
         <f t="shared" si="61"/>
-        <v>0.12289262038563785</v>
+        <v>0.12502944442574956</v>
       </c>
       <c r="H28" s="146">
         <f t="shared" si="7"/>
-        <v>7304</v>
+        <v>7431</v>
       </c>
       <c r="I28" s="160">
         <f t="shared" si="62"/>
@@ -12939,11 +12939,11 @@
       </c>
       <c r="AW28" s="110">
         <f t="shared" si="74"/>
-        <v>0.66147151098066992</v>
+        <v>0.64861856087440539</v>
       </c>
       <c r="AX28" s="110">
         <f t="shared" si="75"/>
-        <v>0.33852848901933003</v>
+        <v>0.35138143912559455</v>
       </c>
       <c r="AY28" s="111">
         <f t="shared" si="32"/>
@@ -12954,11 +12954,11 @@
       </c>
       <c r="BA28" s="120">
         <f t="shared" si="2"/>
-        <v>6536</v>
+        <v>6409</v>
       </c>
       <c r="BB28" s="113">
-        <f>2774+571</f>
-        <v>3345</v>
+        <f>2774+698</f>
+        <v>3472</v>
       </c>
       <c r="BC28" s="112">
         <v>3588</v>
@@ -13026,19 +13026,19 @@
       </c>
       <c r="E29" s="159">
         <f t="shared" si="60"/>
-        <v>0.87693298969072164</v>
+        <v>0.87477957135105811</v>
       </c>
       <c r="F29" s="87">
         <f t="shared" si="5"/>
-        <v>51718</v>
+        <v>51591</v>
       </c>
       <c r="G29" s="159">
         <f t="shared" si="61"/>
-        <v>0.12306701030927836</v>
+        <v>0.12522042864894195</v>
       </c>
       <c r="H29" s="146">
         <f t="shared" si="7"/>
-        <v>7258</v>
+        <v>7385</v>
       </c>
       <c r="I29" s="160">
         <f t="shared" si="62"/>
@@ -13180,11 +13180,11 @@
       </c>
       <c r="AW29" s="110">
         <f t="shared" si="74"/>
-        <v>0.66310806727767146</v>
+        <v>0.65031725249269812</v>
       </c>
       <c r="AX29" s="110">
         <f t="shared" si="75"/>
-        <v>0.33689193272232854</v>
+        <v>0.34968274750730183</v>
       </c>
       <c r="AY29" s="111">
         <f t="shared" si="32"/>
@@ -13195,11 +13195,11 @@
       </c>
       <c r="BA29" s="120">
         <f t="shared" si="2"/>
-        <v>6584</v>
+        <v>6457</v>
       </c>
       <c r="BB29" s="113">
-        <f>2774+571</f>
-        <v>3345</v>
+        <f>2774+698</f>
+        <v>3472</v>
       </c>
       <c r="BC29" s="112">
         <v>3956</v>
@@ -13267,19 +13267,19 @@
       </c>
       <c r="E30" s="159">
         <f t="shared" si="60"/>
-        <v>0.87670165229138519</v>
+        <v>0.87450206103432748</v>
       </c>
       <c r="F30" s="87">
         <f t="shared" si="5"/>
-        <v>50619</v>
+        <v>50492</v>
       </c>
       <c r="G30" s="159">
         <f t="shared" si="61"/>
-        <v>0.12329834770861478</v>
+        <v>0.12549793896567252</v>
       </c>
       <c r="H30" s="146">
         <f t="shared" si="7"/>
-        <v>7119</v>
+        <v>7246</v>
       </c>
       <c r="I30" s="160">
         <f t="shared" si="62"/>
@@ -13421,11 +13421,11 @@
       </c>
       <c r="AW30" s="110">
         <f t="shared" si="74"/>
-        <v>0.65467701342281881</v>
+        <v>0.64135906040268453</v>
       </c>
       <c r="AX30" s="110">
         <f t="shared" si="75"/>
-        <v>0.34532298657718119</v>
+        <v>0.35864093959731541</v>
       </c>
       <c r="AY30" s="111">
         <f t="shared" si="32"/>
@@ -13436,11 +13436,11 @@
       </c>
       <c r="BA30" s="120">
         <f t="shared" si="2"/>
-        <v>6243</v>
+        <v>6116</v>
       </c>
       <c r="BB30" s="113">
-        <f>2722+571</f>
-        <v>3293</v>
+        <f>2722+698</f>
+        <v>3420</v>
       </c>
       <c r="BC30" s="112">
         <v>4141</v>
@@ -13508,19 +13508,19 @@
       </c>
       <c r="E31" s="159">
         <f t="shared" si="60"/>
-        <v>0.78944350555287301</v>
+        <v>0.78561081603090299</v>
       </c>
       <c r="F31" s="87">
         <f t="shared" si="5"/>
-        <v>26159</v>
+        <v>26032</v>
       </c>
       <c r="G31" s="159">
         <f t="shared" si="61"/>
-        <v>0.21055649444712699</v>
+        <v>0.21438918396909706</v>
       </c>
       <c r="H31" s="146">
         <f t="shared" si="7"/>
-        <v>6977</v>
+        <v>7104</v>
       </c>
       <c r="I31" s="160">
         <f t="shared" si="62"/>
@@ -13662,11 +13662,11 @@
       </c>
       <c r="AW31" s="110">
         <f t="shared" si="74"/>
-        <v>0.34060955518945635</v>
+        <v>0.31445634266886324</v>
       </c>
       <c r="AX31" s="110">
         <f t="shared" si="75"/>
-        <v>0.65939044481054365</v>
+        <v>0.68554365733113676</v>
       </c>
       <c r="AY31" s="111">
         <f t="shared" si="32"/>
@@ -13677,11 +13677,11 @@
       </c>
       <c r="BA31" s="120">
         <f t="shared" si="2"/>
-        <v>1654</v>
+        <v>1527</v>
       </c>
       <c r="BB31" s="113">
-        <f>2631+571</f>
-        <v>3202</v>
+        <f>2631+698</f>
+        <v>3329</v>
       </c>
       <c r="BC31" s="112">
         <v>1654</v>
@@ -13749,19 +13749,19 @@
       </c>
       <c r="E32" s="159">
         <f t="shared" si="60"/>
-        <v>0.7590972222222222</v>
+        <v>0.75468749999999996</v>
       </c>
       <c r="F32" s="87">
         <f t="shared" si="5"/>
-        <v>21862</v>
+        <v>21735</v>
       </c>
       <c r="G32" s="159">
         <f t="shared" si="61"/>
-        <v>0.24090277777777777</v>
+        <v>0.24531249999999999</v>
       </c>
       <c r="H32" s="146">
         <f t="shared" si="7"/>
-        <v>6938</v>
+        <v>7065</v>
       </c>
       <c r="I32" s="160">
         <f t="shared" si="62"/>
@@ -13903,11 +13903,11 @@
       </c>
       <c r="AW32" s="169">
         <f t="shared" si="74"/>
-        <v>0.27952668006251397</v>
+        <v>0.25117213663764232</v>
       </c>
       <c r="AX32" s="169">
         <f t="shared" si="75"/>
-        <v>0.72047331993748609</v>
+        <v>0.74882786336235763</v>
       </c>
       <c r="AY32" s="111">
         <f t="shared" si="32"/>
@@ -13918,11 +13918,11 @@
       </c>
       <c r="BA32" s="120">
         <f t="shared" si="2"/>
-        <v>1252</v>
+        <v>1125</v>
       </c>
       <c r="BB32" s="113">
-        <f>2656+571</f>
-        <v>3227</v>
+        <f>2656+698</f>
+        <v>3354</v>
       </c>
       <c r="BC32" s="112">
         <v>1966</v>
@@ -13990,19 +13990,19 @@
       </c>
       <c r="E33" s="159">
         <f t="shared" si="60"/>
-        <v>0.88062583222370172</v>
+        <v>0.87851198402130493</v>
       </c>
       <c r="F33" s="87">
         <f t="shared" si="5"/>
-        <v>52908</v>
+        <v>52781</v>
       </c>
       <c r="G33" s="159">
         <f t="shared" si="61"/>
-        <v>0.11937416777629827</v>
+        <v>0.12148801597869507</v>
       </c>
       <c r="H33" s="146">
         <f t="shared" si="7"/>
-        <v>7172</v>
+        <v>7299</v>
       </c>
       <c r="I33" s="160">
         <f t="shared" si="62"/>
@@ -14143,11 +14143,11 @@
       </c>
       <c r="AW33" s="169">
         <f t="shared" si="74"/>
-        <v>0.67248176621328604</v>
+        <v>0.65996451803666467</v>
       </c>
       <c r="AX33" s="169">
         <f t="shared" si="75"/>
-        <v>0.32751823378671396</v>
+        <v>0.34003548196333533</v>
       </c>
       <c r="AY33" s="111">
         <f t="shared" si="32"/>
@@ -14158,11 +14158,11 @@
       </c>
       <c r="BA33" s="120">
         <f t="shared" si="2"/>
-        <v>6823</v>
+        <v>6696</v>
       </c>
       <c r="BB33" s="113">
-        <f>2752+571</f>
-        <v>3323</v>
+        <f>2752+698</f>
+        <v>3450</v>
       </c>
       <c r="BC33" s="112">
         <v>3929</v>
@@ -14230,19 +14230,19 @@
       </c>
       <c r="E34" s="159">
         <f t="shared" si="60"/>
-        <v>0.89328537170263789</v>
+        <v>0.89142832075802769</v>
       </c>
       <c r="F34" s="87">
         <f t="shared" si="5"/>
-        <v>61090</v>
+        <v>60963</v>
       </c>
       <c r="G34" s="159">
         <f t="shared" si="61"/>
-        <v>0.10671462829736211</v>
+        <v>0.10857167924197228</v>
       </c>
       <c r="H34" s="146">
         <f t="shared" si="7"/>
-        <v>7298</v>
+        <v>7425</v>
       </c>
       <c r="I34" s="160">
         <f t="shared" si="62"/>
@@ -14384,11 +14384,11 @@
       </c>
       <c r="AW34" s="110">
         <f t="shared" si="74"/>
-        <v>0.70287567946694718</v>
+        <v>0.69174118884797475</v>
       </c>
       <c r="AX34" s="110">
         <f t="shared" si="75"/>
-        <v>0.29712432053305277</v>
+        <v>0.30825881115202525</v>
       </c>
       <c r="AY34" s="111">
         <f t="shared" si="32"/>
@@ -14399,11 +14399,11 @@
       </c>
       <c r="BA34" s="120">
         <f t="shared" si="2"/>
-        <v>8017</v>
+        <v>7890</v>
       </c>
       <c r="BB34" s="113">
-        <f>2818+571</f>
-        <v>3389</v>
+        <f>2818+698</f>
+        <v>3516</v>
       </c>
       <c r="BC34" s="112">
         <v>4893</v>
@@ -14471,19 +14471,19 @@
       </c>
       <c r="E35" s="159">
         <f t="shared" si="60"/>
-        <v>0.87938783544386856</v>
+        <v>0.87730463880322818</v>
       </c>
       <c r="F35" s="87">
         <f t="shared" si="5"/>
-        <v>53611</v>
+        <v>53484</v>
       </c>
       <c r="G35" s="159">
         <f t="shared" si="61"/>
-        <v>0.12061216455613148</v>
+        <v>0.12269536119677187</v>
       </c>
       <c r="H35" s="146">
         <f t="shared" si="7"/>
-        <v>7353</v>
+        <v>7480</v>
       </c>
       <c r="I35" s="160">
         <f t="shared" si="62"/>
@@ -14625,11 +14625,11 @@
       </c>
       <c r="AW35" s="110">
         <f t="shared" si="74"/>
-        <v>0.64685855772206746</v>
+        <v>0.63375631899308782</v>
       </c>
       <c r="AX35" s="110">
         <f t="shared" si="75"/>
-        <v>0.35314144227793254</v>
+        <v>0.36624368100691218</v>
       </c>
       <c r="AY35" s="111">
         <f t="shared" si="32"/>
@@ -14640,11 +14640,11 @@
       </c>
       <c r="BA35" s="120">
         <f t="shared" si="2"/>
-        <v>6270</v>
+        <v>6143</v>
       </c>
       <c r="BB35" s="113">
-        <f>2852+571</f>
-        <v>3423</v>
+        <f>2852+698</f>
+        <v>3550</v>
       </c>
       <c r="BC35" s="112">
         <v>4573</v>
@@ -14712,19 +14712,19 @@
       </c>
       <c r="E36" s="159">
         <f t="shared" si="60"/>
-        <v>0.88056981944674506</v>
+        <v>0.87846612555905246</v>
       </c>
       <c r="F36" s="87">
         <f t="shared" si="5"/>
-        <v>53160</v>
+        <v>53033</v>
       </c>
       <c r="G36" s="159">
         <f t="shared" si="61"/>
-        <v>0.11943018055325492</v>
+        <v>0.12153387444094749</v>
       </c>
       <c r="H36" s="146">
         <f t="shared" si="7"/>
-        <v>7210</v>
+        <v>7337</v>
       </c>
       <c r="I36" s="160">
         <f t="shared" si="62"/>
@@ -14866,11 +14866,11 @@
       </c>
       <c r="AW36" s="110">
         <f t="shared" si="74"/>
-        <v>0.65210066336737915</v>
+        <v>0.63872801937453938</v>
       </c>
       <c r="AX36" s="110">
         <f t="shared" si="75"/>
-        <v>0.34789933663262085</v>
+        <v>0.36127198062546068</v>
       </c>
       <c r="AY36" s="111">
         <f t="shared" si="32"/>
@@ -14881,11 +14881,11 @@
       </c>
       <c r="BA36" s="120">
         <f t="shared" si="2"/>
-        <v>6193</v>
+        <v>6066</v>
       </c>
       <c r="BB36" s="113">
-        <f>2733+571</f>
-        <v>3304</v>
+        <f>2733+698</f>
+        <v>3431</v>
       </c>
       <c r="BC36" s="112">
         <v>4318</v>
@@ -15150,6 +15150,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="BJ1:BR2"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="AN3:AN4"/>
+    <mergeCell ref="AR3:AU3"/>
+    <mergeCell ref="BJ3:BJ4"/>
+    <mergeCell ref="BK3:BK4"/>
+    <mergeCell ref="BL3:BN3"/>
+    <mergeCell ref="BO3:BR3"/>
+    <mergeCell ref="AW1:BH2"/>
+    <mergeCell ref="AW3:AW4"/>
+    <mergeCell ref="AX3:AX4"/>
+    <mergeCell ref="AY3:BB3"/>
+    <mergeCell ref="BC3:BH3"/>
     <mergeCell ref="B1:B4"/>
     <mergeCell ref="D1:P2"/>
     <mergeCell ref="R1:AA2"/>
@@ -15166,22 +15182,6 @@
     <mergeCell ref="AE3:AG3"/>
     <mergeCell ref="AH3:AK3"/>
     <mergeCell ref="AM3:AM4"/>
-    <mergeCell ref="BJ1:BR2"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="AN3:AN4"/>
-    <mergeCell ref="AR3:AU3"/>
-    <mergeCell ref="BJ3:BJ4"/>
-    <mergeCell ref="BK3:BK4"/>
-    <mergeCell ref="BL3:BN3"/>
-    <mergeCell ref="BO3:BR3"/>
-    <mergeCell ref="AW1:BH2"/>
-    <mergeCell ref="AW3:AW4"/>
-    <mergeCell ref="AX3:AX4"/>
-    <mergeCell ref="AY3:BB3"/>
-    <mergeCell ref="BC3:BH3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="88" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
@@ -19288,12 +19288,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19544,22 +19548,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E773259D-A732-42EE-8607-1A2C0CE89915}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63CCCE7E-45E5-4704-BEA3-B42CAB7F9CAC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
+    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -19584,12 +19587,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63CCCE7E-45E5-4704-BEA3-B42CAB7F9CAC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E773259D-A732-42EE-8607-1A2C0CE89915}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
-    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>